--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -484,7 +484,11 @@
       </c>
     </row>
     <row r="2" ht="72" customHeight="1">
-      <c r="A2" s="1" t="inlineStr"/>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
           <t>1</t>
@@ -535,7 +539,11 @@
       </c>
     </row>
     <row r="3" ht="72" customHeight="1">
-      <c r="A3" s="1" t="inlineStr"/>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
           <t>2</t>
@@ -586,7 +594,11 @@
       </c>
     </row>
     <row r="4" ht="90" customHeight="1">
-      <c r="A4" s="1" t="inlineStr"/>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
           <t>2</t>
@@ -638,7 +650,11 @@
       </c>
     </row>
     <row r="5" ht="108" customHeight="1">
-      <c r="A5" s="1" t="inlineStr"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
           <t>3</t>
@@ -691,7 +707,11 @@
       </c>
     </row>
     <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="1" t="inlineStr"/>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
           <t>3</t>
@@ -744,7 +764,11 @@
       </c>
     </row>
     <row r="7" ht="54" customHeight="1">
-      <c r="A7" s="1" t="inlineStr"/>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
           <t>4</t>
@@ -794,7 +818,11 @@
       </c>
     </row>
     <row r="8" ht="36" customHeight="1">
-      <c r="A8" s="1" t="inlineStr"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
           <t>4</t>
@@ -843,7 +871,11 @@
       </c>
     </row>
     <row r="9" ht="54" customHeight="1">
-      <c r="A9" s="1" t="inlineStr"/>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
           <t>4</t>
@@ -893,7 +925,11 @@
       </c>
     </row>
     <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="1" t="inlineStr"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
           <t>5</t>
@@ -944,7 +980,11 @@
       </c>
     </row>
     <row r="11" ht="108" customHeight="1">
-      <c r="A11" s="1" t="inlineStr"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
           <t>5</t>
@@ -997,7 +1037,11 @@
       </c>
     </row>
     <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="1" t="inlineStr"/>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
           <t>6</t>
@@ -1046,7 +1090,11 @@
       </c>
     </row>
     <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="1" t="inlineStr"/>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
           <t>6</t>
@@ -1097,7 +1145,11 @@
       </c>
     </row>
     <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="1" t="inlineStr"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
           <t>6</t>
@@ -1147,7 +1199,11 @@
       </c>
     </row>
     <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="1" t="inlineStr"/>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
           <t>7</t>
@@ -1196,7 +1252,11 @@
       </c>
     </row>
     <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="1" t="inlineStr"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
           <t>7</t>

--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1304,6 +1304,2158 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="90" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>26433067858</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the third word in the same way as the second word
+is related to the first word. (The words must be considered as meaningful English
+words and must not be related to each other based on the number of letters/number of
+consonants/vowels in the word.)
+Animal : Zoology :: Plant : ?</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t>Palaeontology</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t>Biology</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t>Botany</t>
+        </is>
+      </c>
+      <c r="J17" s="1" t="inlineStr"/>
+    </row>
+    <row r="18" ht="126" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>26433069255</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>Which option represents the correct order of the given words as they would appear in
+the English dictionary?
+1 Sailboat
+2 Saint
+3 Sailor
+4 Sanction
+5 Sadly</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>3, 5, 1, 2, 4</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>5, 1, 3, 2, 4</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>5, 1, 3, 4, 2</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t>5, 3, 1, 2, 4</t>
+        </is>
+      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+    </row>
+    <row r="19" ht="162" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>26433093138</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>Two Statements are given followed by Two conclusions numbered I and II. Assuming
+the statements to be true, even if they seem to be at variance with commonly known
+facts, decide which of the conclusions logically follow(s) from the statements.
+Statements:
+All buses are cars.
+No jeep is a car.
+Conclusions:
+I. No car is a jeep.
+II. No jeep is a bus.</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion II follows.</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t>Neither conclusion I nor II follows.</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t>Both conclusions I and II follows.</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows.</t>
+        </is>
+      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>26433057903</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>In a code language, 'PARUL' is coded as RDTXN and 'MADHU' is coded as ODFKW.
+How will 'VIJAY' be coded in the same language?</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>XKLCB</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>XLLDA</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>XLMDA</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>XMLCA</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>26433085678</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>Pointing at a girl, Seema said, “She is my father’s mother’s husband’s only son’s
+daughter.” How is that girl related to Seema?</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>Mother’s sister</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t>Daughter</t>
+        </is>
+      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="90" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>26433057314</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>In this question, the statement is followed by two conclusions. Which of the two
+conclusions is/are true?
+Statement: A ≤ D &lt; C = B &gt; E ≥ F &lt; G
+Conclusions: I. B &gt; A
+II. C &lt; F</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>Neither conclusion I nor II is true</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>Both conclusions I and II are true</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion II is true</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I is true</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>26433069199</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following numbers will replace the question mark (?) in the given series?
+3, 7, 5, 61, 363 ?</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>26433068990</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that represents the letters that, when sequentially placed from left to
+right in the blanks below, will complete the letter series.
+_ M _ B A J M Q _ A _ M Q B _ J _ _ B _</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>J Q B J A M Q A</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t>B Q A J M Q A B</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t>A M B Q J M J Q</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t>J A M M Q A B J</t>
+        </is>
+      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>26433079500</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>Town C is to the south of Town A. Town D is to the west of town A. Town B is to the
+east of town D. Town E is to the south of town B and south-east of Town C. What is the
+position of town A with respect to town B?</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>26433067321</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>In a certain code language, 'DAM’ is coded as '50' and 'PAD' is coded as '47'. How will
+'MAP' be coded in that language?</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>26433056550</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>Select the letter-cluster that will replace the question mark (?) in the given series and
+make it logically complete.
+FRP, HTR, JVT, ?, NZX</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>IWV</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>KWU</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t>IUS</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t>LXV</t>
+        </is>
+      </c>
+      <c r="J27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>26433079440</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>Which letter cluster will replace the question mark (?) to complete the given series?
+GROW, NJGG, ?, BTQA, ILIK</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>YDER</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t>VIWQ</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t>PSJW</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t>UBYQ</t>
+        </is>
+      </c>
+      <c r="J28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="126" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>26433069104</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the number are related in the same way as the numbers of the
+given sets. (NOTE : Operations should be performed on the whole numbers, without
+breaking down the numbers into its constituent digits. E.g. 13 – Operations on 13 such
+as adding /subtracting /multiplying etc. to 13 can be performed. Breaking down 13 into
+1 and 3 and then performing mathematical operations on 1 and 3 is not allowed.)
+(182, 156, 13)
+(238, 212, 15)</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>(370, 348, 19)</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t>(336, 302, 17)</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t>(142, 126, 11)</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t>(337, 311, 18)</t>
+        </is>
+      </c>
+      <c r="J29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" ht="216" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>26433058075</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>Read the given statements and conclusions carefully. Assuming that the information
+given in the statements is true, even if it appears to be at variance with commonly
+known facts, decide which of the given conclusions logically follow(s) from the
+statements.
+Statements:
+• All trojans are fairies.
+• No fairy is a flower.
+• All viruses are trojans.
+Conclusions:
+I. No flower is a trojan.
+II. Some viruses are trojans.
+III. No trojan is a virus.</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I and III follow</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I and II follow</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion II follows</t>
+        </is>
+      </c>
+      <c r="J30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>26433067622</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following numbers will replace the question mark (?) in the given series?
+420, 462, 506, ?, 600, 650, 702</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="G31" s="1" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="H31" s="1" t="inlineStr">
+        <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="I31" s="1" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="J31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>26433057236</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>Three of the following four letter-clusters are alike in a certain way and one is different.
+Pick the odd one out.</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>TWGD</t>
+        </is>
+      </c>
+      <c r="G32" s="1" t="inlineStr">
+        <is>
+          <t>ADZE</t>
+        </is>
+      </c>
+      <c r="H32" s="1" t="inlineStr">
+        <is>
+          <t>PSKH</t>
+        </is>
+      </c>
+      <c r="I32" s="1" t="inlineStr">
+        <is>
+          <t>FIUR</t>
+        </is>
+      </c>
+      <c r="J32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" ht="144" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>26433067918</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are related in the same way as are the numbers of
+the following set.
+(NOTE: Operations should be performed on the whole numbers, without breaking
+down the numbers into its constituent digits. E.g. 13 – Operations on 13 such as
+adding /subtracting /multiplying etc. to 13 can be performed. Breaking down 13 into 1
+and 3 and then performing mathematical operations on 1 and 3 is NOT allowed)
+(212, 101, 111)
+(256, 123, 133)</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>(182, 74, 108)</t>
+        </is>
+      </c>
+      <c r="G33" s="1" t="inlineStr">
+        <is>
+          <t>(240, 105, 110)</t>
+        </is>
+      </c>
+      <c r="H33" s="1" t="inlineStr">
+        <is>
+          <t>(196, 89, 91)</t>
+        </is>
+      </c>
+      <c r="I33" s="1" t="inlineStr">
+        <is>
+          <t>(292, 122, 160)</t>
+        </is>
+      </c>
+      <c r="J33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" ht="54" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>26433068692</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>Select the correct combination of mathematical signs to sequentially replace the *
+signs and balance the given equation.
+65	*	56	*	8	*	19	*	2	*	34</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>−, ÷, −, ×, =</t>
+        </is>
+      </c>
+      <c r="G34" s="1" t="inlineStr">
+        <is>
+          <t>+, +, −, ×, =</t>
+        </is>
+      </c>
+      <c r="H34" s="1" t="inlineStr">
+        <is>
+          <t>+, ×, −, ×, =</t>
+        </is>
+      </c>
+      <c r="I34" s="1" t="inlineStr">
+        <is>
+          <t>+, ÷, −, ×, =</t>
+        </is>
+      </c>
+      <c r="J34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>26433057998</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>Three of the following four letter-clusters are alike in a certain way and one is different.
+Pick the odd one out.</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>MPJ</t>
+        </is>
+      </c>
+      <c r="G35" s="1" t="inlineStr">
+        <is>
+          <t>DIB</t>
+        </is>
+      </c>
+      <c r="H35" s="1" t="inlineStr">
+        <is>
+          <t>HKE</t>
+        </is>
+      </c>
+      <c r="I35" s="1" t="inlineStr">
+        <is>
+          <t>TWQ</t>
+        </is>
+      </c>
+      <c r="J35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36" ht="216" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>26433058051</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>Three statements are given followed by three conclusions numbered I, II and III.
+Assuming the statements to be true, even if they seem to be at variance with
+commonly known facts, decide which of the conclusions logically follow(s) from the
+statements.
+Statements:
+All beards are nails.
+Some nails are rings.
+All rings are pendants.
+Conclusions:
+I. All rings can never be nails.
+II. Some beards are rings.
+III. Some nails are pendants.</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusions II and III follow</t>
+        </is>
+      </c>
+      <c r="G36" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion III follows</t>
+        </is>
+      </c>
+      <c r="H36" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusions I and II follow</t>
+        </is>
+      </c>
+      <c r="I36" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows</t>
+        </is>
+      </c>
+      <c r="J36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="126" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>26433068349</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are NOT related in the same way as are the
+numbers of the given set.
+(NOTE: Operations should be performed on the whole numbers, without breaking
+down the numbers into its constituent digits. E.g. 13 – Operations on 13 such as
+adding /subtracting /multiplying etc. to 13 can be performed. Breaking down 13 into 1
+and 3 and then performing mathematical operations on 1 and 3 is not allowed)
+(16, 11, 377)</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>(12, 15, 367)</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>(16, 14, 452)</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>(14, 12, 340)</t>
+        </is>
+      </c>
+      <c r="I37" s="1" t="inlineStr">
+        <is>
+          <t>(18, 13, 493)</t>
+        </is>
+      </c>
+      <c r="J37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" ht="72" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>26433076698</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>Town M is to the west of Town D. Town C is to the south-west of Town D. Town D is to
+the north of Town B. Town A is to the south of Town C. Town M is to the north of Town
+C. Town B is to the north-east of Town A.What is the position of Town B with respect to
+Town M?</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="G38" s="1" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
+      <c r="H38" s="1" t="inlineStr">
+        <is>
+          <t>South-east</t>
+        </is>
+      </c>
+      <c r="I38" s="1" t="inlineStr">
+        <is>
+          <t>North-west</t>
+        </is>
+      </c>
+      <c r="J38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" ht="126" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>26433069113</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are related in the same way as the numbers of the
+given sets. (NOTE : Operations should be performed on the whole numbers, without
+breaking down the numbers into its constituent digits. E.g. 13 – Operations on 13 such
+as adding /subtracting /multiplying etc. to 13 can be performed. Breaking down 13 into
+1 and 3 and then performing mathematical operations on 1 and 3 is not allowed.)
+(11, 100, 221)
+(14, 104, 300)</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>(15, 175, 390)</t>
+        </is>
+      </c>
+      <c r="G39" s="1" t="inlineStr">
+        <is>
+          <t>(17, 131, 410)</t>
+        </is>
+      </c>
+      <c r="H39" s="1" t="inlineStr">
+        <is>
+          <t>(19, 121, 445)</t>
+        </is>
+      </c>
+      <c r="I39" s="1" t="inlineStr">
+        <is>
+          <t>(13, 162, 331)</t>
+        </is>
+      </c>
+      <c r="J39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" ht="54" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>26433067684</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>Which two numbers from amongst the given options should be interchanged to make
+the given equation correct?
+(357 ÷ 2 + 3) ÷ 11 − 4 = (28 × 3 + 7) ÷ 9</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>11 and 28</t>
+        </is>
+      </c>
+      <c r="G40" s="1" t="inlineStr">
+        <is>
+          <t>2 and 3</t>
+        </is>
+      </c>
+      <c r="H40" s="1" t="inlineStr">
+        <is>
+          <t>7 and 9</t>
+        </is>
+      </c>
+      <c r="I40" s="1" t="inlineStr">
+        <is>
+          <t>2 and 9</t>
+        </is>
+      </c>
+      <c r="J40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>26433067890</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the third number in the same way as the second
+number is related to the first number and the sixth number is related to the fifth
+number.
+6 : 43 :: 11 : ? :: 4 : 21</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="G41" s="1" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="H41" s="1" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I41" s="1" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="J41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42" ht="54" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>26433057590</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the third term in the same way as the second term is
+related to the first term and the sixth term is related to the fifth term.
+16 : 50 :: 49 : ? :: 144 : 338</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="G42" s="1" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="H42" s="1" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="I42" s="1" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="J42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>26433056182</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the fifth letter-cluster in the same way as the second
+letter-cluster is related to the first letter-cluster and the fourth letter-cluster is related
+to the third letter-cluster.
+MASTER : TSAMRE :: SMILES : LIMSSE :: FLIMSY : ?</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>FLIMYS</t>
+        </is>
+      </c>
+      <c r="G43" s="1" t="inlineStr">
+        <is>
+          <t>FILMYS</t>
+        </is>
+      </c>
+      <c r="H43" s="1" t="inlineStr">
+        <is>
+          <t>MILFYS</t>
+        </is>
+      </c>
+      <c r="I43" s="1" t="inlineStr">
+        <is>
+          <t>MLYFIS</t>
+        </is>
+      </c>
+      <c r="J43" s="1" t="inlineStr"/>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>26433067624</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following numbers will replace the question mark (?) in the given series?
+144, 127, 110, ?, 76, 59</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G44" s="1" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H44" s="1" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="I44" s="1" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="J44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45" ht="72" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>26433091437</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>Six friends A, C, D, E, F and G are sitting in a straight row, facing north. They are
+waiting for their seventh friend B to join. Exactly three people are sitting to the left of
+A. C is occupying an end seat. F and D are immediate neighbours of G. If D is sitting to
+the immediate left of A, and E is second to the right of A, where will B sit?</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>Fourth to the right of F</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>Fifth to the right of G</t>
+        </is>
+      </c>
+      <c r="H45" s="1" t="inlineStr">
+        <is>
+          <t>To the immediate right of E</t>
+        </is>
+      </c>
+      <c r="I45" s="1" t="inlineStr">
+        <is>
+          <t>Third to the right of D</t>
+        </is>
+      </c>
+      <c r="J45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46" ht="54" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>26433067670</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>If A denotes ‘+’, B denotes ‘×’, C denotes ‘−’, and D denotes ‘÷’, then what will come in
+place of ‘?’ in the following equation?
+140 D 7 A 30 = 25 B ? D 8</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G46" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H46" s="1" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="I46" s="1" t="inlineStr"/>
+      <c r="J46" s="1" t="inlineStr"/>
+    </row>
+    <row r="47" ht="144" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>26433068664</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are related in the same way as are the numbers of
+the following sets.
+(NOTE: Operations should be performed on the whole numbers, without breaking
+down the numbers into its constituent digits. E.g. 13 – Operations on 13 such as
+adding /subtracting /multiplying etc. to 13 can be performed. Breaking down 13 into 1
+and 3 and then performing mathematical operations on 1 and 3 is not allowed)
+(75, 55, 70)
+(65, 55, 68)</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>(95,	85,	124)</t>
+        </is>
+      </c>
+      <c r="G47" s="1" t="inlineStr">
+        <is>
+          <t>(95,	85,	104)</t>
+        </is>
+      </c>
+      <c r="H47" s="1" t="inlineStr">
+        <is>
+          <t>(95,	80,	104)</t>
+        </is>
+      </c>
+      <c r="I47" s="1" t="inlineStr">
+        <is>
+          <t>(90,	85,	104)</t>
+        </is>
+      </c>
+      <c r="J47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>26433067788</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>In a certain code language, 'FUTURE' is coded as ‘91’ and ‘MONEY’ is coded as ‘72’.
+How will 'SECURE' be coded in that language?</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="H48" s="1" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I48" s="1" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J48" s="1" t="inlineStr"/>
+    </row>
+    <row r="49" ht="162" customHeight="1">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>26433087328</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>Study the given pattern carefully and select the number that can replace the question
+mark (?) in it.
+First row - 4, 6, 13
+Second row - 9, 8, 21
+Third row - 5, 6, ?
+(NOTE : Operations should be performed on the whole numbers, without breaking
+down the numbers into its constituent digits. Eg. 13 – Operations on 13 such as
+adding /deleting /multiplying etc. to 13 can be performed. Breaking down 13 into 1 and
+3 and then performing mathematical operations on 1 and 3 is not allowed)</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G49" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H49" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I49" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>26433057905</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>In a code language, 'AMIT' is coded as 86 and 'VIJAY' is coded as</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>How will
+'GARIMA' be coded in the same language?</t>
+        </is>
+      </c>
+      <c r="G50" s="1" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="H50" s="1" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I50" s="1" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="J50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>26433067694</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>Which two symbols from amongst the given options should be interchanged to make
+the given equation correct?
+272 ÷ 17 − 196 ÷ ( 5 × 3 + 1) = 30</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>× and −</t>
+        </is>
+      </c>
+      <c r="G51" s="1" t="inlineStr">
+        <is>
+          <t>× and +</t>
+        </is>
+      </c>
+      <c r="H51" s="1" t="inlineStr">
+        <is>
+          <t>+ and ÷</t>
+        </is>
+      </c>
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>+ and −</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52" ht="216" customHeight="1">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>26433091627</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>Three statements are given, followed by three conclusions numbered I, II and III.
+Assuming the statements to be true, even if they seem to be at variance with
+commonly known facts, decide which of the conclusions logically follow(s) from the
+statements.
+Statements:
+No toy is beautiful.
+Some beautiful are actresses.
+All actresses are rich.
+Conclusions:
+I. No toy is rich.
+II. Some actresses are beautiful.
+III. Some actresses are rich.</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusions II and III follow</t>
+        </is>
+      </c>
+      <c r="G52" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusions I and III follow</t>
+        </is>
+      </c>
+      <c r="H52" s="1" t="inlineStr">
+        <is>
+          <t>All the conclusions follow</t>
+        </is>
+      </c>
+      <c r="I52" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusions I and II follow</t>
+        </is>
+      </c>
+      <c r="J52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53" ht="54" customHeight="1">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>26433067683</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>Which two symbols from amongst the given options should be interchanged to make
+the given equation correct?
+(35 – 2) × 3 = (56 × 8 ÷ 3 + 100) × 11</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>÷ and +</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>× and ÷</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>+ and −</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>× and −</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>26433079386</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>Select the correct option that indicates the arrangement of the following words in a
+logical and meaningful order.</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
+      <c r="G54" s="1" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="H54" s="1" t="inlineStr">
+        <is>
+          <t>West Europe</t>
+        </is>
+      </c>
+      <c r="I54" s="1" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="J54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55" ht="54" customHeight="1">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>26433069675</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>Select the correct combination of mathematical signs to replace the * signs and to
+balance the given equation.
+831 * 3 * 13 * 45 * 245 * 1</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>÷, +, −, =, ×</t>
+        </is>
+      </c>
+      <c r="G55" s="1">
+        <f>, ×, ÷, +, −</f>
+        <v/>
+      </c>
+      <c r="H55" s="1">
+        <f>, −, ÷, +, −</f>
+        <v/>
+      </c>
+      <c r="I55" s="1">
+        <f>, ÷, +, −, ×</f>
+        <v/>
+      </c>
+      <c r="J55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56" ht="25" customHeight="1">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>26433093108</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>What will be the day of the week on 19th November 2053?</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="G56" s="1" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="H56" s="1" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="I56" s="1" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="J56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57" ht="90" customHeight="1">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>26433086988</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>‘P + Q’ means ‘P is the daughter of Q’.
+‘P % Q’ means ‘P is the son of Q’.
+‘P # Q’ means ‘P is the wife of Q’.
+If A + B # C % D # E, which of the following statements is NOT correct?
+Section : General Awareness</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>C is the father of A.</t>
+        </is>
+      </c>
+      <c r="G57" s="1" t="inlineStr">
+        <is>
+          <t>B is sister of E’s son.</t>
+        </is>
+      </c>
+      <c r="H57" s="1" t="inlineStr">
+        <is>
+          <t>D is the mother of B’s husband.</t>
+        </is>
+      </c>
+      <c r="I57" s="1" t="inlineStr">
+        <is>
+          <t>A is the daughter of E’s son.</t>
+        </is>
+      </c>
+      <c r="J57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58" ht="25" customHeight="1">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>26433085248</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>Who among the following Vijayanagara kings defeated the sultan of Bijapur in 1520?</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>Deva Raya II</t>
+        </is>
+      </c>
+      <c r="G58" s="1" t="inlineStr">
+        <is>
+          <t>Krishnadeva Raya</t>
+        </is>
+      </c>
+      <c r="H58" s="1" t="inlineStr">
+        <is>
+          <t>Vira Narasimha Raya</t>
+        </is>
+      </c>
+      <c r="I58" s="1" t="inlineStr">
+        <is>
+          <t>Bukka Raya I</t>
+        </is>
+      </c>
+      <c r="J58" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -870,7 +870,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="54" customHeight="1">
+    <row r="9" ht="25" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
@@ -883,69 +883,121 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>441009247506</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>DER121  , YZM129  , TUH137   , OPC145   , ?</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>JKX153</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t>JKX152</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t>JLX153</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t>JZX153</t>
+        </is>
+      </c>
+      <c r="J9" s="1" t="inlineStr">
+        <is>
+          <t>JKX153</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="54" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D9" s="1" t="inlineStr">
+      <c r="D10" s="1" t="inlineStr">
         <is>
           <t>441009247533</t>
         </is>
       </c>
-      <c r="E9" s="1" t="inlineStr">
+      <c r="E10" s="1" t="inlineStr">
         <is>
           <t>Refer to the following letter, symbol series and answer the question. Counting to be done from left to right only.
 (Left) S @ R N Q Q V + L O Z V Q Y # U D U Z (Right)
 How many such letters are there each of which is immediately preceded by a symbol and also immediately followed by a letter?</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr">
+      <c r="F10" s="1" t="inlineStr">
         <is>
           <t>One</t>
         </is>
       </c>
-      <c r="G9" s="1" t="inlineStr">
+      <c r="G10" s="1" t="inlineStr">
         <is>
           <t>Two</t>
         </is>
       </c>
-      <c r="H9" s="1" t="inlineStr">
+      <c r="H10" s="1" t="inlineStr">
         <is>
           <t>Three</t>
         </is>
       </c>
-      <c r="I9" s="1" t="inlineStr">
+      <c r="I10" s="1" t="inlineStr">
         <is>
           <t>Four</t>
         </is>
       </c>
-      <c r="J9" s="1" t="inlineStr">
+      <c r="J10" s="1" t="inlineStr">
         <is>
           <t>Three</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="72" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="11" ht="72" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="1" t="inlineStr">
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>441009247513</t>
         </is>
       </c>
-      <c r="E10" s="1" t="inlineStr">
+      <c r="E11" s="1" t="inlineStr">
         <is>
           <t>Refer to the following letter, number, symbol series and answer the question. Counting to be done from left to right. All numbers are
 single-digit numbers.
@@ -953,54 +1005,54 @@
 How many such symbols are there each of which is immediately preceded by a letter and also immediately followed by a number?</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr">
+      <c r="F11" s="1" t="inlineStr">
         <is>
           <t>One</t>
         </is>
       </c>
-      <c r="G10" s="1" t="inlineStr">
+      <c r="G11" s="1" t="inlineStr">
         <is>
           <t>Two</t>
         </is>
       </c>
-      <c r="H10" s="1" t="inlineStr">
+      <c r="H11" s="1" t="inlineStr">
         <is>
           <t>Three</t>
         </is>
       </c>
-      <c r="I10" s="1" t="inlineStr">
+      <c r="I11" s="1" t="inlineStr">
         <is>
           <t>Four</t>
         </is>
       </c>
-      <c r="J10" s="1" t="inlineStr">
+      <c r="J11" s="1" t="inlineStr">
         <is>
           <t>One</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="108" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="12" ht="108" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B12" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C11" s="1" t="inlineStr">
+      <c r="C12" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D12" s="1" t="inlineStr">
         <is>
           <t>441009328415</t>
         </is>
       </c>
-      <c r="E11" s="1" t="inlineStr">
+      <c r="E12" s="1" t="inlineStr">
         <is>
           <t>In a certain code,
 'laptop and tablet' is coded as 'fp ln cb'
@@ -1010,107 +1062,153 @@
 What is the code for 'and'?</t>
         </is>
       </c>
-      <c r="F11" s="1" t="inlineStr">
+      <c r="F12" s="1" t="inlineStr">
         <is>
           <t>fb</t>
         </is>
       </c>
-      <c r="G11" s="1" t="inlineStr">
+      <c r="G12" s="1" t="inlineStr">
         <is>
           <t>cb</t>
         </is>
       </c>
-      <c r="H11" s="1" t="inlineStr">
+      <c r="H12" s="1" t="inlineStr">
         <is>
           <t>in</t>
         </is>
       </c>
-      <c r="I11" s="1" t="inlineStr">
+      <c r="I12" s="1" t="inlineStr">
         <is>
           <t>tc</t>
         </is>
       </c>
-      <c r="J11" s="1" t="inlineStr">
+      <c r="J12" s="1" t="inlineStr">
         <is>
           <t>cb</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="13" ht="54" customHeight="1">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>441009328415</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>'laptop and tablet' ను 'fp ln cb' అని కోడ్ చేస్తారు
+'laptop movies is' ను 'fp tc dy' అని కోడ్ చేస్తారు
+'vacation tablet movies' ను 'gb ln tc' అని కోడ్ చేస్తారు</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t>cb</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr"/>
+      <c r="I13" s="1" t="inlineStr"/>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C12" s="1" t="inlineStr">
+      <c r="C14" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D12" s="1" t="inlineStr">
+      <c r="D14" s="1" t="inlineStr">
         <is>
           <t>441009247541</t>
         </is>
       </c>
-      <c r="E12" s="1" t="inlineStr">
+      <c r="E14" s="1" t="inlineStr">
         <is>
           <t>In a certain code language, ‘GOWN’ is coded as ‘4593’ and ‘SOWN’ is coded as ‘9135’.What is the code for ‘S’ in the given code
 language?</t>
         </is>
       </c>
-      <c r="F12" s="1" t="inlineStr">
+      <c r="F14" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G12" s="1" t="inlineStr">
+      <c r="G14" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="H12" s="1" t="inlineStr">
+      <c r="H14" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I12" s="1" t="inlineStr">
+      <c r="I14" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J12" s="1" t="inlineStr">
+      <c r="J14" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="72" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="15" ht="72" customHeight="1">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
+      <c r="B15" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C13" s="1" t="inlineStr">
+      <c r="C15" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="1" t="inlineStr">
+      <c r="D15" s="1" t="inlineStr">
         <is>
           <t>441009328438</t>
         </is>
       </c>
-      <c r="E13" s="1" t="inlineStr">
+      <c r="E15" s="1" t="inlineStr">
         <is>
           <t>In the following triad, each group of letters is related to the subsequent one following a certain logic. Select from the given options, the one
 which follows the same logic.
@@ -1118,214 +1216,319 @@
 KIND - NKID - DNIK</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>HOTS - THOS - STOH</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="G15" s="1" t="inlineStr">
         <is>
           <t>CARD - CRAD - DRAC</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="H15" s="1" t="inlineStr">
         <is>
           <t>MIND - IMND - DINM</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="I15" s="1" t="inlineStr">
         <is>
           <t>SHOP - OSHP - HOPS</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="J15" s="1" t="inlineStr">
         <is>
           <t>HOTS - THOS - STOH</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="54" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B16" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C14" s="1" t="inlineStr">
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>441009328438</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>SINK - NSIK - KNIS
+KIND - NKID - DNIK</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>HOTS - THOS - STOH</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t>CARD - CRAD - DRAC</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t>MIND - IMND - DINM</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t>SHOP - OSHP - HOPS</t>
+        </is>
+      </c>
+      <c r="J16" s="1" t="inlineStr">
+        <is>
+          <t>HOTS - THOS - STOH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="54" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D17" s="1" t="inlineStr">
         <is>
           <t>441009328444</t>
         </is>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E17" s="1" t="inlineStr">
         <is>
           <t>Based on the alphabetical order, three of the following four are alike in a certain way and thus form a group. Which is the one that does not
 belong to that group?
 (Note: The odd one out is not based on the number of consonants/vowels or their position in the letter cluster)</t>
         </is>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F17" s="1" t="inlineStr">
         <is>
           <t>MRO</t>
         </is>
       </c>
-      <c r="G14" s="1" t="inlineStr">
+      <c r="G17" s="1" t="inlineStr">
         <is>
           <t>INS</t>
         </is>
       </c>
-      <c r="H14" s="1" t="inlineStr">
+      <c r="H17" s="1" t="inlineStr">
         <is>
           <t>NSX</t>
         </is>
       </c>
-      <c r="I14" s="1" t="inlineStr">
+      <c r="I17" s="1" t="inlineStr">
         <is>
           <t>DIN</t>
         </is>
       </c>
-      <c r="J14" s="1" t="inlineStr">
+      <c r="J17" s="1" t="inlineStr">
         <is>
           <t>MRO</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B18" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C15" s="1" t="inlineStr">
+      <c r="C18" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D15" s="1" t="inlineStr">
+      <c r="D18" s="1" t="inlineStr">
         <is>
           <t>441009328455</t>
         </is>
       </c>
-      <c r="E15" s="1" t="inlineStr">
+      <c r="E18" s="1" t="inlineStr">
         <is>
           <t>The following contain two pairs of words which are related to each other in a certain way. Three of the following four word pairs are alike
 as these have the same relationship and thus form a group. Which word pair is the one that does not belong to that group?</t>
         </is>
       </c>
-      <c r="F15" s="1" t="inlineStr">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Below-Above</t>
         </is>
       </c>
-      <c r="G15" s="1" t="inlineStr">
+      <c r="G18" s="1" t="inlineStr">
         <is>
           <t>Select-Choose</t>
         </is>
       </c>
-      <c r="H15" s="1" t="inlineStr">
+      <c r="H18" s="1" t="inlineStr">
         <is>
           <t>Trip-Journey</t>
         </is>
       </c>
-      <c r="I15" s="1" t="inlineStr">
+      <c r="I18" s="1" t="inlineStr">
         <is>
           <t>Good-Fine</t>
         </is>
       </c>
-      <c r="J15" s="1" t="inlineStr">
+      <c r="J18" s="1" t="inlineStr">
         <is>
           <t>Below-Above</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>AP  Technical education service exam 2026</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B19" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C19" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="1" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>441009247566</t>
         </is>
       </c>
-      <c r="E16" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>What should come in place of ‘?’ in the given series?
 20   58   98   214   410    ?</t>
         </is>
       </c>
-      <c r="F16" s="1" t="inlineStr">
+      <c r="F19" s="1" t="inlineStr">
         <is>
           <t>836</t>
         </is>
       </c>
-      <c r="G16" s="1" t="inlineStr">
+      <c r="G19" s="1" t="inlineStr">
         <is>
           <t>837</t>
         </is>
       </c>
-      <c r="H16" s="1" t="inlineStr">
+      <c r="H19" s="1" t="inlineStr">
         <is>
           <t>838</t>
         </is>
       </c>
-      <c r="I16" s="1" t="inlineStr">
+      <c r="I19" s="1" t="inlineStr">
         <is>
           <t>839</t>
         </is>
       </c>
-      <c r="J16" s="1" t="inlineStr">
+      <c r="J19" s="1" t="inlineStr">
         <is>
           <t>838</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="90" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="20" ht="25" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>441009247566</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>20   58   98   214   410    ?</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>836</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t>839</t>
+        </is>
+      </c>
+      <c r="J20" s="1" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="1" t="inlineStr">
+      <c r="C21" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="1" t="inlineStr">
+      <c r="D21" s="1" t="inlineStr">
         <is>
           <t>26433067858</t>
         </is>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E21" s="1" t="inlineStr">
         <is>
           <t>Select the option that is related to the third word in the same way as the second word
 is related to the first word. (The words must be considered as meaningful English
@@ -1334,50 +1537,103 @@
 Animal : Zoology :: Plant : ?</t>
         </is>
       </c>
-      <c r="F17" s="1" t="inlineStr">
+      <c r="F21" s="1" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="G17" s="1" t="inlineStr">
+      <c r="G21" s="1" t="inlineStr">
         <is>
           <t>Palaeontology</t>
         </is>
       </c>
-      <c r="H17" s="1" t="inlineStr">
+      <c r="H21" s="1" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="I17" s="1" t="inlineStr">
+      <c r="I21" s="1" t="inlineStr">
         <is>
           <t>Botany</t>
         </is>
       </c>
-      <c r="J17" s="1" t="inlineStr"/>
-    </row>
-    <row r="18" ht="126" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="J21" s="1" t="inlineStr"/>
+    </row>
+    <row r="22" ht="108" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B22" s="1" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C18" s="1" t="inlineStr">
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>26433074619</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>A, B, C, D, E, F, G and H are sitting around a square table not facing the centre. Some
+of them are sitting at the corners while some are sitting at the exact centre of the
+sides. A is sitting to the immediate right of F and immediate left of E. C is sitting to the
+immediate right of E. G is sitting two places from the right of E. B is sitting to the
+immediate right of G. H is sitting to the immediate right of B and immediate left of D. D
+is sitting to the left of F. Who is sitting between A and D?</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+    </row>
+    <row r="23" ht="126" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="1" t="inlineStr">
+      <c r="D23" s="1" t="inlineStr">
         <is>
           <t>26433069255</t>
         </is>
       </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Which option represents the correct order of the given words as they would appear in
 the English dictionary?
@@ -1388,50 +1644,50 @@
 5 Sadly</t>
         </is>
       </c>
-      <c r="F18" s="1" t="inlineStr">
+      <c r="F23" s="1" t="inlineStr">
         <is>
           <t>3, 5, 1, 2, 4</t>
         </is>
       </c>
-      <c r="G18" s="1" t="inlineStr">
+      <c r="G23" s="1" t="inlineStr">
         <is>
           <t>5, 1, 3, 2, 4</t>
         </is>
       </c>
-      <c r="H18" s="1" t="inlineStr">
+      <c r="H23" s="1" t="inlineStr">
         <is>
           <t>5, 1, 3, 4, 2</t>
         </is>
       </c>
-      <c r="I18" s="1" t="inlineStr">
+      <c r="I23" s="1" t="inlineStr">
         <is>
           <t>5, 3, 1, 2, 4</t>
         </is>
       </c>
-      <c r="J18" s="1" t="inlineStr"/>
-    </row>
-    <row r="19" ht="162" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="J23" s="1" t="inlineStr"/>
+    </row>
+    <row r="24" ht="162" customHeight="1">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B24" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C19" s="1" t="inlineStr">
+      <c r="C24" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D19" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>26433093138</t>
         </is>
       </c>
-      <c r="E19" s="1" t="inlineStr">
+      <c r="E24" s="1" t="inlineStr">
         <is>
           <t>Two Statements are given followed by Two conclusions numbered I and II. Assuming
 the statements to be true, even if they seem to be at variance with commonly known
@@ -1444,148 +1700,148 @@
 II. No jeep is a bus.</t>
         </is>
       </c>
-      <c r="F19" s="1" t="inlineStr">
+      <c r="F24" s="1" t="inlineStr">
         <is>
           <t>Only conclusion II follows.</t>
         </is>
       </c>
-      <c r="G19" s="1" t="inlineStr">
+      <c r="G24" s="1" t="inlineStr">
         <is>
           <t>Neither conclusion I nor II follows.</t>
         </is>
       </c>
-      <c r="H19" s="1" t="inlineStr">
+      <c r="H24" s="1" t="inlineStr">
         <is>
           <t>Both conclusions I and II follows.</t>
         </is>
       </c>
-      <c r="I19" s="1" t="inlineStr">
+      <c r="I24" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I follows.</t>
         </is>
       </c>
-      <c r="J19" s="1" t="inlineStr"/>
-    </row>
-    <row r="20" ht="36" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="J24" s="1" t="inlineStr"/>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C20" s="1" t="inlineStr">
+      <c r="C25" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
+      <c r="D25" s="1" t="inlineStr">
         <is>
           <t>26433057903</t>
         </is>
       </c>
-      <c r="E20" s="1" t="inlineStr">
+      <c r="E25" s="1" t="inlineStr">
         <is>
           <t>In a code language, 'PARUL' is coded as RDTXN and 'MADHU' is coded as ODFKW.
 How will 'VIJAY' be coded in the same language?</t>
         </is>
       </c>
-      <c r="F20" s="1" t="inlineStr">
+      <c r="F25" s="1" t="inlineStr">
         <is>
           <t>XKLCB</t>
         </is>
       </c>
-      <c r="G20" s="1" t="inlineStr">
+      <c r="G25" s="1" t="inlineStr">
         <is>
           <t>XLLDA</t>
         </is>
       </c>
-      <c r="H20" s="1" t="inlineStr">
+      <c r="H25" s="1" t="inlineStr">
         <is>
           <t>XLMDA</t>
         </is>
       </c>
-      <c r="I20" s="1" t="inlineStr">
+      <c r="I25" s="1" t="inlineStr">
         <is>
           <t>XMLCA</t>
         </is>
       </c>
-      <c r="J20" s="1" t="inlineStr"/>
-    </row>
-    <row r="21" ht="36" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="J25" s="1" t="inlineStr"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B26" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C21" s="1" t="inlineStr">
+      <c r="C26" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D21" s="1" t="inlineStr">
+      <c r="D26" s="1" t="inlineStr">
         <is>
           <t>26433085678</t>
         </is>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>Pointing at a girl, Seema said, “She is my father’s mother’s husband’s only son’s
 daughter.” How is that girl related to Seema?</t>
         </is>
       </c>
-      <c r="F21" s="1" t="inlineStr">
+      <c r="F26" s="1" t="inlineStr">
         <is>
           <t>Mother’s sister</t>
         </is>
       </c>
-      <c r="G21" s="1" t="inlineStr">
+      <c r="G26" s="1" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="H21" s="1" t="inlineStr">
+      <c r="H26" s="1" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
-      <c r="I21" s="1" t="inlineStr">
+      <c r="I26" s="1" t="inlineStr">
         <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="J21" s="1" t="inlineStr"/>
-    </row>
-    <row r="22" ht="90" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="J26" s="1" t="inlineStr"/>
+    </row>
+    <row r="27" ht="90" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B27" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C22" s="1" t="inlineStr">
+      <c r="C27" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D22" s="1" t="inlineStr">
+      <c r="D27" s="1" t="inlineStr">
         <is>
           <t>26433057314</t>
         </is>
       </c>
-      <c r="E22" s="1" t="inlineStr">
+      <c r="E27" s="1" t="inlineStr">
         <is>
           <t>In this question, the statement is followed by two conclusions. Which of the two
 conclusions is/are true?
@@ -1594,347 +1850,347 @@
 II. C &lt; F</t>
         </is>
       </c>
-      <c r="F22" s="1" t="inlineStr">
+      <c r="F27" s="1" t="inlineStr">
         <is>
           <t>Neither conclusion I nor II is true</t>
         </is>
       </c>
-      <c r="G22" s="1" t="inlineStr">
+      <c r="G27" s="1" t="inlineStr">
         <is>
           <t>Both conclusions I and II are true</t>
         </is>
       </c>
-      <c r="H22" s="1" t="inlineStr">
+      <c r="H27" s="1" t="inlineStr">
         <is>
           <t>Only conclusion II is true</t>
         </is>
       </c>
-      <c r="I22" s="1" t="inlineStr">
+      <c r="I27" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I is true</t>
         </is>
       </c>
-      <c r="J22" s="1" t="inlineStr"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="J27" s="1" t="inlineStr"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B28" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C23" s="1" t="inlineStr">
+      <c r="C28" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D28" s="1" t="inlineStr">
         <is>
           <t>26433069199</t>
         </is>
       </c>
-      <c r="E23" s="1" t="inlineStr">
+      <c r="E28" s="1" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 3, 7, 5, 61, 363 ?</t>
         </is>
       </c>
-      <c r="F23" s="1" t="inlineStr">
+      <c r="F28" s="1" t="inlineStr">
         <is>
           <t>3367</t>
         </is>
       </c>
-      <c r="G23" s="1" t="inlineStr">
+      <c r="G28" s="1" t="inlineStr">
         <is>
           <t>3348</t>
         </is>
       </c>
-      <c r="H23" s="1" t="inlineStr">
+      <c r="H28" s="1" t="inlineStr">
         <is>
           <t>3630</t>
         </is>
       </c>
-      <c r="I23" s="1" t="inlineStr">
+      <c r="I28" s="1" t="inlineStr">
         <is>
           <t>3267</t>
         </is>
       </c>
-      <c r="J23" s="1" t="inlineStr"/>
-    </row>
-    <row r="24" ht="54" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="J28" s="1" t="inlineStr"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B29" s="1" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C24" s="1" t="inlineStr">
+      <c r="C29" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D24" s="1" t="inlineStr">
+      <c r="D29" s="1" t="inlineStr">
         <is>
           <t>26433068990</t>
         </is>
       </c>
-      <c r="E24" s="1" t="inlineStr">
+      <c r="E29" s="1" t="inlineStr">
         <is>
           <t>Select the option that represents the letters that, when sequentially placed from left to
 right in the blanks below, will complete the letter series.
 _ M _ B A J M Q _ A _ M Q B _ J _ _ B _</t>
         </is>
       </c>
-      <c r="F24" s="1" t="inlineStr">
+      <c r="F29" s="1" t="inlineStr">
         <is>
           <t>J Q B J A M Q A</t>
         </is>
       </c>
-      <c r="G24" s="1" t="inlineStr">
+      <c r="G29" s="1" t="inlineStr">
         <is>
           <t>B Q A J M Q A B</t>
         </is>
       </c>
-      <c r="H24" s="1" t="inlineStr">
+      <c r="H29" s="1" t="inlineStr">
         <is>
           <t>A M B Q J M J Q</t>
         </is>
       </c>
-      <c r="I24" s="1" t="inlineStr">
+      <c r="I29" s="1" t="inlineStr">
         <is>
           <t>J A M M Q A B J</t>
         </is>
       </c>
-      <c r="J24" s="1" t="inlineStr"/>
-    </row>
-    <row r="25" ht="54" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="J29" s="1" t="inlineStr"/>
+    </row>
+    <row r="30" ht="54" customHeight="1">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B30" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C25" s="1" t="inlineStr">
+      <c r="C30" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D30" s="1" t="inlineStr">
         <is>
           <t>26433079500</t>
         </is>
       </c>
-      <c r="E25" s="1" t="inlineStr">
+      <c r="E30" s="1" t="inlineStr">
         <is>
           <t>Town C is to the south of Town A. Town D is to the west of town A. Town B is to the
 east of town D. Town E is to the south of town B and south-east of Town C. What is the
 position of town A with respect to town B?</t>
         </is>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F30" s="1" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="G25" s="1" t="inlineStr">
+      <c r="G30" s="1" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="H25" s="1" t="inlineStr">
+      <c r="H30" s="1" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="I25" s="1" t="inlineStr">
+      <c r="I30" s="1" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="J25" s="1" t="inlineStr"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="J30" s="1" t="inlineStr"/>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B31" s="1" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="C31" s="1" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D31" s="1" t="inlineStr">
         <is>
           <t>26433067321</t>
         </is>
       </c>
-      <c r="E26" s="1" t="inlineStr">
+      <c r="E31" s="1" t="inlineStr">
         <is>
           <t>In a certain code language, 'DAM’ is coded as '50' and 'PAD' is coded as '47'. How will
 'MAP' be coded in that language?</t>
         </is>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F31" s="1" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G26" s="1" t="inlineStr">
+      <c r="G31" s="1" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="H26" s="1" t="inlineStr">
+      <c r="H31" s="1" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="I26" s="1" t="inlineStr">
+      <c r="I31" s="1" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="J26" s="1" t="inlineStr"/>
-    </row>
-    <row r="27" ht="54" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="J31" s="1" t="inlineStr"/>
+    </row>
+    <row r="32" ht="54" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B32" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C27" s="1" t="inlineStr">
+      <c r="C32" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D32" s="1" t="inlineStr">
         <is>
           <t>26433056550</t>
         </is>
       </c>
-      <c r="E27" s="1" t="inlineStr">
+      <c r="E32" s="1" t="inlineStr">
         <is>
           <t>Select the letter-cluster that will replace the question mark (?) in the given series and
 make it logically complete.
 FRP, HTR, JVT, ?, NZX</t>
         </is>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F32" s="1" t="inlineStr">
         <is>
           <t>IWV</t>
         </is>
       </c>
-      <c r="G27" s="1" t="inlineStr">
+      <c r="G32" s="1" t="inlineStr">
         <is>
           <t>KWU</t>
         </is>
       </c>
-      <c r="H27" s="1" t="inlineStr">
+      <c r="H32" s="1" t="inlineStr">
         <is>
           <t>IUS</t>
         </is>
       </c>
-      <c r="I27" s="1" t="inlineStr">
+      <c r="I32" s="1" t="inlineStr">
         <is>
           <t>LXV</t>
         </is>
       </c>
-      <c r="J27" s="1" t="inlineStr"/>
-    </row>
-    <row r="28" ht="36" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="J32" s="1" t="inlineStr"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B33" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C28" s="1" t="inlineStr">
+      <c r="C33" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D33" s="1" t="inlineStr">
         <is>
           <t>26433079440</t>
         </is>
       </c>
-      <c r="E28" s="1" t="inlineStr">
+      <c r="E33" s="1" t="inlineStr">
         <is>
           <t>Which letter cluster will replace the question mark (?) to complete the given series?
 GROW, NJGG, ?, BTQA, ILIK</t>
         </is>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F33" s="1" t="inlineStr">
         <is>
           <t>YDER</t>
         </is>
       </c>
-      <c r="G28" s="1" t="inlineStr">
+      <c r="G33" s="1" t="inlineStr">
         <is>
           <t>VIWQ</t>
         </is>
       </c>
-      <c r="H28" s="1" t="inlineStr">
+      <c r="H33" s="1" t="inlineStr">
         <is>
           <t>PSJW</t>
         </is>
       </c>
-      <c r="I28" s="1" t="inlineStr">
+      <c r="I33" s="1" t="inlineStr">
         <is>
           <t>UBYQ</t>
         </is>
       </c>
-      <c r="J28" s="1" t="inlineStr"/>
-    </row>
-    <row r="29" ht="126" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="J33" s="1" t="inlineStr"/>
+    </row>
+    <row r="34" ht="126" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="B34" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C29" s="1" t="inlineStr">
+      <c r="C34" s="1" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D34" s="1" t="inlineStr">
         <is>
           <t>26433069104</t>
         </is>
       </c>
-      <c r="E29" s="1" t="inlineStr">
+      <c r="E34" s="1" t="inlineStr">
         <is>
           <t>Select the set in which the number are related in the same way as the numbers of the
 given sets. (NOTE : Operations should be performed on the whole numbers, without
@@ -1945,50 +2201,50 @@
 (238, 212, 15)</t>
         </is>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F34" s="1" t="inlineStr">
         <is>
           <t>(370, 348, 19)</t>
         </is>
       </c>
-      <c r="G29" s="1" t="inlineStr">
+      <c r="G34" s="1" t="inlineStr">
         <is>
           <t>(336, 302, 17)</t>
         </is>
       </c>
-      <c r="H29" s="1" t="inlineStr">
+      <c r="H34" s="1" t="inlineStr">
         <is>
           <t>(142, 126, 11)</t>
         </is>
       </c>
-      <c r="I29" s="1" t="inlineStr">
+      <c r="I34" s="1" t="inlineStr">
         <is>
           <t>(337, 311, 18)</t>
         </is>
       </c>
-      <c r="J29" s="1" t="inlineStr"/>
-    </row>
-    <row r="30" ht="216" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="J34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35" ht="216" customHeight="1">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B35" s="1" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="C30" s="1" t="inlineStr">
+      <c r="C35" s="1" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D35" s="1" t="inlineStr">
         <is>
           <t>26433058075</t>
         </is>
       </c>
-      <c r="E30" s="1" t="inlineStr">
+      <c r="E35" s="1" t="inlineStr">
         <is>
           <t>Read the given statements and conclusions carefully. Assuming that the information
 given in the statements is true, even if it appears to be at variance with commonly
@@ -2004,148 +2260,148 @@
 III. No trojan is a virus.</t>
         </is>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F35" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I follows</t>
         </is>
       </c>
-      <c r="G30" s="1" t="inlineStr">
+      <c r="G35" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I and III follow</t>
         </is>
       </c>
-      <c r="H30" s="1" t="inlineStr">
+      <c r="H35" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I and II follow</t>
         </is>
       </c>
-      <c r="I30" s="1" t="inlineStr">
+      <c r="I35" s="1" t="inlineStr">
         <is>
           <t>Only conclusion II follows</t>
         </is>
       </c>
-      <c r="J30" s="1" t="inlineStr"/>
-    </row>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="J35" s="1" t="inlineStr"/>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B36" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C31" s="1" t="inlineStr">
+      <c r="C36" s="1" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D31" s="1" t="inlineStr">
+      <c r="D36" s="1" t="inlineStr">
         <is>
           <t>26433067622</t>
         </is>
       </c>
-      <c r="E31" s="1" t="inlineStr">
+      <c r="E36" s="1" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 420, 462, 506, ?, 600, 650, 702</t>
         </is>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F36" s="1" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="G31" s="1" t="inlineStr">
+      <c r="G36" s="1" t="inlineStr">
         <is>
           <t>552</t>
         </is>
       </c>
-      <c r="H31" s="1" t="inlineStr">
+      <c r="H36" s="1" t="inlineStr">
         <is>
           <t>562</t>
         </is>
       </c>
-      <c r="I31" s="1" t="inlineStr">
+      <c r="I36" s="1" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="J31" s="1" t="inlineStr"/>
-    </row>
-    <row r="32" ht="36" customHeight="1">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="J36" s="1" t="inlineStr"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B37" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C32" s="1" t="inlineStr">
+      <c r="C37" s="1" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D37" s="1" t="inlineStr">
         <is>
           <t>26433057236</t>
         </is>
       </c>
-      <c r="E32" s="1" t="inlineStr">
+      <c r="E37" s="1" t="inlineStr">
         <is>
           <t>Three of the following four letter-clusters are alike in a certain way and one is different.
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F37" s="1" t="inlineStr">
         <is>
           <t>TWGD</t>
         </is>
       </c>
-      <c r="G32" s="1" t="inlineStr">
+      <c r="G37" s="1" t="inlineStr">
         <is>
           <t>ADZE</t>
         </is>
       </c>
-      <c r="H32" s="1" t="inlineStr">
+      <c r="H37" s="1" t="inlineStr">
         <is>
           <t>PSKH</t>
         </is>
       </c>
-      <c r="I32" s="1" t="inlineStr">
+      <c r="I37" s="1" t="inlineStr">
         <is>
           <t>FIUR</t>
         </is>
       </c>
-      <c r="J32" s="1" t="inlineStr"/>
-    </row>
-    <row r="33" ht="144" customHeight="1">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="J37" s="1" t="inlineStr"/>
+    </row>
+    <row r="38" ht="144" customHeight="1">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B38" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C33" s="1" t="inlineStr">
+      <c r="C38" s="1" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D33" s="1" t="inlineStr">
+      <c r="D38" s="1" t="inlineStr">
         <is>
           <t>26433067918</t>
         </is>
       </c>
-      <c r="E33" s="1" t="inlineStr">
+      <c r="E38" s="1" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as are the numbers of
 the following set.
@@ -2157,149 +2413,149 @@
 (256, 123, 133)</t>
         </is>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F38" s="1" t="inlineStr">
         <is>
           <t>(182, 74, 108)</t>
         </is>
       </c>
-      <c r="G33" s="1" t="inlineStr">
+      <c r="G38" s="1" t="inlineStr">
         <is>
           <t>(240, 105, 110)</t>
         </is>
       </c>
-      <c r="H33" s="1" t="inlineStr">
+      <c r="H38" s="1" t="inlineStr">
         <is>
           <t>(196, 89, 91)</t>
         </is>
       </c>
-      <c r="I33" s="1" t="inlineStr">
+      <c r="I38" s="1" t="inlineStr">
         <is>
           <t>(292, 122, 160)</t>
         </is>
       </c>
-      <c r="J33" s="1" t="inlineStr"/>
-    </row>
-    <row r="34" ht="54" customHeight="1">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="J38" s="1" t="inlineStr"/>
+    </row>
+    <row r="39" ht="54" customHeight="1">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B39" s="1" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
+      <c r="C39" s="1" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D34" s="1" t="inlineStr">
+      <c r="D39" s="1" t="inlineStr">
         <is>
           <t>26433068692</t>
         </is>
       </c>
-      <c r="E34" s="1" t="inlineStr">
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>Select the correct combination of mathematical signs to sequentially replace the *
 signs and balance the given equation.
 65	*	56	*	8	*	19	*	2	*	34</t>
         </is>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F39" s="1" t="inlineStr">
         <is>
           <t>−, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="G34" s="1" t="inlineStr">
+      <c r="G39" s="1" t="inlineStr">
         <is>
           <t>+, +, −, ×, =</t>
         </is>
       </c>
-      <c r="H34" s="1" t="inlineStr">
+      <c r="H39" s="1" t="inlineStr">
         <is>
           <t>+, ×, −, ×, =</t>
         </is>
       </c>
-      <c r="I34" s="1" t="inlineStr">
+      <c r="I39" s="1" t="inlineStr">
         <is>
           <t>+, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="J34" s="1" t="inlineStr"/>
-    </row>
-    <row r="35" ht="36" customHeight="1">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="J39" s="1" t="inlineStr"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
+      <c r="B40" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
+      <c r="C40" s="1" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D35" s="1" t="inlineStr">
+      <c r="D40" s="1" t="inlineStr">
         <is>
           <t>26433057998</t>
         </is>
       </c>
-      <c r="E35" s="1" t="inlineStr">
+      <c r="E40" s="1" t="inlineStr">
         <is>
           <t>Three of the following four letter-clusters are alike in a certain way and one is different.
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F40" s="1" t="inlineStr">
         <is>
           <t>MPJ</t>
         </is>
       </c>
-      <c r="G35" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>DIB</t>
         </is>
       </c>
-      <c r="H35" s="1" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>HKE</t>
         </is>
       </c>
-      <c r="I35" s="1" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>TWQ</t>
         </is>
       </c>
-      <c r="J35" s="1" t="inlineStr"/>
-    </row>
-    <row r="36" ht="216" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr"/>
+    </row>
+    <row r="41" ht="216" customHeight="1">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
+      <c r="B41" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
+      <c r="C41" s="1" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D36" s="1" t="inlineStr">
+      <c r="D41" s="1" t="inlineStr">
         <is>
           <t>26433058051</t>
         </is>
       </c>
-      <c r="E36" s="1" t="inlineStr">
+      <c r="E41" s="1" t="inlineStr">
         <is>
           <t>Three statements are given followed by three conclusions numbered I, II and III.
 Assuming the statements to be true, even if they seem to be at variance with
@@ -2315,50 +2571,50 @@
 III. Some nails are pendants.</t>
         </is>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F41" s="1" t="inlineStr">
         <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="G36" s="1" t="inlineStr">
+      <c r="G41" s="1" t="inlineStr">
         <is>
           <t>Only conclusion III follows</t>
         </is>
       </c>
-      <c r="H36" s="1" t="inlineStr">
+      <c r="H41" s="1" t="inlineStr">
         <is>
           <t>Only conclusions I and II follow</t>
         </is>
       </c>
-      <c r="I36" s="1" t="inlineStr">
+      <c r="I41" s="1" t="inlineStr">
         <is>
           <t>Only conclusion I follows</t>
         </is>
       </c>
-      <c r="J36" s="1" t="inlineStr"/>
-    </row>
-    <row r="37" ht="126" customHeight="1">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="J41" s="1" t="inlineStr"/>
+    </row>
+    <row r="42" ht="126" customHeight="1">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
+      <c r="B42" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
+      <c r="C42" s="1" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D37" s="1" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>26433068349</t>
         </is>
       </c>
-      <c r="E37" s="1" t="inlineStr">
+      <c r="E42" s="1" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are NOT related in the same way as are the
 numbers of the given set.
@@ -2369,50 +2625,50 @@
 (16, 11, 377)</t>
         </is>
       </c>
-      <c r="F37" s="1" t="inlineStr">
+      <c r="F42" s="1" t="inlineStr">
         <is>
           <t>(12, 15, 367)</t>
         </is>
       </c>
-      <c r="G37" s="1" t="inlineStr">
+      <c r="G42" s="1" t="inlineStr">
         <is>
           <t>(16, 14, 452)</t>
         </is>
       </c>
-      <c r="H37" s="1" t="inlineStr">
+      <c r="H42" s="1" t="inlineStr">
         <is>
           <t>(14, 12, 340)</t>
         </is>
       </c>
-      <c r="I37" s="1" t="inlineStr">
+      <c r="I42" s="1" t="inlineStr">
         <is>
           <t>(18, 13, 493)</t>
         </is>
       </c>
-      <c r="J37" s="1" t="inlineStr"/>
-    </row>
-    <row r="38" ht="72" customHeight="1">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="J42" s="1" t="inlineStr"/>
+    </row>
+    <row r="43" ht="72" customHeight="1">
+      <c r="A43" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
+      <c r="B43" s="1" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
+      <c r="C43" s="1" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D38" s="1" t="inlineStr">
+      <c r="D43" s="1" t="inlineStr">
         <is>
           <t>26433076698</t>
         </is>
       </c>
-      <c r="E38" s="1" t="inlineStr">
+      <c r="E43" s="1" t="inlineStr">
         <is>
           <t>Town M is to the west of Town D. Town C is to the south-west of Town D. Town D is to
 the north of Town B. Town A is to the south of Town C. Town M is to the north of Town
@@ -2420,50 +2676,50 @@
 Town M?</t>
         </is>
       </c>
-      <c r="F38" s="1" t="inlineStr">
+      <c r="F43" s="1" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="G38" s="1" t="inlineStr">
+      <c r="G43" s="1" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="H38" s="1" t="inlineStr">
+      <c r="H43" s="1" t="inlineStr">
         <is>
           <t>South-east</t>
         </is>
       </c>
-      <c r="I38" s="1" t="inlineStr">
+      <c r="I43" s="1" t="inlineStr">
         <is>
           <t>North-west</t>
         </is>
       </c>
-      <c r="J38" s="1" t="inlineStr"/>
-    </row>
-    <row r="39" ht="126" customHeight="1">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="J43" s="1" t="inlineStr"/>
+    </row>
+    <row r="44" ht="126" customHeight="1">
+      <c r="A44" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B44" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
+      <c r="C44" s="1" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>26433069113</t>
         </is>
       </c>
-      <c r="E39" s="1" t="inlineStr">
+      <c r="E44" s="1" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as the numbers of the
 given sets. (NOTE : Operations should be performed on the whole numbers, without
@@ -2474,100 +2730,100 @@
 (14, 104, 300)</t>
         </is>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F44" s="1" t="inlineStr">
         <is>
           <t>(15, 175, 390)</t>
         </is>
       </c>
-      <c r="G39" s="1" t="inlineStr">
+      <c r="G44" s="1" t="inlineStr">
         <is>
           <t>(17, 131, 410)</t>
         </is>
       </c>
-      <c r="H39" s="1" t="inlineStr">
+      <c r="H44" s="1" t="inlineStr">
         <is>
           <t>(19, 121, 445)</t>
         </is>
       </c>
-      <c r="I39" s="1" t="inlineStr">
+      <c r="I44" s="1" t="inlineStr">
         <is>
           <t>(13, 162, 331)</t>
         </is>
       </c>
-      <c r="J39" s="1" t="inlineStr"/>
-    </row>
-    <row r="40" ht="54" customHeight="1">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="J44" s="1" t="inlineStr"/>
+    </row>
+    <row r="45" ht="54" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B45" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
+      <c r="C45" s="1" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>26433067684</t>
         </is>
       </c>
-      <c r="E40" s="1" t="inlineStr">
+      <c r="E45" s="1" t="inlineStr">
         <is>
           <t>Which two numbers from amongst the given options should be interchanged to make
 the given equation correct?
 (357 ÷ 2 + 3) ÷ 11 − 4 = (28 × 3 + 7) ÷ 9</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F45" s="1" t="inlineStr">
         <is>
           <t>11 and 28</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="G45" s="1" t="inlineStr">
         <is>
           <t>2 and 3</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="H45" s="1" t="inlineStr">
         <is>
           <t>7 and 9</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="I45" s="1" t="inlineStr">
         <is>
           <t>2 and 9</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr"/>
-    </row>
-    <row r="41" ht="72" customHeight="1">
-      <c r="A41" s="1" t="inlineStr">
+      <c r="J45" s="1" t="inlineStr"/>
+    </row>
+    <row r="46" ht="72" customHeight="1">
+      <c r="A46" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B46" s="1" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
+      <c r="C46" s="1" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D46" s="1" t="inlineStr">
         <is>
           <t>26433067890</t>
         </is>
       </c>
-      <c r="E41" s="1" t="inlineStr">
+      <c r="E46" s="1" t="inlineStr">
         <is>
           <t>Select the option that is related to the third number in the same way as the second
 number is related to the first number and the sixth number is related to the fifth
@@ -2575,100 +2831,100 @@
 6 : 43 :: 11 : ? :: 4 : 21</t>
         </is>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F46" s="1" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="G41" s="1" t="inlineStr">
+      <c r="G46" s="1" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="H41" s="1" t="inlineStr">
+      <c r="H46" s="1" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="I41" s="1" t="inlineStr">
+      <c r="I46" s="1" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="J41" s="1" t="inlineStr"/>
-    </row>
-    <row r="42" ht="54" customHeight="1">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="J46" s="1" t="inlineStr"/>
+    </row>
+    <row r="47" ht="54" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B47" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C47" s="1" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D47" s="1" t="inlineStr">
         <is>
           <t>26433057590</t>
         </is>
       </c>
-      <c r="E42" s="1" t="inlineStr">
+      <c r="E47" s="1" t="inlineStr">
         <is>
           <t>Select the option that is related to the third term in the same way as the second term is
 related to the first term and the sixth term is related to the fifth term.
 16 : 50 :: 49 : ? :: 144 : 338</t>
         </is>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F47" s="1" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="G42" s="1" t="inlineStr">
+      <c r="G47" s="1" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="H42" s="1" t="inlineStr">
+      <c r="H47" s="1" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="I42" s="1" t="inlineStr">
+      <c r="I47" s="1" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="J42" s="1" t="inlineStr"/>
-    </row>
-    <row r="43" ht="72" customHeight="1">
-      <c r="A43" s="1" t="inlineStr">
+      <c r="J47" s="1" t="inlineStr"/>
+    </row>
+    <row r="48" ht="72" customHeight="1">
+      <c r="A48" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B48" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
+      <c r="C48" s="1" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D48" s="1" t="inlineStr">
         <is>
           <t>26433056182</t>
         </is>
       </c>
-      <c r="E43" s="1" t="inlineStr">
+      <c r="E48" s="1" t="inlineStr">
         <is>
           <t>Select the option that is related to the fifth letter-cluster in the same way as the second
 letter-cluster is related to the first letter-cluster and the fourth letter-cluster is related
@@ -2676,99 +2932,99 @@
 MASTER : TSAMRE :: SMILES : LIMSSE :: FLIMSY : ?</t>
         </is>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F48" s="1" t="inlineStr">
         <is>
           <t>FLIMYS</t>
         </is>
       </c>
-      <c r="G43" s="1" t="inlineStr">
+      <c r="G48" s="1" t="inlineStr">
         <is>
           <t>FILMYS</t>
         </is>
       </c>
-      <c r="H43" s="1" t="inlineStr">
+      <c r="H48" s="1" t="inlineStr">
         <is>
           <t>MILFYS</t>
         </is>
       </c>
-      <c r="I43" s="1" t="inlineStr">
+      <c r="I48" s="1" t="inlineStr">
         <is>
           <t>MLYFIS</t>
         </is>
       </c>
-      <c r="J43" s="1" t="inlineStr"/>
-    </row>
-    <row r="44" ht="36" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="J48" s="1" t="inlineStr"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
+      <c r="B49" s="1" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
+      <c r="C49" s="1" t="inlineStr">
         <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D44" s="1" t="inlineStr">
+      <c r="D49" s="1" t="inlineStr">
         <is>
           <t>26433067624</t>
         </is>
       </c>
-      <c r="E44" s="1" t="inlineStr">
+      <c r="E49" s="1" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 144, 127, 110, ?, 76, 59</t>
         </is>
       </c>
-      <c r="F44" s="1" t="inlineStr">
+      <c r="F49" s="1" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="G44" s="1" t="inlineStr">
+      <c r="G49" s="1" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="H44" s="1" t="inlineStr">
+      <c r="H49" s="1" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="I44" s="1" t="inlineStr">
+      <c r="I49" s="1" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="J44" s="1" t="inlineStr"/>
-    </row>
-    <row r="45" ht="72" customHeight="1">
-      <c r="A45" s="1" t="inlineStr">
+      <c r="J49" s="1" t="inlineStr"/>
+    </row>
+    <row r="50" ht="72" customHeight="1">
+      <c r="A50" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
+      <c r="B50" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
+      <c r="C50" s="1" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D45" s="1" t="inlineStr">
+      <c r="D50" s="1" t="inlineStr">
         <is>
           <t>26433091437</t>
         </is>
       </c>
-      <c r="E45" s="1" t="inlineStr">
+      <c r="E50" s="1" t="inlineStr">
         <is>
           <t>Six friends A, C, D, E, F and G are sitting in a straight row, facing north. They are
 waiting for their seventh friend B to join. Exactly three people are sitting to the left of
@@ -2776,96 +3032,100 @@
 the immediate left of A, and E is second to the right of A, where will B sit?</t>
         </is>
       </c>
-      <c r="F45" s="1" t="inlineStr">
+      <c r="F50" s="1" t="inlineStr">
         <is>
           <t>Fourth to the right of F</t>
         </is>
       </c>
-      <c r="G45" s="1" t="inlineStr">
+      <c r="G50" s="1" t="inlineStr">
         <is>
           <t>Fifth to the right of G</t>
         </is>
       </c>
-      <c r="H45" s="1" t="inlineStr">
+      <c r="H50" s="1" t="inlineStr">
         <is>
           <t>To the immediate right of E</t>
         </is>
       </c>
-      <c r="I45" s="1" t="inlineStr">
+      <c r="I50" s="1" t="inlineStr">
         <is>
           <t>Third to the right of D</t>
         </is>
       </c>
-      <c r="J45" s="1" t="inlineStr"/>
-    </row>
-    <row r="46" ht="54" customHeight="1">
-      <c r="A46" s="1" t="inlineStr">
+      <c r="J50" s="1" t="inlineStr"/>
+    </row>
+    <row r="51" ht="54" customHeight="1">
+      <c r="A51" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B51" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
+      <c r="C51" s="1" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D51" s="1" t="inlineStr">
         <is>
           <t>26433067670</t>
         </is>
       </c>
-      <c r="E46" s="1" t="inlineStr">
+      <c r="E51" s="1" t="inlineStr">
         <is>
           <t>If A denotes ‘+’, B denotes ‘×’, C denotes ‘−’, and D denotes ‘÷’, then what will come in
 place of ‘?’ in the following equation?
 140 D 7 A 30 = 25 B ? D 8</t>
         </is>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F51" s="1" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G46" s="1" t="inlineStr">
+      <c r="G51" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H46" s="1" t="inlineStr">
+      <c r="H51" s="1" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="I46" s="1" t="inlineStr"/>
-      <c r="J46" s="1" t="inlineStr"/>
-    </row>
-    <row r="47" ht="144" customHeight="1">
-      <c r="A47" s="1" t="inlineStr">
+      <c r="I51" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52" ht="144" customHeight="1">
+      <c r="A52" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B52" s="1" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
+      <c r="C52" s="1" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D52" s="1" t="inlineStr">
         <is>
           <t>26433068664</t>
         </is>
       </c>
-      <c r="E47" s="1" t="inlineStr">
+      <c r="E52" s="1" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as are the numbers of
 the following sets.
@@ -2877,99 +3137,150 @@
 (65, 55, 68)</t>
         </is>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F52" s="1" t="inlineStr">
         <is>
           <t>(95,	85,	124)</t>
         </is>
       </c>
-      <c r="G47" s="1" t="inlineStr">
+      <c r="G52" s="1" t="inlineStr">
         <is>
           <t>(95,	85,	104)</t>
         </is>
       </c>
-      <c r="H47" s="1" t="inlineStr">
+      <c r="H52" s="1" t="inlineStr">
         <is>
           <t>(95,	80,	104)</t>
         </is>
       </c>
-      <c r="I47" s="1" t="inlineStr">
+      <c r="I52" s="1" t="inlineStr">
         <is>
           <t>(90,	85,	104)</t>
         </is>
       </c>
-      <c r="J47" s="1" t="inlineStr"/>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="1" t="inlineStr">
+      <c r="J52" s="1" t="inlineStr"/>
+    </row>
+    <row r="53" ht="72" customHeight="1">
+      <c r="A53" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>26433093131</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>I, J, K, L, M, N and O are seven friends having different ages. I is elder than K but
+younger than J. K is elder than N but younger than I. J is elder than I but younger than
+2 persons. L is elder than J. M is not the eldest and O is the youngest. The age of how
+many people is between I and N?</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G53" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H53" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I53" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J53" s="1" t="inlineStr"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
+      <c r="C54" s="1" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D54" s="1" t="inlineStr">
         <is>
           <t>26433067788</t>
         </is>
       </c>
-      <c r="E48" s="1" t="inlineStr">
+      <c r="E54" s="1" t="inlineStr">
         <is>
           <t>In a certain code language, 'FUTURE' is coded as ‘91’ and ‘MONEY’ is coded as ‘72’.
 How will 'SECURE' be coded in that language?</t>
         </is>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F54" s="1" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="G48" s="1" t="inlineStr">
+      <c r="G54" s="1" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="H48" s="1" t="inlineStr">
+      <c r="H54" s="1" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="I48" s="1" t="inlineStr">
+      <c r="I54" s="1" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="J48" s="1" t="inlineStr"/>
-    </row>
-    <row r="49" ht="162" customHeight="1">
-      <c r="A49" s="1" t="inlineStr">
+      <c r="J54" s="1" t="inlineStr"/>
+    </row>
+    <row r="55" ht="162" customHeight="1">
+      <c r="A55" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C49" s="1" t="inlineStr">
+      <c r="C55" s="1" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D55" s="1" t="inlineStr">
         <is>
           <t>26433087328</t>
         </is>
       </c>
-      <c r="E49" s="1" t="inlineStr">
+      <c r="E55" s="1" t="inlineStr">
         <is>
           <t>Study the given pattern carefully and select the number that can replace the question
 mark (?) in it.
@@ -2982,149 +3293,149 @@
 3 and then performing mathematical operations on 1 and 3 is not allowed)</t>
         </is>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F55" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G49" s="1" t="inlineStr">
+      <c r="G55" s="1" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H49" s="1" t="inlineStr">
+      <c r="H55" s="1" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="I49" s="1" t="inlineStr">
+      <c r="I55" s="1" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J49" s="1" t="inlineStr"/>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="1" t="inlineStr">
+      <c r="J55" s="1" t="inlineStr"/>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
+      <c r="C56" s="1" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D56" s="1" t="inlineStr">
         <is>
           <t>26433057905</t>
         </is>
       </c>
-      <c r="E50" s="1" t="inlineStr">
+      <c r="E56" s="1" t="inlineStr">
         <is>
           <t>In a code language, 'AMIT' is coded as 86 and 'VIJAY' is coded as</t>
         </is>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F56" s="1" t="inlineStr">
         <is>
           <t>How will
 'GARIMA' be coded in the same language?</t>
         </is>
       </c>
-      <c r="G50" s="1" t="inlineStr">
+      <c r="G56" s="1" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="H50" s="1" t="inlineStr">
+      <c r="H56" s="1" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="I50" s="1" t="inlineStr">
+      <c r="I56" s="1" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="J50" s="1" t="inlineStr"/>
-    </row>
-    <row r="51" ht="54" customHeight="1">
-      <c r="A51" s="1" t="inlineStr">
+      <c r="J56" s="1" t="inlineStr"/>
+    </row>
+    <row r="57" ht="54" customHeight="1">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
+      <c r="C57" s="1" t="inlineStr">
         <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D57" s="1" t="inlineStr">
         <is>
           <t>26433067694</t>
         </is>
       </c>
-      <c r="E51" s="1" t="inlineStr">
+      <c r="E57" s="1" t="inlineStr">
         <is>
           <t>Which two symbols from amongst the given options should be interchanged to make
 the given equation correct?
 272 ÷ 17 − 196 ÷ ( 5 × 3 + 1) = 30</t>
         </is>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F57" s="1" t="inlineStr">
         <is>
           <t>× and −</t>
         </is>
       </c>
-      <c r="G51" s="1" t="inlineStr">
+      <c r="G57" s="1" t="inlineStr">
         <is>
           <t>× and +</t>
         </is>
       </c>
-      <c r="H51" s="1" t="inlineStr">
+      <c r="H57" s="1" t="inlineStr">
         <is>
           <t>+ and ÷</t>
         </is>
       </c>
-      <c r="I51" s="1" t="inlineStr">
+      <c r="I57" s="1" t="inlineStr">
         <is>
           <t>+ and −</t>
         </is>
       </c>
-      <c r="J51" s="1" t="inlineStr"/>
-    </row>
-    <row r="52" ht="216" customHeight="1">
-      <c r="A52" s="1" t="inlineStr">
+      <c r="J57" s="1" t="inlineStr"/>
+    </row>
+    <row r="58" ht="216" customHeight="1">
+      <c r="A58" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
+      <c r="C58" s="1" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D52" s="1" t="inlineStr">
+      <c r="D58" s="1" t="inlineStr">
         <is>
           <t>26433091627</t>
         </is>
       </c>
-      <c r="E52" s="1" t="inlineStr">
+      <c r="E58" s="1" t="inlineStr">
         <is>
           <t>Three statements are given, followed by three conclusions numbered I, II and III.
 Assuming the statements to be true, even if they seem to be at variance with
@@ -3140,244 +3451,244 @@
 III. Some actresses are rich.</t>
         </is>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="F58" s="1" t="inlineStr">
         <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="G52" s="1" t="inlineStr">
+      <c r="G58" s="1" t="inlineStr">
         <is>
           <t>Only conclusions I and III follow</t>
         </is>
       </c>
-      <c r="H52" s="1" t="inlineStr">
+      <c r="H58" s="1" t="inlineStr">
         <is>
           <t>All the conclusions follow</t>
         </is>
       </c>
-      <c r="I52" s="1" t="inlineStr">
+      <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Only conclusions I and II follow</t>
         </is>
       </c>
-      <c r="J52" s="1" t="inlineStr"/>
-    </row>
-    <row r="53" ht="54" customHeight="1">
-      <c r="A53" s="1" t="inlineStr">
+      <c r="J58" s="1" t="inlineStr"/>
+    </row>
+    <row r="59" ht="54" customHeight="1">
+      <c r="A59" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
+      <c r="C59" s="1" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D53" s="1" t="inlineStr">
+      <c r="D59" s="1" t="inlineStr">
         <is>
           <t>26433067683</t>
         </is>
       </c>
-      <c r="E53" s="1" t="inlineStr">
+      <c r="E59" s="1" t="inlineStr">
         <is>
           <t>Which two symbols from amongst the given options should be interchanged to make
 the given equation correct?
 (35 – 2) × 3 = (56 × 8 ÷ 3 + 100) × 11</t>
         </is>
       </c>
-      <c r="F53" s="1" t="inlineStr">
+      <c r="F59" s="1" t="inlineStr">
         <is>
           <t>÷ and +</t>
         </is>
       </c>
-      <c r="G53" s="1" t="inlineStr">
+      <c r="G59" s="1" t="inlineStr">
         <is>
           <t>× and ÷</t>
         </is>
       </c>
-      <c r="H53" s="1" t="inlineStr">
+      <c r="H59" s="1" t="inlineStr">
         <is>
           <t>+ and −</t>
         </is>
       </c>
-      <c r="I53" s="1" t="inlineStr">
+      <c r="I59" s="1" t="inlineStr">
         <is>
           <t>× and −</t>
         </is>
       </c>
-      <c r="J53" s="1" t="inlineStr"/>
-    </row>
-    <row r="54" ht="36" customHeight="1">
-      <c r="A54" s="1" t="inlineStr">
+      <c r="J59" s="1" t="inlineStr"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
+      <c r="C60" s="1" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D54" s="1" t="inlineStr">
+      <c r="D60" s="1" t="inlineStr">
         <is>
           <t>26433079386</t>
         </is>
       </c>
-      <c r="E54" s="1" t="inlineStr">
+      <c r="E60" s="1" t="inlineStr">
         <is>
           <t>Select the correct option that indicates the arrangement of the following words in a
 logical and meaningful order.</t>
         </is>
       </c>
-      <c r="F54" s="1" t="inlineStr">
+      <c r="F60" s="1" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="G54" s="1" t="inlineStr">
+      <c r="G60" s="1" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="H54" s="1" t="inlineStr">
+      <c r="H60" s="1" t="inlineStr">
         <is>
           <t>West Europe</t>
         </is>
       </c>
-      <c r="I54" s="1" t="inlineStr">
+      <c r="I60" s="1" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="J54" s="1" t="inlineStr"/>
-    </row>
-    <row r="55" ht="54" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="J60" s="1" t="inlineStr"/>
+    </row>
+    <row r="61" ht="54" customHeight="1">
+      <c r="A61" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B55" s="1" t="inlineStr">
+      <c r="B61" s="1" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="C55" s="1" t="inlineStr">
+      <c r="C61" s="1" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D55" s="1" t="inlineStr">
+      <c r="D61" s="1" t="inlineStr">
         <is>
           <t>26433069675</t>
         </is>
       </c>
-      <c r="E55" s="1" t="inlineStr">
+      <c r="E61" s="1" t="inlineStr">
         <is>
           <t>Select the correct combination of mathematical signs to replace the * signs and to
 balance the given equation.
 831 * 3 * 13 * 45 * 245 * 1</t>
         </is>
       </c>
-      <c r="F55" s="1" t="inlineStr">
+      <c r="F61" s="1" t="inlineStr">
         <is>
           <t>÷, +, −, =, ×</t>
         </is>
       </c>
-      <c r="G55" s="1">
+      <c r="G61" s="1">
         <f>, ×, ÷, +, −</f>
         <v/>
       </c>
-      <c r="H55" s="1">
+      <c r="H61" s="1">
         <f>, −, ÷, +, −</f>
         <v/>
       </c>
-      <c r="I55" s="1">
+      <c r="I61" s="1">
         <f>, ÷, +, −, ×</f>
         <v/>
       </c>
-      <c r="J55" s="1" t="inlineStr"/>
-    </row>
-    <row r="56" ht="25" customHeight="1">
-      <c r="A56" s="1" t="inlineStr">
+      <c r="J61" s="1" t="inlineStr"/>
+    </row>
+    <row r="62" ht="25" customHeight="1">
+      <c r="A62" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
+      <c r="B62" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
+      <c r="C62" s="1" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D56" s="1" t="inlineStr">
+      <c r="D62" s="1" t="inlineStr">
         <is>
           <t>26433093108</t>
         </is>
       </c>
-      <c r="E56" s="1" t="inlineStr">
+      <c r="E62" s="1" t="inlineStr">
         <is>
           <t>What will be the day of the week on 19th November 2053?</t>
         </is>
       </c>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="F62" s="1" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="G56" s="1" t="inlineStr">
+      <c r="G62" s="1" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="H56" s="1" t="inlineStr">
+      <c r="H62" s="1" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I56" s="1" t="inlineStr">
+      <c r="I62" s="1" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="J56" s="1" t="inlineStr"/>
-    </row>
-    <row r="57" ht="90" customHeight="1">
-      <c r="A57" s="1" t="inlineStr">
+      <c r="J62" s="1" t="inlineStr"/>
+    </row>
+    <row r="63" ht="90" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
+      <c r="C63" s="1" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D57" s="1" t="inlineStr">
+      <c r="D63" s="1" t="inlineStr">
         <is>
           <t>26433086988</t>
         </is>
       </c>
-      <c r="E57" s="1" t="inlineStr">
+      <c r="E63" s="1" t="inlineStr">
         <is>
           <t>‘P + Q’ means ‘P is the daughter of Q’.
 ‘P % Q’ means ‘P is the son of Q’.
@@ -3386,75 +3697,3546 @@
 Section : General Awareness</t>
         </is>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F63" s="1" t="inlineStr">
         <is>
           <t>C is the father of A.</t>
         </is>
       </c>
-      <c r="G57" s="1" t="inlineStr">
+      <c r="G63" s="1" t="inlineStr">
         <is>
           <t>B is sister of E’s son.</t>
         </is>
       </c>
-      <c r="H57" s="1" t="inlineStr">
+      <c r="H63" s="1" t="inlineStr">
         <is>
           <t>D is the mother of B’s husband.</t>
         </is>
       </c>
-      <c r="I57" s="1" t="inlineStr">
+      <c r="I63" s="1" t="inlineStr">
         <is>
           <t>A is the daughter of E’s son.</t>
         </is>
       </c>
-      <c r="J57" s="1" t="inlineStr"/>
-    </row>
-    <row r="58" ht="25" customHeight="1">
-      <c r="A58" s="1" t="inlineStr">
+      <c r="J63" s="1" t="inlineStr"/>
+    </row>
+    <row r="64" ht="36" customHeight="1">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>26433055395</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>Pandit Anokhe Lal Mishra, a gem among musicians in India, was a renowned player of
+which of the following instruments?</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>Sitar</t>
+        </is>
+      </c>
+      <c r="G64" s="1" t="inlineStr">
+        <is>
+          <t>Tabla</t>
+        </is>
+      </c>
+      <c r="H64" s="1" t="inlineStr">
+        <is>
+          <t>Ghatam</t>
+        </is>
+      </c>
+      <c r="I64" s="1" t="inlineStr">
+        <is>
+          <t>Sarangi</t>
+        </is>
+      </c>
+      <c r="J64" s="1" t="inlineStr"/>
+    </row>
+    <row r="65" ht="25" customHeight="1">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D58" s="1" t="inlineStr">
+      <c r="D65" s="1" t="inlineStr">
         <is>
           <t>26433085248</t>
         </is>
       </c>
-      <c r="E58" s="1" t="inlineStr">
+      <c r="E65" s="1" t="inlineStr">
         <is>
           <t>Who among the following Vijayanagara kings defeated the sultan of Bijapur in 1520?</t>
         </is>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F65" s="1" t="inlineStr">
         <is>
           <t>Deva Raya II</t>
         </is>
       </c>
-      <c r="G58" s="1" t="inlineStr">
+      <c r="G65" s="1" t="inlineStr">
         <is>
           <t>Krishnadeva Raya</t>
         </is>
       </c>
-      <c r="H58" s="1" t="inlineStr">
+      <c r="H65" s="1" t="inlineStr">
         <is>
           <t>Vira Narasimha Raya</t>
         </is>
       </c>
-      <c r="I58" s="1" t="inlineStr">
+      <c r="I65" s="1" t="inlineStr">
         <is>
           <t>Bukka Raya I</t>
         </is>
       </c>
-      <c r="J58" s="1" t="inlineStr"/>
+      <c r="J65" s="1" t="inlineStr"/>
+    </row>
+    <row r="66" ht="25" customHeight="1">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>26433091451</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following books was written by Megasthenes?</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>Nitisara</t>
+        </is>
+      </c>
+      <c r="G66" s="1" t="inlineStr">
+        <is>
+          <t>Nagananda</t>
+        </is>
+      </c>
+      <c r="H66" s="1" t="inlineStr">
+        <is>
+          <t>Buddha charita</t>
+        </is>
+      </c>
+      <c r="I66" s="1" t="inlineStr">
+        <is>
+          <t>Indica</t>
+        </is>
+      </c>
+      <c r="J66" s="1" t="inlineStr"/>
+    </row>
+    <row r="67" ht="72" customHeight="1">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr"/>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>Parts of the following sentence have been given as options. Select the option that
+contains an error.
+She was fond of walking along the path besides the lake.
+A</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>along the path
+s/</t>
+        </is>
+      </c>
+      <c r="G67" s="1" t="inlineStr">
+        <is>
+          <t>besides the lake</t>
+        </is>
+      </c>
+      <c r="H67" s="1" t="inlineStr">
+        <is>
+          <t>She was</t>
+        </is>
+      </c>
+      <c r="I67" s="1" t="inlineStr">
+        <is>
+          <t>fond of walking</t>
+        </is>
+      </c>
+      <c r="J67" s="1" t="inlineStr"/>
+    </row>
+    <row r="68" ht="90" customHeight="1">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr"/>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>The following sentence has been divided into parts. One of them may contain an error.
+Select the part that contains the error from the given options. If you don’t find any
+error mark 'No error' as your answer.
+Father took the newspaper / in his hand to / go through it once again.
+s/</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>No error</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>in his hand to</t>
+        </is>
+      </c>
+      <c r="H68" s="1" t="inlineStr">
+        <is>
+          <t>go through it once again</t>
+        </is>
+      </c>
+      <c r="I68" s="1" t="inlineStr">
+        <is>
+          <t>Father took the newspaper</t>
+        </is>
+      </c>
+      <c r="J68" s="1" t="inlineStr"/>
+    </row>
+    <row r="69" ht="90" customHeight="1">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr"/>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>Parts of the following sentence have been underlined and given as options. Select the
+option that contains an error.
+Policeman came to my village and asked about a person who burgled a house last
+night.
+^</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>policeman</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>a house</t>
+        </is>
+      </c>
+      <c r="H69" s="1" t="inlineStr">
+        <is>
+          <t>my village</t>
+        </is>
+      </c>
+      <c r="I69" s="1" t="inlineStr">
+        <is>
+          <t>a person</t>
+        </is>
+      </c>
+      <c r="J69" s="1" t="inlineStr"/>
+    </row>
+    <row r="70" ht="54" customHeight="1">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr"/>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>Select the option that will improve the given sentence by using the most appropriate
+verb.
+Soorya walking to college every day.</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>Soorya walk to college every day.
+\^</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>Soorya walked to college every day.</t>
+        </is>
+      </c>
+      <c r="H70" s="1" t="inlineStr">
+        <is>
+          <t>Soorya have walked to college every day.</t>
+        </is>
+      </c>
+      <c r="I70" s="1" t="inlineStr">
+        <is>
+          <t>Soorya is walking to college every day.</t>
+        </is>
+      </c>
+      <c r="J70" s="1" t="inlineStr"/>
+    </row>
+    <row r="71" ht="216" customHeight="1">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr"/>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to fill in blank no.</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>controls</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>opens</t>
+        </is>
+      </c>
+      <c r="H71" s="1" t="inlineStr">
+        <is>
+          <t>leads</t>
+        </is>
+      </c>
+      <c r="I71" s="1" t="inlineStr">
+        <is>
+          <t>closes
+Comprehension:
+In the following passage, some words have been deleted. Read the passage carefully and
+select the most appropriate option to fill in each blank.
+What is literacy? It is the golden key that (1)_______ the gates to a whole new world. It
+heralds the dawn of a new (2)______. But the media hype seems to give the impression that
+literacy simply means the ability to sign one’s name, instead of putting thumb impression. Isn’t
+that a very (3)______ , simplistic interpretation of the word?
+Taking up this narrow meaning of the word, politicians proclaim that their states have
+achieved 80 or 90 per cent literacy or even (4)______ . But quite often, what happens is, once
+the training course is over, to produce (5)______ , the neo-literates soon lapse into illiteracy.
+SubQuestion No : 6</t>
+        </is>
+      </c>
+      <c r="J71" s="1" t="inlineStr"/>
+    </row>
+    <row r="72" ht="216" customHeight="1">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr"/>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to fill in blank no.</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="G72" s="1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="H72" s="1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="I72" s="1" t="inlineStr">
+        <is>
+          <t>season
+Comprehension:
+In the following passage, some words have been deleted. Read the passage carefully and
+select the most appropriate option to fill in each blank.
+What is literacy? It is the golden key that (1)_______ the gates to a whole new world. It
+heralds the dawn of a new (2)______. But the media hype seems to give the impression that
+literacy simply means the ability to sign one’s name, instead of putting thumb impression. Isn’t
+that a very (3)______ , simplistic interpretation of the word?
+Taking up this narrow meaning of the word, politicians proclaim that their states have
+achieved 80 or 90 per cent literacy or even (4)______ . But quite often, what happens is, once
+the training course is over, to produce (5)______ , the neo-literates soon lapse into illiteracy.
+SubQuestion No : 7</t>
+        </is>
+      </c>
+      <c r="J72" s="1" t="inlineStr"/>
+    </row>
+    <row r="73" ht="25" customHeight="1">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr"/>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to fill in blank no.</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>wide</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>daunted</t>
+        </is>
+      </c>
+      <c r="H73" s="1" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>small</t>
+        </is>
+      </c>
+      <c r="J73" s="1" t="inlineStr"/>
+    </row>
+    <row r="74" ht="216" customHeight="1">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr"/>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to fill in blank no.</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>better</t>
+        </is>
+      </c>
+      <c r="H74" s="1" t="inlineStr">
+        <is>
+          <t>higher</t>
+        </is>
+      </c>
+      <c r="I74" s="1" t="inlineStr">
+        <is>
+          <t>lower
+Comprehension:
+In the following passage, some words have been deleted. Read the passage carefully and
+select the most appropriate option to fill in each blank.
+What is literacy? It is the golden key that (1)_______ the gates to a whole new world. It
+heralds the dawn of a new (2)______. But the media hype seems to give the impression that
+literacy simply means the ability to sign one’s name, instead of putting thumb impression. Isn’t
+that a very (3)______ , simplistic interpretation of the word?
+Taking up this narrow meaning of the word, politicians proclaim that their states have
+achieved 80 or 90 per cent literacy or even (4)______ . But quite often, what happens is, once
+the training course is over, to produce (5)______ , the neo-literates soon lapse into illiteracy.
+SubQuestion No : 9</t>
+        </is>
+      </c>
+      <c r="J74" s="1" t="inlineStr"/>
+    </row>
+    <row r="75" ht="25" customHeight="1">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr"/>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to fill in blank no.</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>beginners</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>literates</t>
+        </is>
+      </c>
+      <c r="H75" s="1" t="inlineStr">
+        <is>
+          <t>pupils</t>
+        </is>
+      </c>
+      <c r="I75" s="1" t="inlineStr">
+        <is>
+          <t>education</t>
+        </is>
+      </c>
+      <c r="J75" s="1" t="inlineStr"/>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr"/>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate ANTONYM of the underlined word in the given sentence.
+He is not friendly with him in the office.</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>Gregarious</t>
+        </is>
+      </c>
+      <c r="G76" s="1" t="inlineStr">
+        <is>
+          <t>Revel</t>
+        </is>
+      </c>
+      <c r="H76" s="1" t="inlineStr">
+        <is>
+          <t>Intelligent</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>Hostile</t>
+        </is>
+      </c>
+      <c r="J76" s="1" t="inlineStr"/>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr"/>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>Identify the most appropriate ANTONYM of the given word.</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>Help
+He worked alone as he did not want anyone to hamper his project.</t>
+        </is>
+      </c>
+      <c r="G77" s="1" t="inlineStr">
+        <is>
+          <t>Impede</t>
+        </is>
+      </c>
+      <c r="H77" s="1" t="inlineStr">
+        <is>
+          <t>Care</t>
+        </is>
+      </c>
+      <c r="I77" s="1" t="inlineStr">
+        <is>
+          <t>Finish</t>
+        </is>
+      </c>
+      <c r="J77" s="1" t="inlineStr"/>
+    </row>
+    <row r="78" ht="36" customHeight="1">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate synonym of the given word.</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>Aboriginal
+Indigenous</t>
+        </is>
+      </c>
+      <c r="G78" s="1" t="inlineStr">
+        <is>
+          <t>Artificial</t>
+        </is>
+      </c>
+      <c r="H78" s="1" t="inlineStr">
+        <is>
+          <t>Tangible</t>
+        </is>
+      </c>
+      <c r="I78" s="1" t="inlineStr">
+        <is>
+          <t>Literary</t>
+        </is>
+      </c>
+      <c r="J78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79" ht="54" customHeight="1">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate collocation to fill in the blank.</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>committing
+Ujjwal was imprisoned for
+a crime.</t>
+        </is>
+      </c>
+      <c r="G79" s="1" t="inlineStr">
+        <is>
+          <t>making</t>
+        </is>
+      </c>
+      <c r="H79" s="1" t="inlineStr">
+        <is>
+          <t>undertaking</t>
+        </is>
+      </c>
+      <c r="I79" s="1" t="inlineStr">
+        <is>
+          <t>involving</t>
+        </is>
+      </c>
+      <c r="J79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80" ht="54" customHeight="1">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option that can substitute the underlined segment in the
+given sentence. If there is no need to substitute it, select ‘No substitution required’.
+I cannot use my office at the moment because it being painted.</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>it has being painted</t>
+        </is>
+      </c>
+      <c r="G80" s="1" t="inlineStr">
+        <is>
+          <t>it is being painted</t>
+        </is>
+      </c>
+      <c r="H80" s="1" t="inlineStr">
+        <is>
+          <t>No substitution required</t>
+        </is>
+      </c>
+      <c r="I80" s="1" t="inlineStr">
+        <is>
+          <t>it had been paint</t>
+        </is>
+      </c>
+      <c r="J80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81" ht="54" customHeight="1">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr"/>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>The following sentence has been split into four segments. Identify the segment that
+contains a grammatical error.
+When Serena / will arrive, / she will / call you.</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>will arrive</t>
+        </is>
+      </c>
+      <c r="G81" s="1" t="inlineStr">
+        <is>
+          <t>When Serena</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="inlineStr">
+        <is>
+          <t>call you</t>
+        </is>
+      </c>
+      <c r="I81" s="1" t="inlineStr">
+        <is>
+          <t>she will</t>
+        </is>
+      </c>
+      <c r="J81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82" ht="36" customHeight="1">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr"/>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate meaning of the given idiom.
+A sting in the tail</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>A situation in which a large group has to do something to satisfy a small group</t>
+        </is>
+      </c>
+      <c r="G82" s="1" t="inlineStr">
+        <is>
+          <t>Something which seems bad at first but contains a pleasant part at the end</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="inlineStr">
+        <is>
+          <t>To initiate a situation that is very complicated or problematic</t>
+        </is>
+      </c>
+      <c r="I82" s="1" t="inlineStr">
+        <is>
+          <t>An unexpected, typically unpleasant or problematic end to something</t>
+        </is>
+      </c>
+      <c r="J82" s="1" t="inlineStr"/>
+    </row>
+    <row r="83" ht="36" customHeight="1">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr"/>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate synonym of the given word.
+Magnificent</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G83" s="1" t="inlineStr">
+        <is>
+          <t>Humble</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="inlineStr">
+        <is>
+          <t>Modest</t>
+        </is>
+      </c>
+      <c r="I83" s="1" t="inlineStr">
+        <is>
+          <t>Splendid
+'^|^ Download SSC C:GL, ( :i HSL E-BOOKS ^—^</t>
+        </is>
+      </c>
+      <c r="J83" s="1" t="inlineStr"/>
+    </row>
+    <row r="84" ht="54" customHeight="1">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B84" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D84" s="1" t="inlineStr"/>
+      <c r="E84" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option that can substitute the underlined segment in the
+given sentence.
+No sooner did we reach at the party that it began to rain.</t>
+        </is>
+      </c>
+      <c r="F84" s="1" t="inlineStr">
+        <is>
+          <t>before it began to rain</t>
+        </is>
+      </c>
+      <c r="G84" s="1" t="inlineStr">
+        <is>
+          <t>as it began to rain</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="inlineStr">
+        <is>
+          <t>it began to rain</t>
+        </is>
+      </c>
+      <c r="I84" s="1" t="inlineStr">
+        <is>
+          <t>than it began to rain</t>
+        </is>
+      </c>
+      <c r="J84" s="1" t="inlineStr"/>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B85" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D85" s="1" t="inlineStr"/>
+      <c r="E85" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate synonym of ‘amazement’ to fill the blank.</t>
+        </is>
+      </c>
+      <c r="F85" s="1" t="inlineStr">
+        <is>
+          <t>astonishment
+Leena was filled with _______ when she saw the diamond ring as her wedding gift.</t>
+        </is>
+      </c>
+      <c r="G85" s="1" t="inlineStr">
+        <is>
+          <t>measurement</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="inlineStr">
+        <is>
+          <t>happiness</t>
+        </is>
+      </c>
+      <c r="I85" s="1" t="inlineStr">
+        <is>
+          <t>haughtiness</t>
+        </is>
+      </c>
+      <c r="J85" s="1" t="inlineStr"/>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B86" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D86" s="1" t="inlineStr"/>
+      <c r="E86" s="1" t="inlineStr">
+        <is>
+          <t>Identify the INCORRECTLY spelt word in the following sentence.
+To avoid indigetion, it is necessary to chew food properly.</t>
+        </is>
+      </c>
+      <c r="F86" s="1" t="inlineStr">
+        <is>
+          <t>chew</t>
+        </is>
+      </c>
+      <c r="G86" s="1" t="inlineStr">
+        <is>
+          <t>necessary</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="inlineStr">
+        <is>
+          <t>indigetion</t>
+        </is>
+      </c>
+      <c r="I86" s="1" t="inlineStr">
+        <is>
+          <t>properly</t>
+        </is>
+      </c>
+      <c r="J86" s="1" t="inlineStr"/>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B87" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D87" s="1" t="inlineStr"/>
+      <c r="E87" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate pair of words to fill in the blanks.</t>
+        </is>
+      </c>
+      <c r="F87" s="1" t="inlineStr">
+        <is>
+          <t>ate; eight
+Yesterday, he ________ pizza and _________burgers in one go.</t>
+        </is>
+      </c>
+      <c r="G87" s="1" t="inlineStr">
+        <is>
+          <t>eight; ate</t>
+        </is>
+      </c>
+      <c r="H87" s="1" t="inlineStr">
+        <is>
+          <t>eight; eight</t>
+        </is>
+      </c>
+      <c r="I87" s="1" t="inlineStr">
+        <is>
+          <t>ate; ate</t>
+        </is>
+      </c>
+      <c r="J87" s="1" t="inlineStr"/>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B88" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr"/>
+      <c r="E88" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate meaning of the given idiom.
+Gift of the gab</t>
+        </is>
+      </c>
+      <c r="F88" s="1" t="inlineStr">
+        <is>
+          <t>Humorous</t>
+        </is>
+      </c>
+      <c r="G88" s="1" t="inlineStr">
+        <is>
+          <t>Talent for speaking</t>
+        </is>
+      </c>
+      <c r="H88" s="1" t="inlineStr">
+        <is>
+          <t>Witty</t>
+        </is>
+      </c>
+      <c r="I88" s="1" t="inlineStr">
+        <is>
+          <t>Talent for singing</t>
+        </is>
+      </c>
+      <c r="J88" s="1" t="inlineStr"/>
+    </row>
+    <row r="89" ht="72" customHeight="1">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B89" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr"/>
+      <c r="E89" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option that can substitute the underlined words in the
+following sentence.
+The interdisciplinary approach utilised in this study facilitates comprehensive
+understanding of the complex phenomenon under investigation.</t>
+        </is>
+      </c>
+      <c r="F89" s="1" t="inlineStr">
+        <is>
+          <t>is facilitates a comprehensive understanding</t>
+        </is>
+      </c>
+      <c r="G89" s="1" t="inlineStr">
+        <is>
+          <t>will have facilitated a comprehensive understanding</t>
+        </is>
+      </c>
+      <c r="H89" s="1" t="inlineStr">
+        <is>
+          <t>utilises a comprehensive understanding</t>
+        </is>
+      </c>
+      <c r="I89" s="1" t="inlineStr">
+        <is>
+          <t>facilitated a comprehensive understanding</t>
+        </is>
+      </c>
+      <c r="J89" s="1" t="inlineStr"/>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B90" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D90" s="1" t="inlineStr"/>
+      <c r="E90" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate spelling of the underlined word in the given sentence.
+He lost all senisation in his legs through a cramp.</t>
+        </is>
+      </c>
+      <c r="F90" s="1" t="inlineStr">
+        <is>
+          <t>syansation</t>
+        </is>
+      </c>
+      <c r="G90" s="1" t="inlineStr">
+        <is>
+          <t>sansation</t>
+        </is>
+      </c>
+      <c r="H90" s="1" t="inlineStr">
+        <is>
+          <t>sensation</t>
+        </is>
+      </c>
+      <c r="I90" s="1" t="inlineStr">
+        <is>
+          <t>sensition</t>
+        </is>
+      </c>
+      <c r="J90" s="1" t="inlineStr"/>
+    </row>
+    <row r="91" ht="36" customHeight="1">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B91" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D91" s="1" t="inlineStr"/>
+      <c r="E91" s="1" t="inlineStr">
+        <is>
+          <t>Select the most appropriate ANTONYM of the given word.
+Abandon</t>
+        </is>
+      </c>
+      <c r="F91" s="1" t="inlineStr">
+        <is>
+          <t>Adopt</t>
+        </is>
+      </c>
+      <c r="G91" s="1" t="inlineStr">
+        <is>
+          <t>Surrender</t>
+        </is>
+      </c>
+      <c r="H91" s="1" t="inlineStr">
+        <is>
+          <t>Destroy</t>
+        </is>
+      </c>
+      <c r="I91" s="1" t="inlineStr">
+        <is>
+          <t>Randomize</t>
+        </is>
+      </c>
+      <c r="J91" s="1" t="inlineStr"/>
+    </row>
+    <row r="92" ht="36" customHeight="1">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B92" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D92" s="1" t="inlineStr"/>
+      <c r="E92" s="1" t="inlineStr">
+        <is>
+          <t>If ‘A’ stands for ‘÷’, ‘B’ stands for ‘×’, ‘C’ stands for ‘+’ and ‘D’ stands for ‘–’, then the
+resultant of which of the following will be 100?</t>
+        </is>
+      </c>
+      <c r="F92" s="1" t="inlineStr">
+        <is>
+          <t>15 B 9 D 810 A 9 C 55</t>
+        </is>
+      </c>
+      <c r="G92" s="1" t="inlineStr">
+        <is>
+          <t>15 C 9 D 810 A 9 B 55</t>
+        </is>
+      </c>
+      <c r="H92" s="1" t="inlineStr">
+        <is>
+          <t>15 A 9 D 810 B 9 C 55</t>
+        </is>
+      </c>
+      <c r="I92" s="1" t="inlineStr">
+        <is>
+          <t>15 D 9 B 810 A 9 C 55</t>
+        </is>
+      </c>
+      <c r="J92" s="1" t="inlineStr"/>
+    </row>
+    <row r="93" ht="54" customHeight="1">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B93" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D93" s="1" t="inlineStr"/>
+      <c r="E93" s="1" t="inlineStr">
+        <is>
+          <t>Select the correct option that when filled in the blanks in the same sequence will make
+the series logically complete.
+QUAI_Q_YIL_U_ILQUU_L</t>
+        </is>
+      </c>
+      <c r="F93" s="1" t="inlineStr">
+        <is>
+          <t>LUQWI</t>
+        </is>
+      </c>
+      <c r="G93" s="1" t="inlineStr">
+        <is>
+          <t>LIQAU</t>
+        </is>
+      </c>
+      <c r="H93" s="1" t="inlineStr">
+        <is>
+          <t>LXIUQ</t>
+        </is>
+      </c>
+      <c r="I93" s="1" t="inlineStr">
+        <is>
+          <t>LWQUI</t>
+        </is>
+      </c>
+      <c r="J93" s="1" t="inlineStr"/>
+    </row>
+    <row r="94" ht="36" customHeight="1">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D94" s="1" t="inlineStr"/>
+      <c r="E94" s="1" t="inlineStr">
+        <is>
+          <t>Ill a certain code language, DZLW is coded as 'HDIT and 'CQYH' is coded as ‘GUWF’. What is the code for ‘MTBE</t>
+        </is>
+      </c>
+      <c r="F94" s="1" t="inlineStr">
+        <is>
+          <t>QXZC
+in the given code language?</t>
+        </is>
+      </c>
+      <c r="G94" s="1" t="inlineStr">
+        <is>
+          <t>YZXB</t>
+        </is>
+      </c>
+      <c r="H94" s="1" t="inlineStr">
+        <is>
+          <t>QZYB</t>
+        </is>
+      </c>
+      <c r="I94" s="1" t="inlineStr">
+        <is>
+          <t>YAYB</t>
+        </is>
+      </c>
+      <c r="J94" s="1" t="inlineStr"/>
+    </row>
+    <row r="95" ht="36" customHeight="1">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D95" s="1" t="inlineStr"/>
+      <c r="E95" s="1" t="inlineStr">
+        <is>
+          <t>If 24 July 1999 was Saturday, then what was the day of the week on 28 July 2003?</t>
+        </is>
+      </c>
+      <c r="F95" s="1" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="G95" s="1" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="H95" s="1" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="I95" s="1" t="inlineStr">
+        <is>
+          <t>Sunday
+^^ Download SSO C:GL,( :i dSL E-BOOKS ^—^</t>
+        </is>
+      </c>
+      <c r="J95" s="1" t="inlineStr"/>
+    </row>
+    <row r="96" ht="144" customHeight="1">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr"/>
+      <c r="E96" s="1" t="inlineStr">
+        <is>
+          <t>hi a certain language,
+A &amp; B means A is the wife of B,
+A t B means A is the daughter of B,
+A x B means A is the son of B,
+A + B means A is the sister of B and
+A @ B means A is the father of B.
+P&amp;Q@L+T&amp;U@V
+Based on the above, how is Q related to V?</t>
+        </is>
+      </c>
+      <c r="F96" s="1" t="inlineStr">
+        <is>
+          <t>Mother's father</t>
+        </is>
+      </c>
+      <c r="G96" s="1" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="H96" s="1" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="I96" s="1" t="inlineStr">
+        <is>
+          <t>Father's mother</t>
+        </is>
+      </c>
+      <c r="J96" s="1" t="inlineStr"/>
+    </row>
+    <row r="97" ht="54" customHeight="1">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr"/>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t>JHDC is related to KGEB in a certain way based on the English alphabetical order. In
+the same way, QOKJ is related to RNLI. To which of the following is USON related,
+following the same logic?</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t>VRQM</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t>VSQM</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t>VSPM</t>
+        </is>
+      </c>
+      <c r="I97" s="1" t="inlineStr"/>
+      <c r="J97" s="1" t="inlineStr"/>
+    </row>
+    <row r="98" ht="216" customHeight="1">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D98" s="1" t="inlineStr"/>
+      <c r="E98" s="1" t="inlineStr">
+        <is>
+          <t>In this question, three statements are given, followed by three conclusions numbered
+I, II and III. Assuming the statements to be true, even if they seem to be at variance
+with commonly known facts, decide which of the conclusion(s) logically follows/follow
+from the statements.
+Statements:
+All ladders are chairs.
+All chairs are tables.
+No table is a stair.
+Conclusions:
+I. Some tables are ladders.
+II. No chair is a stair.
+III. Some ladders are stairs.</t>
+        </is>
+      </c>
+      <c r="F98" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion III follows.</t>
+        </is>
+      </c>
+      <c r="G98" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows.</t>
+        </is>
+      </c>
+      <c r="H98" s="1" t="inlineStr">
+        <is>
+          <t>Both conclusions I and II follow.</t>
+        </is>
+      </c>
+      <c r="I98" s="1" t="inlineStr">
+        <is>
+          <t>Only conclusion II follows.</t>
+        </is>
+      </c>
+      <c r="J98" s="1" t="inlineStr"/>
+    </row>
+    <row r="99" ht="144" customHeight="1">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D99" s="1" t="inlineStr"/>
+      <c r="E99" s="1" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are related in the same way as are the numbers of
+the following sets.
+(NOTE: Operations should be performed on the whole numbers, without breaking
+down the numbers into their constituent digits. E.g. 13 – Operations on 13 such as
+adding/subtracting/multiplying etc. to 13 can be performed. Breaking down 13 into 1
+and 3 and then performing mathematical operations on 1 and 3 is not allowed.)
+(12, 4, 16)
+(27, 9, 36)</t>
+        </is>
+      </c>
+      <c r="F99" s="1" t="inlineStr">
+        <is>
+          <t>(39, 13, 52)</t>
+        </is>
+      </c>
+      <c r="G99" s="1" t="inlineStr">
+        <is>
+          <t>(37, 13, 52)</t>
+        </is>
+      </c>
+      <c r="H99" s="1" t="inlineStr">
+        <is>
+          <t>(39, 13, 54)</t>
+        </is>
+      </c>
+      <c r="I99" s="1" t="inlineStr">
+        <is>
+          <t>(39, 15, 52)</t>
+        </is>
+      </c>
+      <c r="J99" s="1" t="inlineStr"/>
+    </row>
+    <row r="100" ht="108" customHeight="1">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D100" s="1" t="inlineStr"/>
+      <c r="E100" s="1" t="inlineStr">
+        <is>
+          <t>Select the word-pair that best represents a similar relationship to the one expressed in
+the pair of words given below.
+(The words must be considered as meaningful English words and must not be related
+to each other based on the number of letters/number of consonants/vowels in the
+word.)
+Leaf : Oak</t>
+        </is>
+      </c>
+      <c r="F100" s="1" t="inlineStr">
+        <is>
+          <t>Needle : Pine</t>
+        </is>
+      </c>
+      <c r="G100" s="1" t="inlineStr">
+        <is>
+          <t>Tree : Forest</t>
+        </is>
+      </c>
+      <c r="H100" s="1" t="inlineStr">
+        <is>
+          <t>Berry : Fruit</t>
+        </is>
+      </c>
+      <c r="I100" s="1" t="inlineStr">
+        <is>
+          <t>Bulb : Tulip</t>
+        </is>
+      </c>
+      <c r="J100" s="1" t="inlineStr"/>
+    </row>
+    <row r="101" ht="54" customHeight="1">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D101" s="1" t="inlineStr"/>
+      <c r="E101" s="1" t="inlineStr">
+        <is>
+          <t>If ‘A’ stands for ’^-', -B‘ stands for ‘x’, ‘C’ stands for *+’ and ‘D’ stands for •-’, what will come in place of the question
+mark (?) in the following equation?
+62 B 2 D 190 A 5 C 7 = ?</t>
+        </is>
+      </c>
+      <c r="F101" s="1" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G101" s="1" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H101" s="1" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I101" s="1" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J101" s="1" t="inlineStr"/>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D102" s="1" t="inlineStr"/>
+      <c r="E102" s="1" t="inlineStr">
+        <is>
+          <t>What should come in place of the question mark (?) m the given series?
+66,</t>
+        </is>
+      </c>
+      <c r="F102" s="1" t="inlineStr">
+        <is>
+          <t>99, 132,</t>
+        </is>
+      </c>
+      <c r="G102" s="1" t="inlineStr">
+        <is>
+          <t>?</t>
+        </is>
+      </c>
+      <c r="H102" s="1" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="I102" s="1" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="J102" s="1" t="inlineStr"/>
+    </row>
+    <row r="103" ht="72" customHeight="1">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D103" s="1" t="inlineStr"/>
+      <c r="E103" s="1" t="inlineStr">
+        <is>
+          <t>Four letter-clusters have been given, out of which three are alike in some manner and
+one is different. Select the letter-cluster that is different.
+(Note: The odd one out is not based on the number of consonants/vowels or their
+position in the letter cluster)</t>
+        </is>
+      </c>
+      <c r="F103" s="1" t="inlineStr">
+        <is>
+          <t>PKRI</t>
+        </is>
+      </c>
+      <c r="G103" s="1" t="inlineStr">
+        <is>
+          <t>MNOL</t>
+        </is>
+      </c>
+      <c r="H103" s="1" t="inlineStr">
+        <is>
+          <t>AZCX</t>
+        </is>
+      </c>
+      <c r="I103" s="1" t="inlineStr">
+        <is>
+          <t>PLRI</t>
+        </is>
+      </c>
+      <c r="J103" s="1" t="inlineStr"/>
+    </row>
+    <row r="104" ht="54" customHeight="1">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D104" s="1" t="inlineStr"/>
+      <c r="E104" s="1" t="inlineStr">
+        <is>
+          <t>GJHK is related to IMKM in a certain way based on the English alphabetical order. In
+the same way, QTRU is related to SWUW. To which of the following is ILJM related,
+following the same logic?</t>
+        </is>
+      </c>
+      <c r="F104" s="1" t="inlineStr">
+        <is>
+          <t>KPNP</t>
+        </is>
+      </c>
+      <c r="G104" s="1" t="inlineStr">
+        <is>
+          <t>KOMO</t>
+        </is>
+      </c>
+      <c r="H104" s="1" t="inlineStr">
+        <is>
+          <t>KMON</t>
+        </is>
+      </c>
+      <c r="I104" s="1" t="inlineStr">
+        <is>
+          <t>KNMN</t>
+        </is>
+      </c>
+      <c r="J104" s="1" t="inlineStr"/>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr"/>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t>Select the correct mirror image of the given figtire when the mirror is placed at NIN as shown below.
+Dh57erk</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t>kisveha</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t>Mi 97 S ri Cl</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t>M J a V 2 ri a</t>
+        </is>
+      </c>
+      <c r="I105" s="1" t="inlineStr"/>
+      <c r="J105" s="1" t="inlineStr"/>
+    </row>
+    <row r="106" ht="54" customHeight="1">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D106" s="1" t="inlineStr"/>
+      <c r="E106" s="1" t="inlineStr">
+        <is>
+          <t>Study the given graph and answer the question that follows.
+The graph shows the marks obtained by Riya and Rida in six subjects in the CBSE
+12th exam. The maximum marks in Maths. Physics and Chemistry are</t>
+        </is>
+      </c>
+      <c r="F106" s="1" t="inlineStr">
+        <is>
+          <t>and that
+in English. IP and Biology are</t>
+        </is>
+      </c>
+      <c r="G106" s="1" t="inlineStr">
+        <is>
+          <t>M«tM PlryUCI OimwMry t^lU&gt; IP fbclogy
+What is the difference between the percentage of marks obtained by Riya and Rida
+in IP?</t>
+        </is>
+      </c>
+      <c r="H106" s="1" t="inlineStr">
+        <is>
+          <t>19 %</t>
+        </is>
+      </c>
+      <c r="I106" s="1" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="J106" s="1" t="inlineStr"/>
+    </row>
+    <row r="107" ht="72" customHeight="1">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D107" s="1" t="inlineStr"/>
+      <c r="E107" s="1" t="inlineStr">
+        <is>
+          <t>1 + cos 0 sin 0
+The value of I
+is equal to:
+.tan 0 + cot0</t>
+        </is>
+      </c>
+      <c r="F107" s="1" t="inlineStr">
+        <is>
+          <t>tan 0</t>
+        </is>
+      </c>
+      <c r="G107" s="1" t="inlineStr">
+        <is>
+          <t>2 sin 9</t>
+        </is>
+      </c>
+      <c r="H107" s="1" t="inlineStr">
+        <is>
+          <t>2 cos 0</t>
+        </is>
+      </c>
+      <c r="I107" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J107" s="1" t="inlineStr"/>
+    </row>
+    <row r="108" ht="360" customHeight="1">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr"/>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>The given table represents the percentage marks of three students in three subjects. Study the table and answer
+the question.
+subject
+Geography
+History
+Economics
+Student
+Rohan
+78
+77
+74
+Sohan
+84
+80
+82
+Mohan
+87
+S3
+86
+The average marks (to the nearest integer) obtained by the students in Histoiy and Economics (repectively) are:</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t>80 and 81</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t>78 and 80</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t>81 and 80</t>
+        </is>
+      </c>
+      <c r="I108" s="1" t="inlineStr">
+        <is>
+          <t>80 and 78</t>
+        </is>
+      </c>
+      <c r="J108" s="1" t="inlineStr"/>
+    </row>
+    <row r="109" ht="25" customHeight="1">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D109" s="1" t="inlineStr"/>
+      <c r="E109" s="1" t="inlineStr">
+        <is>
+          <t>A number increased by 20% gives</t>
+        </is>
+      </c>
+      <c r="F109" s="1" t="inlineStr">
+        <is>
+          <t>Find the number.</t>
+        </is>
+      </c>
+      <c r="G109" s="1" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H109" s="1" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="I109" s="1" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J109" s="1" t="inlineStr"/>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr"/>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t>By what percentage should a racer increase the speed to reduce the time by 25% to
+cover a fixed distance?</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t>33-%</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="I110" s="1" t="inlineStr">
+        <is>
+          <t>37-%</t>
+        </is>
+      </c>
+      <c r="J110" s="1" t="inlineStr"/>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr"/>
+      <c r="E111" s="1" t="inlineStr">
+        <is>
+          <t>If the number 6p5157q is divisible by 88, then p × q = ______ , where p and q are single
+digit numbers.</t>
+        </is>
+      </c>
+      <c r="F111" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G111" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H111" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I111" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J111" s="1" t="inlineStr"/>
+    </row>
+    <row r="112" ht="54" customHeight="1">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr"/>
+      <c r="E112" s="1" t="inlineStr">
+        <is>
+          <t>PQR is a triangle. MN is a line segment intersecting PQ in M and PR in N such that MN
+II QR and divides APQR into two parts, which are equal in area. What is the ratio of MQ
+to PQ?</t>
+        </is>
+      </c>
+      <c r="F112" s="1" t="inlineStr">
+        <is>
+          <t>1 : V2</t>
+        </is>
+      </c>
+      <c r="G112" s="1" t="inlineStr">
+        <is>
+          <t>V2 :1</t>
+        </is>
+      </c>
+      <c r="H112" s="1" t="inlineStr">
+        <is>
+          <t>(V 2 — 1) : V 2</t>
+        </is>
+      </c>
+      <c r="I112" s="1" t="inlineStr"/>
+      <c r="J112" s="1" t="inlineStr"/>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D113" s="1" t="inlineStr"/>
+      <c r="E113" s="1" t="inlineStr">
+        <is>
+          <t>From a circle of radius r units, the largest equilateral triangle is cut out. What is the
+length (in units) of the side of the triangle?</t>
+        </is>
+      </c>
+      <c r="F113" s="1" t="inlineStr">
+        <is>
+          <t>V2r</t>
+        </is>
+      </c>
+      <c r="G113" s="1" t="inlineStr">
+        <is>
+          <t>V3r</t>
+        </is>
+      </c>
+      <c r="H113" s="1" t="inlineStr"/>
+      <c r="I113" s="1" t="inlineStr"/>
+      <c r="J113" s="1" t="inlineStr"/>
+    </row>
+    <row r="114" ht="36" customHeight="1">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D114" s="1" t="inlineStr"/>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>Find the altitude (in cm) from the vertex Q to side PR of triangle PQR with side lengths
+PQ = 40 cm, PR = 40 cm and QR = 60 cm.</t>
+        </is>
+      </c>
+      <c r="F114" s="1" t="inlineStr">
+        <is>
+          <t>25V7</t>
+        </is>
+      </c>
+      <c r="G114" s="1" t="inlineStr">
+        <is>
+          <t>20V7</t>
+        </is>
+      </c>
+      <c r="H114" s="1" t="inlineStr">
+        <is>
+          <t>15^7</t>
+        </is>
+      </c>
+      <c r="I114" s="1" t="inlineStr">
+        <is>
+          <t>30v'7</t>
+        </is>
+      </c>
+      <c r="J114" s="1" t="inlineStr"/>
+    </row>
+    <row r="115" ht="25" customHeight="1">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D115" s="1" t="inlineStr"/>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>A shopkeeper sells goods at 40% loss on cost price but uses 25% less weight. What is his percentage profit or loss?</t>
+        </is>
+      </c>
+      <c r="F115" s="1" t="inlineStr">
+        <is>
+          <t>Loss. 10%</t>
+        </is>
+      </c>
+      <c r="G115" s="1" t="inlineStr">
+        <is>
+          <t>Profit. 10%</t>
+        </is>
+      </c>
+      <c r="H115" s="1" t="inlineStr">
+        <is>
+          <t>Loss, 20%</t>
+        </is>
+      </c>
+      <c r="I115" s="1" t="inlineStr">
+        <is>
+          <t>Profit. 20%</t>
+        </is>
+      </c>
+      <c r="J115" s="1" t="inlineStr"/>
+    </row>
+    <row r="116" ht="25" customHeight="1">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D116" s="1" t="inlineStr"/>
+      <c r="E116" s="1" t="inlineStr">
+        <is>
+          <t>Which Commission drew the boundary line between India and Pakistan?</t>
+        </is>
+      </c>
+      <c r="F116" s="1" t="inlineStr">
+        <is>
+          <t>Radcliffe Boundary Commission</t>
+        </is>
+      </c>
+      <c r="G116" s="1" t="inlineStr">
+        <is>
+          <t>Gandhi Irwin Pact</t>
+        </is>
+      </c>
+      <c r="H116" s="1" t="inlineStr">
+        <is>
+          <t>Hilton Young Commission</t>
+        </is>
+      </c>
+      <c r="I116" s="1" t="inlineStr">
+        <is>
+          <t>Bretton woods Commission</t>
+        </is>
+      </c>
+      <c r="J116" s="1" t="inlineStr"/>
+    </row>
+    <row r="117" ht="25" customHeight="1">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr"/>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t>Which Indian festival is a festival of lights?</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t>Bihu</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t>Holi</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t>Onam</t>
+        </is>
+      </c>
+      <c r="I117" s="1" t="inlineStr">
+        <is>
+          <t>Diwali</t>
+        </is>
+      </c>
+      <c r="J117" s="1" t="inlineStr"/>
+    </row>
+    <row r="118" ht="54" customHeight="1">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr"/>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t>What is/are the objective(s) of Fiscal Policy?
+1) Boost growth
+2) Control inflation</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t>Both 1 and 2</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t>Only 2</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t>Only 1</t>
+        </is>
+      </c>
+      <c r="I118" s="1" t="inlineStr">
+        <is>
+          <t>Neither 1 nor 2</t>
+        </is>
+      </c>
+      <c r="J118" s="1" t="inlineStr"/>
+    </row>
+    <row r="119" ht="36" customHeight="1">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr"/>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following statements most accurately describes the Cyclostomata
+group?</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t>Their skin is covered with scales/plates and their hearts have only two chambers.</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t>They are ectothermic animals having mucus glands in the skin, and a three­
+chambered heart.</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t>They are warm-blooded, oviparous, bipedal, feathered, winged and toothless
+vertebrates.</t>
+        </is>
+      </c>
+      <c r="I119" s="1" t="inlineStr">
+        <is>
+          <t>They are characterised by having an elongated eel-like body, circular mouth, slimy
+skin and are scaleless.</t>
+        </is>
+      </c>
+      <c r="J119" s="1" t="inlineStr"/>
+    </row>
+    <row r="120" ht="25" customHeight="1">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr"/>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>In Microsoft Office, how is the font size determined?</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t>Pixels</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t>Points</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t>Inches</t>
+        </is>
+      </c>
+      <c r="I120" s="1" t="inlineStr">
+        <is>
+          <t>Centimetres</t>
+        </is>
+      </c>
+      <c r="J120" s="1" t="inlineStr"/>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr"/>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>The Parliament of India has passed the 86th Constitutional Amendment Act 2002,
+which establishes the basic rights of primary education for children between:</t>
+        </is>
+      </c>
+      <c r="F121" s="1" t="inlineStr">
+        <is>
+          <t>6-14 Years</t>
+        </is>
+      </c>
+      <c r="G121" s="1" t="inlineStr">
+        <is>
+          <t>7-16 Years</t>
+        </is>
+      </c>
+      <c r="H121" s="1" t="inlineStr">
+        <is>
+          <t>5-11 years</t>
+        </is>
+      </c>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t>6-17 Years</t>
+        </is>
+      </c>
+      <c r="J121" s="1" t="inlineStr"/>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B122" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr"/>
+      <c r="E122" s="1" t="inlineStr">
+        <is>
+          <t>__________ was named as the new Shiv Sena president at the party national executive</t>
+        </is>
+      </c>
+      <c r="F122" s="1" t="inlineStr">
+        <is>
+          <t>Eknath Shinde
+meeting in Mumbai in</t>
+        </is>
+      </c>
+      <c r="G122" s="1" t="inlineStr">
+        <is>
+          <t>Narayan Rane</t>
+        </is>
+      </c>
+      <c r="H122" s="1" t="inlineStr">
+        <is>
+          <t>Rahul Ramesh Shewale</t>
+        </is>
+      </c>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t>Aditya Uddhav Thackeray</t>
+        </is>
+      </c>
+      <c r="J122" s="1" t="inlineStr"/>
+    </row>
+    <row r="123" ht="25" customHeight="1">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B123" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D123" s="1" t="inlineStr"/>
+      <c r="E123" s="1" t="inlineStr">
+        <is>
+          <t>The famous folk music of Rajasthan that was developed in royal courts is known as:</t>
+        </is>
+      </c>
+      <c r="F123" s="1" t="inlineStr">
+        <is>
+          <t>Maand</t>
+        </is>
+      </c>
+      <c r="G123" s="1" t="inlineStr">
+        <is>
+          <t>Lavani</t>
+        </is>
+      </c>
+      <c r="H123" s="1" t="inlineStr">
+        <is>
+          <t>Sohar</t>
+        </is>
+      </c>
+      <c r="I123" s="1" t="inlineStr">
+        <is>
+          <t>Dandiya</t>
+        </is>
+      </c>
+      <c r="J123" s="1" t="inlineStr"/>
+    </row>
+    <row r="124" ht="25" customHeight="1">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B124" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D124" s="1" t="inlineStr"/>
+      <c r="E124" s="1" t="inlineStr">
+        <is>
+          <t>Where did India win its last Olympic medal in men’s hockey? (As of March, 2024).</t>
+        </is>
+      </c>
+      <c r="F124" s="1" t="inlineStr">
+        <is>
+          <t>Rio</t>
+        </is>
+      </c>
+      <c r="G124" s="1" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="H124" s="1" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="I124" s="1" t="inlineStr">
+        <is>
+          <t>Mexico City</t>
+        </is>
+      </c>
+      <c r="J124" s="1" t="inlineStr"/>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B125" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D125" s="1" t="inlineStr"/>
+      <c r="E125" s="1" t="inlineStr">
+        <is>
+          <t>Delhi ridge is the water divide between which of the following rivers?</t>
+        </is>
+      </c>
+      <c r="F125" s="1" t="inlineStr">
+        <is>
+          <t>Ganges and Sind</t>
+        </is>
+      </c>
+      <c r="G125" s="1" t="inlineStr">
+        <is>
+          <t>Indus and Mahi</t>
+        </is>
+      </c>
+      <c r="H125" s="1" t="inlineStr">
+        <is>
+          <t>Ganges and Indus</t>
+        </is>
+      </c>
+      <c r="I125" s="1" t="inlineStr">
+        <is>
+          <t>Ganges and Yamuna
+In which Gharana do singers perform the Khandhar Vani and Gauhar Vani?</t>
+        </is>
+      </c>
+      <c r="J125" s="1" t="inlineStr"/>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B126" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D126" s="1" t="inlineStr"/>
+      <c r="E126" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following isotopes is used as a fuel in nuclear power plants for
+generating electricity?</t>
+        </is>
+      </c>
+      <c r="F126" s="1" t="inlineStr">
+        <is>
+          <t>Arsenic-74</t>
+        </is>
+      </c>
+      <c r="G126" s="1" t="inlineStr">
+        <is>
+          <t>Carbon-14</t>
+        </is>
+      </c>
+      <c r="H126" s="1" t="inlineStr">
+        <is>
+          <t>Uranium- 235</t>
+        </is>
+      </c>
+      <c r="I126" s="1" t="inlineStr">
+        <is>
+          <t>Sodium-24</t>
+        </is>
+      </c>
+      <c r="J126" s="1" t="inlineStr"/>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B127" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D127" s="1" t="inlineStr"/>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>Most major sports awards are accompanied by a cash reward. Which of the following
+is the only national sports award that does NOT include a cash reward?</t>
+        </is>
+      </c>
+      <c r="F127" s="1" t="inlineStr">
+        <is>
+          <t>Major Dhyan Chand Khel Ratna</t>
+        </is>
+      </c>
+      <c r="G127" s="1" t="inlineStr">
+        <is>
+          <t>Rashtriya Khel Protsahan Puruskar</t>
+        </is>
+      </c>
+      <c r="H127" s="1" t="inlineStr">
+        <is>
+          <t>Maulana Abul Kalam Azad Trophy</t>
+        </is>
+      </c>
+      <c r="I127" s="1" t="inlineStr">
+        <is>
+          <t>Dronacharya Award</t>
+        </is>
+      </c>
+      <c r="J127" s="1" t="inlineStr"/>
+    </row>
+    <row r="128" ht="36" customHeight="1">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr"/>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following statements about planet Saturn is true?</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t>Saturn is the fourth planet from the Sun and the largest planet in our solar system.</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t>Satellites like Enceladus and Titan of Saturn are home to internal oceans, could
+possibly support life.</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t>Saturn's environment is conducive to life.</t>
+        </is>
+      </c>
+      <c r="I128" s="1" t="inlineStr">
+        <is>
+          <t>Saturn is a massive ball made up mostly of nitrogen.</t>
+        </is>
+      </c>
+      <c r="J128" s="1" t="inlineStr"/>
+    </row>
+    <row r="129" ht="36" customHeight="1">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr"/>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t>The Lucknow Gharana of Kathak was founded by ___________ , a devotee of the
+Bhakti movement who lived in southeast Uttar Pradesh.</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t>Ram Kumar</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t>Bhagwan Ram</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t>Ishwari Prasad</t>
+        </is>
+      </c>
+      <c r="I129" s="1" t="inlineStr">
+        <is>
+          <t>Shyam Kumar</t>
+        </is>
+      </c>
+      <c r="J129" s="1" t="inlineStr"/>
+    </row>
+    <row r="130" ht="25" customHeight="1">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B130" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D130" s="1" t="inlineStr"/>
+      <c r="E130" s="1" t="inlineStr">
+        <is>
+          <t>Articles 344 (1) and 351 of the Constitution of India are related to the:</t>
+        </is>
+      </c>
+      <c r="F130" s="1" t="inlineStr">
+        <is>
+          <t>Eighth Schedule</t>
+        </is>
+      </c>
+      <c r="G130" s="1" t="inlineStr">
+        <is>
+          <t>Third Schedule</t>
+        </is>
+      </c>
+      <c r="H130" s="1" t="inlineStr">
+        <is>
+          <t>Sixth Schedule</t>
+        </is>
+      </c>
+      <c r="I130" s="1" t="inlineStr">
+        <is>
+          <t>Fifth Schedule</t>
+        </is>
+      </c>
+      <c r="J130" s="1" t="inlineStr"/>
+    </row>
+    <row r="131" ht="90" customHeight="1">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr"/>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t>Match the states in column A with their official languages in column B.
+Column A
+Column B
+(Official Languages)
+(States)</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh
+a. Malayalam</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t>Kerala
+b. Telugu</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t>Karnataka
+c. Konkani</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t>Goa
+d. Kannada</t>
+        </is>
+      </c>
+      <c r="J131" s="1" t="inlineStr"/>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr"/>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t>The Fundamental Duties of Citizens were introduced by the 42nd Amendment in the
+year:</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t>1978</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="J132" s="1" t="inlineStr"/>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B133" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D133" s="1" t="inlineStr"/>
+      <c r="E133" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following statement/(s) is /are true with respect to Supreme Court
+Observation in A.G. Perarivalan vs The State Of Tamil Nadu State?</t>
+        </is>
+      </c>
+      <c r="F133" s="1" t="inlineStr">
+        <is>
+          <t>It highlighted that the Governor’s powers are qualified by the constitutional
+mandate, chiefly requiring them to act in aid and advice of the council of ministers</t>
+        </is>
+      </c>
+      <c r="G133" s="1" t="inlineStr">
+        <is>
+          <t>The bench headed by justice L Nageswara Rao ordered the freedom of one of the
+convicts in the Rajiv Gandhi assassination case.</t>
+        </is>
+      </c>
+      <c r="H133" s="1" t="inlineStr">
+        <is>
+          <t>The bench was of the opinion that there are three sources of power-Governor,
+Council of Ministers and the Constitution.</t>
+        </is>
+      </c>
+      <c r="I133" s="1" t="inlineStr">
+        <is>
+          <t>Both 1 and 2</t>
+        </is>
+      </c>
+      <c r="J133" s="1" t="inlineStr"/>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B134" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr"/>
+      <c r="E134" s="1" t="inlineStr">
+        <is>
+          <t>On 11 August 2021, the General Insurance Business (Nationalisation) Amendment Bill,
+2021 was passed by the Parliament and it amended the _____ .</t>
+        </is>
+      </c>
+      <c r="F134" s="1" t="inlineStr">
+        <is>
+          <t>Motor Insurance (Nationalisation) Act, 1980</t>
+        </is>
+      </c>
+      <c r="G134" s="1" t="inlineStr">
+        <is>
+          <t>General Insurance Business (Nationalisation) Act, 1972</t>
+        </is>
+      </c>
+      <c r="H134" s="1" t="inlineStr">
+        <is>
+          <t>General Business (Nationalisation) Act, 1970</t>
+        </is>
+      </c>
+      <c r="I134" s="1" t="inlineStr">
+        <is>
+          <t>Life Insurance (Nationalisation) Act, 1975</t>
+        </is>
+      </c>
+      <c r="J134" s="1" t="inlineStr"/>
+    </row>
+    <row r="135" ht="25" customHeight="1">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B135" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D135" s="1" t="inlineStr"/>
+      <c r="E135" s="1" t="inlineStr">
+        <is>
+          <t>Which of the following is NOT the colour of a warning card in kabaddi?</t>
+        </is>
+      </c>
+      <c r="F135" s="1" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
+      <c r="G135" s="1" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="H135" s="1" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
+      <c r="J135" s="1" t="inlineStr"/>
+    </row>
+    <row r="136" ht="25" customHeight="1">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B136" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D136" s="1" t="inlineStr"/>
+      <c r="E136" s="1" t="inlineStr">
+        <is>
+          <t>The Howrah bridge was officially opened in the year _______ .</t>
+        </is>
+      </c>
+      <c r="F136" s="1" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="G136" s="1" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="H136" s="1" t="inlineStr">
+        <is>
+          <t>1948</t>
+        </is>
+      </c>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t>1943</t>
+        </is>
+      </c>
+      <c r="J136" s="1" t="inlineStr"/>
+    </row>
+    <row r="137" ht="36" customHeight="1">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B137" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr"/>
+      <c r="E137" s="1" t="inlineStr">
+        <is>
+          <t>The slide number can be added to each slide of the MS PowerPoint presentation from
+which of the following?</t>
+        </is>
+      </c>
+      <c r="F137" s="1" t="inlineStr">
+        <is>
+          <t>Footer</t>
+        </is>
+      </c>
+      <c r="G137" s="1" t="inlineStr">
+        <is>
+          <t>Page Formatting</t>
+        </is>
+      </c>
+      <c r="H137" s="1" t="inlineStr">
+        <is>
+          <t>View</t>
+        </is>
+      </c>
+      <c r="I137" s="1" t="inlineStr">
+        <is>
+          <t>Table Design
+'^^ Download SSO C:gi L-.Ch1SL E-BOOKS hau^</t>
+        </is>
+      </c>
+      <c r="J137" s="1" t="inlineStr"/>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B138" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr">
+        <is>
+          <t>Which Mughal ruler was responsible for the execution of Guru Tegh Bahadur in the
+year 1675?</t>
+        </is>
+      </c>
+      <c r="F138" s="1" t="inlineStr">
+        <is>
+          <t>Jahangir</t>
+        </is>
+      </c>
+      <c r="G138" s="1" t="inlineStr">
+        <is>
+          <t>Akbar</t>
+        </is>
+      </c>
+      <c r="H138" s="1" t="inlineStr">
+        <is>
+          <t>Aurangzeb</t>
+        </is>
+      </c>
+      <c r="I138" s="1" t="inlineStr">
+        <is>
+          <t>Shahjahan</t>
+        </is>
+      </c>
+      <c r="J138" s="1" t="inlineStr"/>
+    </row>
+    <row r="139" ht="36" customHeight="1">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr"/>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t>In which year did Swami Vivekananda give his speech at the Chicago Parliament of
+Religions?</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t>1892</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t>1891</t>
+        </is>
+      </c>
+      <c r="I139" s="1" t="inlineStr">
+        <is>
+          <t>1890
+'^^ Download SSO C Page L 23 of 23 1SL E-BOOKS ^—&lt;&lt;</t>
+        </is>
+      </c>
+      <c r="J139" s="1" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -1354,7 +1354,11 @@
           <t>Botany</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Botany</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -1409,7 +1413,11 @@
           <t>E</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1465,7 +1473,11 @@
           <t>5, 3, 1, 2, 4</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5, 1, 3, 2, 4</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1523,7 +1535,11 @@
           <t>Only conclusion I follows.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Both conclusions I and II follows.</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
@@ -1574,7 +1590,11 @@
           <t>XMLCA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>XLLDA</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
@@ -1625,7 +1645,11 @@
           <t>Daughter</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
@@ -1679,7 +1703,11 @@
           <t>Only conclusion I is true</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Only conclusion I is true</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
@@ -1730,7 +1758,11 @@
           <t>3267</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -1782,7 +1814,11 @@
           <t>J A M M Q A B J</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>J Q B J A M Q A</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
@@ -1834,7 +1870,11 @@
           <t>South</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>West</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
@@ -1885,7 +1925,11 @@
           <t>42</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1937,7 +1981,11 @@
           <t>LXV</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>LXV</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr"/>
@@ -1988,7 +2036,11 @@
           <t>UBYQ</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>UBYQ</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -2044,7 +2096,11 @@
           <t>(337, 311, 18)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>(337, 311, 18)</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr"/>
@@ -2105,7 +2161,11 @@
           <t>Only conclusion II follows</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Only conclusion I and II follow</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
@@ -2156,7 +2216,11 @@
           <t>554</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -2207,7 +2271,11 @@
           <t>FIUR</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>ADZE</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
@@ -2264,7 +2332,11 @@
           <t>(292, 122, 160)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>(182, 74, 108)</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
@@ -2316,7 +2388,11 @@
           <t>+, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>+, ÷, −, ×, =</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
@@ -2367,7 +2443,11 @@
           <t>TWQ</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>DIB</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
@@ -2428,7 +2508,11 @@
           <t>Only conclusion I follows</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Only conclusion III follows</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
@@ -2484,7 +2568,11 @@
           <t>(18, 13, 493)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>(12, 15, 367)</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
@@ -2537,7 +2625,11 @@
           <t>North-west</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>South-east</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
@@ -2593,7 +2685,11 @@
           <t>(13, 162, 331)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>(13, 162, 331)</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
@@ -2645,7 +2741,11 @@
           <t>2 and 9</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2 and 3</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
@@ -2698,7 +2798,11 @@
           <t>128</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
@@ -2750,7 +2854,11 @@
           <t>124</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -2803,7 +2911,11 @@
           <t>MLYFIS</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>MILFYS</t>
+        </is>
+      </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr"/>
@@ -2854,7 +2966,11 @@
           <t>97</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
@@ -2907,7 +3023,11 @@
           <t>Third to the right of D</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Fourth to the right of F</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr"/>
@@ -2964,7 +3084,11 @@
           <t>(90,	85,	104)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>(95,	85,	104)</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -3017,7 +3141,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
@@ -3068,7 +3196,11 @@
           <t>75</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
@@ -3126,7 +3258,11 @@
           <t>16</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
@@ -3177,7 +3313,12 @@
           <t>78</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>How will
+'GARIMA' be coded in the same language?</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
@@ -3229,7 +3370,11 @@
           <t>+ and −</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>+ and −</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
@@ -3290,7 +3435,11 @@
           <t>Only conclusions I and II follow</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Only conclusions II and III follow</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
@@ -3342,7 +3491,11 @@
           <t>× and −</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>× and ÷</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
@@ -3393,7 +3546,11 @@
           <t>France</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
@@ -3442,7 +3599,11 @@
         <f>, ÷, +, −, ×</f>
         <v/>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>÷, +, −, =, ×</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -3492,7 +3653,11 @@
           <t>Monday</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
@@ -3546,7 +3711,11 @@
           <t>A is the daughter of E’s son.</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>B is sister of E’s son.</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
@@ -3811,7 +3980,12 @@
           <t>YAYB</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>QXZC
+in the given code language?</t>
+        </is>
+      </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
@@ -3919,7 +4093,11 @@
           <t>Father's mother</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Mother's father</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
@@ -4085,7 +4263,11 @@
           <t>(39, 15, 52)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>(39, 13, 52)</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
@@ -4550,7 +4732,12 @@
           <t>Aditya Uddhav Thackeray</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Eknath Shinde
+meeting in Mumbai in</t>
+        </is>
+      </c>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
@@ -4600,7 +4787,11 @@
           <t>Dandiya</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Maand</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr"/>
@@ -4855,7 +5046,11 @@
 '^^ Download SSO C Page L 23 of 23 1SL E-BOOKS ^—&lt;&lt;</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>

--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Extraction Report" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +26,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+        <bgColor rgb="00D9EAF7"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +56,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,104 +424,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="22" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="37" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Exam Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Page Number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Question Number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Question Image</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>AI Answer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Reasoning Type</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Regex Topic</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>LLM Topic</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Solution</t>
         </is>
@@ -536,42 +541,41 @@
 Who sits at the rightmost end of the line?</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -593,42 +597,41 @@
 Following the same pattern, if D is related to May, and B is related to February, then to which month is F related?</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Feburuary</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Feburuary</t>
+          <t>August</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>August</t>
+          <t>October</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>April</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>October</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Month Based Puzzle</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,42 +654,41 @@
 Conclusions (II) : Some fruits are trees</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Only conclusion (I) follows</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Only conclusion (I) follows</t>
+          <t>Only conclusion (II) follows</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>Neither conclusion (I) nor (II) follows</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Both conclusions (I) and (II) follow</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Only conclusion (II) follows</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Neither conclusion (I) nor (II) follows</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Both conclusions (I) and (II) follow</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Only conclusion (II) follows</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -710,42 +712,41 @@
 Based on the above, how is R related to O if ‘R+A%C@K#O ’?</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Wife's sister</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>Wife's mother</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Wife's sister</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Wife's mother</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Wife's sister</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -769,42 +770,41 @@
 II. G &lt; E</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Only I is true</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Only I is true</t>
+          <t>Only II is true</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Both I and II are true</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Neither I nor II is true</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Only II is true</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Both I and II are true</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Neither I nor II is true</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Only II is true</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Mathematical Inequality (Direct)</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -825,42 +825,41 @@
 How many people have scored more than S?</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>One</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Two</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Three</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Four</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>One</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Ranking (Marks / Score)</t>
         </is>
       </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -880,42 +879,41 @@
 DER121  , YZM129  , TUH137   , OPC145   , ?</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>JKX153</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>JKX152</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>JLX153</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>JZX153</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>JKX153</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>JKX152</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>JLX153</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>JZX153</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>JKX153</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -936,42 +934,41 @@
 How many such letters are there each of which is immediately preceded by a symbol and also immediately followed by a letter?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>Three</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Four</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Three</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -993,42 +990,41 @@
 How many such symbols are there each of which is immediately preceded by a letter and also immediately followed by a number?</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>One</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Two</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Three</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Four</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>One</t>
-        </is>
-      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1052,42 +1048,41 @@
 What is the code for 'and'?</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>fb</t>
+          <t>cb</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>cb</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>in</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>tc</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>cb</t>
-        </is>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1107,42 +1102,41 @@
 language?</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1164,42 +1158,41 @@
 KIND - NKID - DNIK</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>HOTS - THOS - STOH</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>CARD - CRAD - DRAC</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>MIND - IMND - DINM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>SHOP - OSHP - HOPS</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>HOTS - THOS - STOH</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>CARD - CRAD - DRAC</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>MIND - IMND - DINM</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>SHOP - OSHP - HOPS</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>HOTS - THOS - STOH</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1220,42 +1213,41 @@
 (Note: The odd one out is not based on the number of consonants/vowels or their position in the letter cluster)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>MRO</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>INS</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>NSX</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>DIN</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
           <t>MRO</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>INS</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>NSX</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>DIN</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>MRO</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Word Classification</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1275,42 +1267,41 @@
 as these have the same relationship and thus form a group. Which word pair is the one that does not belong to that group?</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Below-Above</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>Select-Choose</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Trip-Journey</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Good-Fine</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>Below-Above</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Select-Choose</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Trip-Journey</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Good-Fine</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Below-Above</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1333,20 +1324,24 @@
 Animal : Zoology :: Plant : ?</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Geology</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Geology</t>
+          <t>Palaeontology</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Palaeontology</t>
+          <t>Biology</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Biology</t>
+          <t>Botany</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1354,21 +1349,16 @@
           <t>Botany</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Botany</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1392,42 +1382,41 @@
 is sitting to the left of F. Who is sitting between A and D?</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>F</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>H</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1452,42 +1441,41 @@
 5 Sadly</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>3, 5, 1, 2, 4</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3, 5, 1, 2, 4</t>
+          <t>5, 1, 3, 2, 4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>5, 1, 3, 4, 2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>5, 3, 1, 2, 4</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>5, 1, 3, 2, 4</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>5, 1, 3, 4, 2</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5, 3, 1, 2, 4</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>5, 1, 3, 2, 4</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1514,42 +1502,41 @@
 II. No jeep is a bus.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Only conclusion II follows.</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Only conclusion II follows.</t>
+          <t>Neither conclusion I nor II follows.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neither conclusion I nor II follows.</t>
+          <t>Both conclusions I and II follows.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>Only conclusion I follows.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>Both conclusions I and II follows.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Only conclusion I follows.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Both conclusions I and II follows.</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1569,42 +1556,41 @@
 How will 'VIJAY' be coded in the same language?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>XKLCB</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>XKLCB</t>
+          <t>XLLDA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
+          <t>XLMDA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>XMLCA</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>XLLDA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>XLMDA</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>XMLCA</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>XLLDA</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1624,42 +1610,41 @@
 daughter.” How is that girl related to Seema?</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mother’s sister</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mother’s sister</t>
+          <t>Sister</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Daughter</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Daughter</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1682,20 +1667,24 @@
 II. C &lt; F</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Neither conclusion I nor II is true</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Neither conclusion I nor II is true</t>
+          <t>Both conclusions I and II are true</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Both conclusions I and II are true</t>
+          <t>Only conclusion II is true</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Only conclusion II is true</t>
+          <t>Only conclusion I is true</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1703,21 +1692,16 @@
           <t>Only conclusion I is true</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Only conclusion I is true</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Mathematical Inequality (Direct)</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1737,42 +1721,41 @@
 3, 7, 5, 61, 363 ?</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
+          <t>3348</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>3630</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
           <t>3367</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>3348</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>3630</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>3367</t>
-        </is>
-      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1793,42 +1776,41 @@
 _ M _ B A J M Q _ A _ M Q B _ J _ _ B _</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>J Q B J A M Q A</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
+          <t>B Q A J M Q A B</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>A M B Q J M J Q</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>J A M M Q A B J</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>J Q B J A M Q A</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>B Q A J M Q A B</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>A M B Q J M J Q</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>J A M M Q A B J</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>J Q B J A M Q A</t>
-        </is>
-      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Letter Series</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1849,42 +1831,41 @@
 position of town A with respect to town B?</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>East</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>West</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>West</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>North</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>South</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>West</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1904,42 +1885,41 @@
 'MAP' be coded in that language?</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1960,20 +1940,24 @@
 FRP, HTR, JVT, ?, NZX</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>IWV</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IWV</t>
+          <t>KWU</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>KWU</t>
+          <t>IUS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>IUS</t>
+          <t>LXV</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1981,21 +1965,16 @@
           <t>LXV</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>LXV</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2015,20 +1994,24 @@
 GROW, NJGG, ?, BTQA, ILIK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>YDER</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>YDER</t>
+          <t>VIWQ</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>VIWQ</t>
+          <t>PSJW</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>PSJW</t>
+          <t>UBYQ</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2036,21 +2019,16 @@
           <t>UBYQ</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>UBYQ</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2075,20 +2053,24 @@
 (238, 212, 15)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>(370, 348, 19)</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>(370, 348, 19)</t>
+          <t>(336, 302, 17)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>(336, 302, 17)</t>
+          <t>(142, 126, 11)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(142, 126, 11)</t>
+          <t>(337, 311, 18)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2096,21 +2078,16 @@
           <t>(337, 311, 18)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>(337, 311, 18)</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2140,42 +2117,41 @@
 III. No trojan is a virus.</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Only conclusion I follows</t>
+          <t>Only conclusion I and III follow</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Only conclusion I and III follow</t>
+          <t>Only conclusion I and II follow</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Only conclusion II follows</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>Only conclusion I and II follow</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Only conclusion II follows</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Only conclusion I and II follow</t>
-        </is>
-      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2195,42 +2171,41 @@
 420, 462, 506, ?, 600, 650, 702</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>552</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
+          <t>562</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>554</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>552</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>562</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>554</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2250,42 +2225,41 @@
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TWGD</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TWGD</t>
+          <t>ADZE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
+          <t>PSKH</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>FIUR</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>ADZE</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>PSKH</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>FIUR</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ADZE</t>
-        </is>
-      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Word Classification</t>
         </is>
       </c>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2311,42 +2285,41 @@
 (256, 123, 133)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>(182, 74, 108)</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
+          <t>(240, 105, 110)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>(196, 89, 91)</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(292, 122, 160)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>(182, 74, 108)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>(240, 105, 110)</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(196, 89, 91)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>(292, 122, 160)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>(182, 74, 108)</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2367,20 +2340,24 @@
 65	*	56	*	8	*	19	*	2	*	34</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>−, ÷, −, ×, =</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>−, ÷, −, ×, =</t>
+          <t>+, +, −, ×, =</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+, +, −, ×, =</t>
+          <t>+, ×, −, ×, =</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>+, ×, −, ×, =</t>
+          <t>+, ÷, −, ×, =</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2388,21 +2365,16 @@
           <t>+, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>+, ÷, −, ×, =</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2422,42 +2394,41 @@
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>MPJ</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>MPJ</t>
+          <t>DIB</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>HKE</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TWQ</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>DIB</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>HKE</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>TWQ</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>DIB</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Word Classification</t>
         </is>
       </c>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2487,42 +2458,41 @@
 III. Some nails are pendants.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Only conclusions II and III follow</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Only conclusions II and III follow</t>
+          <t>Only conclusion III follows</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
+          <t>Only conclusions I and II follow</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>Only conclusion III follows</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Only conclusions I and II follow</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Only conclusion I follows</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Only conclusion III follows</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2547,42 +2517,41 @@
 (16, 11, 377)</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>(12, 15, 367)</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>(16, 14, 452)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>(14, 12, 340)</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(18, 13, 493)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>(12, 15, 367)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>(16, 14, 452)</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(14, 12, 340)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>(18, 13, 493)</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>(12, 15, 367)</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2604,42 +2573,41 @@
 Town M?</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>East</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>East</t>
+          <t>South-east</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
+          <t>North-west</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
           <t>South-east</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>North-west</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>South-east</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2664,20 +2632,24 @@
 (14, 104, 300)</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>(15, 175, 390)</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>(15, 175, 390)</t>
+          <t>(17, 131, 410)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>(17, 131, 410)</t>
+          <t>(19, 121, 445)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(19, 121, 445)</t>
+          <t>(13, 162, 331)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2685,21 +2657,16 @@
           <t>(13, 162, 331)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>(13, 162, 331)</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2720,42 +2687,41 @@
 (357 ÷ 2 + 3) ÷ 11 − 4 = (28 × 3 + 7) ÷ 9</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>11 and 28</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11 and 28</t>
+          <t>2 and 3</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
+          <t>7 and 9</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2 and 9</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>2 and 3</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>7 and 9</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>2 and 9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2 and 3</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2777,42 +2743,41 @@
 6 : 43 :: 11 : ? :: 4 : 21</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>133</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2833,42 +2798,41 @@
 16 : 50 :: 49 : ? :: 144 : 338</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
       <c r="F42" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2890,42 +2854,41 @@
 MASTER : TSAMRE :: SMILES : LIMSSE :: FLIMSY : ?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>FLIMYS</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FLIMYS</t>
+          <t>FILMYS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>FILMYS</t>
+          <t>MILFYS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
+          <t>MLYFIS</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
           <t>MILFYS</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>MLYFIS</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>MILFYS</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2945,42 +2908,41 @@
 144, 127, 110, ?, 76, 59</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3002,42 +2964,41 @@
 the immediate left of A, and E is second to the right of A, where will B sit?</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Fourth to the right of F</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Fifth to the right of G</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>To the immediate right of E</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Third to the right of D</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Fourth to the right of F</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Fifth to the right of G</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>To the immediate right of E</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Third to the right of D</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Fourth to the right of F</t>
-        </is>
-      </c>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3063,42 +3024,41 @@
 (65, 55, 68)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(95,	85,	124)</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>(95,	85,	124)</t>
+          <t>(95,	85,	104)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
+          <t>(95,	80,	104)</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(90,	85,	104)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>(95,	85,	104)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>(95,	80,	104)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>(90,	85,	104)</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>(95,	85,	104)</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3120,20 +3080,24 @@
 many people is between I and N?</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3141,21 +3105,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Year/Age Puzzle</t>
         </is>
       </c>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3175,42 +3134,41 @@
 How will 'SECURE' be coded in that language?</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>71</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3237,42 +3195,41 @@
 3 and then performing mathematical operations on 1 and 3 is not allowed)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3291,44 +3248,43 @@
           <t>In a code language, 'AMIT' is coded as 86 and 'VIJAY' is coded as</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>How will
 'GARIMA' be coded in the same language?</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
         <is>
           <t>How will
 'GARIMA' be coded in the same language?</t>
         </is>
       </c>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3349,20 +3305,24 @@
 272 ÷ 17 − 196 ÷ ( 5 × 3 + 1) = 30</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>× and −</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>× and −</t>
+          <t>× and +</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>× and +</t>
+          <t>+ and ÷</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>+ and ÷</t>
+          <t>+ and −</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3370,21 +3330,16 @@
           <t>+ and −</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>+ and −</t>
-        </is>
-      </c>
+      <c r="J51" t="inlineStr"/>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3414,42 +3369,41 @@
 III. Some actresses are rich.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Only conclusions II and III follow</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr">
         <is>
+          <t>Only conclusions I and III follow</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>All the conclusions follow</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Only conclusions I and II follow</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Only conclusions I and III follow</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>All the conclusions follow</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Only conclusions I and II follow</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Only conclusions II and III follow</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3470,42 +3424,41 @@
 (35 – 2) × 3 = (56 × 8 ÷ 3 + 100) × 11</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>÷ and +</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>÷ and +</t>
+          <t>× and ÷</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
+          <t>+ and −</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>× and −</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>× and ÷</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>+ and −</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>× and −</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>× and ÷</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3525,42 +3478,41 @@
 logical and meaningful order.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Nice</t>
+        </is>
+      </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>West Europe</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Europe</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>West Europe</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Nice</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3581,39 +3533,38 @@
 831 * 3 * 13 * 45 * 245 * 1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>÷, +, −, =, ×</t>
         </is>
       </c>
-      <c r="G55">
+      <c r="F55">
         <f>, ×, ÷, +, −</f>
         <v/>
       </c>
-      <c r="H55">
+      <c r="G55">
         <f>, −, ÷, +, −</f>
         <v/>
       </c>
-      <c r="I55">
+      <c r="H55">
         <f>, ÷, +, −, ×</f>
         <v/>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>÷, +, −, =, ×</t>
         </is>
       </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3632,42 +3583,41 @@
           <t>What will be the day of the week on 19th November 2053?</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Monday</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Day Based Puzzle</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3690,42 +3640,41 @@
 Section : General Awareness</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>C is the father of A.</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>C is the father of A.</t>
+          <t>B is sister of E’s son.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
+          <t>D is the mother of B’s husband.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>A is the daughter of E’s son.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>B is sister of E’s son.</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>D is the mother of B’s husband.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>A is the daughter of E’s son.</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>B is sister of E’s son.</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3747,39 +3696,38 @@
 A</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>along the path
 s/</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>besides the lake</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>besides the lake</t>
+          <t>She was</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>She was</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
           <t>fond of walking</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3802,38 +3750,37 @@
 s/</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>No error</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>No error</t>
+          <t>in his hand to</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>in his hand to</t>
+          <t>go through it once again</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>go through it once again</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
           <t>Father took the newspaper</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3856,38 +3803,37 @@
 ^</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>policeman</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>policeman</t>
+          <t>a house</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>a house</t>
+          <t>my village</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>my village</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
           <t>a person</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3908,38 +3854,37 @@
 No sooner did we reach at the party that it began to rain.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>before it began to rain</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>before it began to rain</t>
+          <t>as it began to rain</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>as it began to rain</t>
+          <t>it began to rain</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>it began to rain</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
           <t>than it began to rain</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3958,44 +3903,43 @@
           <t>Ill a certain code language, DZLW is coded as 'HDIT and 'CQYH' is coded as ‘GUWF’. What is the code for ‘MTBE</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>QXZC
 in the given code language?</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>YZXB</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>YZXB</t>
+          <t>QZYB</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>QZYB</t>
+          <t>YAYB</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
-        <is>
-          <t>YAYB</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
         <is>
           <t>QXZC
 in the given code language?</t>
         </is>
       </c>
+      <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4014,39 +3958,38 @@
           <t>If 24 July 1999 was Saturday, then what was the day of the week on 28 July 2003?</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
         <is>
           <t>Sunday
 ^^ Download SSO C:GL,( :i dSL E-BOOKS ^—^</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Day Based Puzzle</t>
         </is>
       </c>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4072,42 +4015,41 @@
 Based on the above, how is Q related to V?</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Mother's father</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Sister</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Mother</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Father's mother</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>Mother's father</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Father's mother</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Mother's father</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4128,34 +4070,33 @@
 following the same logic?</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>VRQM</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VRQM</t>
+          <t>VSQM</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>VSQM</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
           <t>VSPM</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4185,38 +4126,37 @@
 III. Some ladders are stairs.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Only conclusion III follows.</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Only conclusion III follows.</t>
+          <t>Only conclusion I follows.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Only conclusion I follows.</t>
+          <t>Both conclusions I and II follow.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Both conclusions I and II follow.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
           <t>Only conclusion II follows.</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4242,42 +4182,41 @@
 (27, 9, 36)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>(39, 13, 52)</t>
+        </is>
+      </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>(37, 13, 52)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>(39, 13, 54)</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(39, 15, 52)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
           <t>(39, 13, 52)</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>(37, 13, 52)</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>(39, 13, 54)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>(39, 15, 52)</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>(39, 13, 52)</t>
-        </is>
-      </c>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4301,38 +4240,37 @@
 Leaf : Oak</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Needle : Pine</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Needle : Pine</t>
+          <t>Tree : Forest</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tree : Forest</t>
+          <t>Berry : Fruit</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Berry : Fruit</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
           <t>Bulb : Tulip</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4353,38 +4291,37 @@
 62 B 2 D 190 A 5 C 7 = ?</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>93</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
           <t>90</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4404,38 +4341,37 @@
 66,</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>99, 132,</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>99, 132,</t>
+          <t>?</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>231</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
           <t>232</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4457,38 +4393,37 @@
 position in the letter cluster)</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>PKRI</t>
+        </is>
+      </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>PKRI</t>
+          <t>MNOL</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>MNOL</t>
+          <t>AZCX</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>AZCX</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
           <t>PLRI</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4509,38 +4444,37 @@
 following the same logic?</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>KPNP</t>
+        </is>
+      </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KPNP</t>
+          <t>KOMO</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>KOMO</t>
+          <t>KMON</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KMON</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
           <t>KNMN</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
+      <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4560,34 +4494,33 @@
 Dh57erk</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>kisveha</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>kisveha</t>
+          <t>Mi 97 S ri Cl</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mi 97 S ri Cl</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
           <t>M J a V 2 ri a</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4606,38 +4539,37 @@
           <t>A number increased by 20% gives</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Find the number.</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Find the number.</t>
+          <t>250</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>280</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
           <t>200</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4657,41 +4589,40 @@
 group?</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Their skin is covered with scales/plates and their hearts have only two chambers.</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
-        <is>
-          <t>Their skin is covered with scales/plates and their hearts have only two chambers.</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>They are ectothermic animals having mucus glands in the skin, and a three­
 chambered heart.</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>They are warm-blooded, oviparous, bipedal, feathered, winged and toothless
 vertebrates.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>They are characterised by having an elongated eel-like body, circular mouth, slimy
 skin and are scaleless.</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Circular Seating Arrangement</t>
         </is>
       </c>
+      <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4710,44 +4641,43 @@
           <t>__________ was named as the new Shiv Sena president at the party national executive</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Eknath Shinde
 meeting in Mumbai in</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Narayan Rane</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Narayan Rane</t>
+          <t>Rahul Ramesh Shewale</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Rahul Ramesh Shewale</t>
+          <t>Aditya Uddhav Thackeray</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
-        <is>
-          <t>Aditya Uddhav Thackeray</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
         <is>
           <t>Eknath Shinde
 meeting in Mumbai in</t>
         </is>
       </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Time Slot / Scheduling Puzzle</t>
         </is>
       </c>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4766,42 +4696,41 @@
           <t>The famous folk music of Rajasthan that was developed in royal courts is known as:</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Maand</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>Lavani</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Sohar</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Dandiya</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
           <t>Maand</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Lavani</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>Sohar</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Dandiya</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Maand</t>
-        </is>
-      </c>
+      <c r="J77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4820,38 +4749,37 @@
           <t>Where did India win its last Olympic medal in men’s hockey? (As of March, 2024).</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Rio</t>
+        </is>
+      </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rio</t>
+          <t>Tokyo</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tokyo</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Munich</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
           <t>Mexico City</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Month Based Puzzle</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4871,38 +4799,37 @@
 generating electricity?</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Arsenic-74</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arsenic-74</t>
+          <t>Carbon-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbon-14</t>
+          <t>Uranium- 235</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Uranium- 235</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
           <t>Sodium-24</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
+      <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4921,39 +4848,38 @@
           <t>Which of the following statements about planet Saturn is true?</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Saturn is the fourth planet from the Sun and the largest planet in our solar system.</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr">
-        <is>
-          <t>Saturn is the fourth planet from the Sun and the largest planet in our solar system.</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>Satellites like Enceladus and Titan of Saturn are home to internal oceans, could
 possibly support life.</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Saturn's environment is conducive to life.</t>
+        </is>
+      </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Saturn's environment is conducive to life.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
           <t>Saturn is a massive ball made up mostly of nitrogen.</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
+      <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4973,38 +4899,37 @@
 2021 was passed by the Parliament and it amended the _____ .</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Motor Insurance (Nationalisation) Act, 1980</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motor Insurance (Nationalisation) Act, 1980</t>
+          <t>General Insurance Business (Nationalisation) Act, 1972</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>General Insurance Business (Nationalisation) Act, 1972</t>
+          <t>General Business (Nationalisation) Act, 1970</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>General Business (Nationalisation) Act, 1970</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
           <t>Life Insurance (Nationalisation) Act, 1975</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Month Based Puzzle</t>
         </is>
       </c>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5024,43 +4949,201 @@
 Religions?</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1893</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>1893</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
-        <is>
-          <t>1891</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
         <is>
           <t>1890
 '^^ Download SSO C Page L 23 of 23 1SL E-BOOKS ^—&lt;&lt;</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>1893</t>
         </is>
       </c>
+      <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Mathematical Inequality (Direct)</t>
         </is>
       </c>
+      <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PDF Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Pages Count</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Parsed Questions</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Detected Answer Keys</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Applied Answers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Missing Answers</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Answer Coverage %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Reasoning Questions Kept</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026.pdf</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="n">
+        <v>19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1.pdf</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" t="n">
+        <v>46</v>
+      </c>
+      <c r="D3" t="n">
+        <v>53</v>
+      </c>
+      <c r="E3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>100</v>
+      </c>
+      <c r="H3" t="n">
+        <v>42</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>26</v>
+      </c>
+      <c r="C4" t="n">
+        <v>73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>20</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53</v>
+      </c>
+      <c r="G4" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/extracted/extracted_questions.xlsx
+++ b/data/extracted/extracted_questions.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,6 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="37" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -512,11 +511,6 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>LLM Topic</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
           <t>Solution</t>
         </is>
       </c>
@@ -575,7 +569,6 @@
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,7 +624,6 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -688,7 +680,6 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,67 +691,9 @@
         <v>3</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>In a certain code language,
-A+ B means ‘A is the daughter of B’
-A @ B means ‘A is the brother of B’
-A # B means ‘A is the wife of B’
-A % B means ‘A is the father of B’
-Based on the above, how is R related to O if ‘R+A%C@K#O ’?</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Wife's sister</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Wife's mother</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Wife's sister</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Blood Relations (General)</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AP  Technical education service exam 2026</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D6" t="inlineStr">
         <is>
           <t>In this question, statement is followed by two conclusions, numbered I and II. Find out which conclusion is true based on the given
 statements.
@@ -770,29 +703,83 @@
 II. G &lt; E</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Only I is true</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Only II is true</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Both I and II are true</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Neither I nor II is true</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Only II is true</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Mathematical Inequality (Direct)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>A,B,C,S,T and U each scored different marks.Only two people have scored more than A.Only C has scored less than U.S has scored more
+than T but less than B.
+How many people have scored more than S?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Only I is true</t>
+          <t>One</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Only II is true</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Both I and II are true</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Neither I nor II is true</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Only II is true</t>
+          <t>One</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -800,11 +787,10 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Mathematical Inequality (Direct)</t>
+          <t>Ranking (Marks / Score)</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -816,38 +802,37 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A,B,C,S,T and U each scored different marks.Only two people have scored more than A.Only C has scored less than U.S has scored more
-than T but less than B.
-How many people have scored more than S?</t>
+          <t>Which of the following letter-number clusters will replace the question mark (?) in the given series to make it logically complete?
+DER121  , YZM129  , TUH137   , OPC145   , ?</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>JKX153</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Two</t>
+          <t>JKX152</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>JLX153</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Four</t>
+          <t>JZX153</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>One</t>
+          <t>JKX153</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
@@ -855,11 +840,10 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Ranking (Marks / Score)</t>
+          <t>Missing Character / Number</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -871,37 +855,38 @@
         <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Which of the following letter-number clusters will replace the question mark (?) in the given series to make it logically complete?
-DER121  , YZM129  , TUH137   , OPC145   , ?</t>
+          <t>Refer to the following letter, symbol series and answer the question. Counting to be done from left to right only.
+(Left) S @ R N Q Q V + L O Z V Q Y # U D U Z (Right)
+How many such letters are there each of which is immediately preceded by a symbol and also immediately followed by a letter?</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JKX153</t>
+          <t>One</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JKX152</t>
+          <t>Two</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JLX153</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>JZX153</t>
+          <t>Four</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>JKX153</t>
+          <t>Three</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -909,11 +894,10 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Missing Character / Number</t>
+          <t>Symbol Coding</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -922,16 +906,17 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refer to the following letter, symbol series and answer the question. Counting to be done from left to right only.
-(Left) S @ R N Q Q V + L O Z V Q Y # U D U Z (Right)
-How many such letters are there each of which is immediately preceded by a symbol and also immediately followed by a letter?</t>
+          <t>Refer to the following letter, number, symbol series and answer the question. Counting to be done from left to right. All numbers are
+single-digit numbers.
+(Left) 8 2 F N &amp; C U &amp; A Q X P 2 7 X ? 3 W / W @ $ (Right)
+How many such symbols are there each of which is immediately preceded by a letter and also immediately followed by a number?</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -956,7 +941,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Three</t>
+          <t>One</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -968,7 +953,6 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -980,65 +964,9 @@
         <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>Refer to the following letter, number, symbol series and answer the question. Counting to be done from left to right. All numbers are
-single-digit numbers.
-(Left) 8 2 F N &amp; C U &amp; A Q X P 2 7 X ? 3 W / W @ $ (Right)
-How many such symbols are there each of which is immediately preceded by a letter and also immediately followed by a number?</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>One</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Two</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Three</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Four</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>One</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Symbol Coding</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>AP  Technical education service exam 2026</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" t="n">
-        <v>10</v>
-      </c>
-      <c r="D11" t="inlineStr">
         <is>
           <t>In a certain code,
 'laptop and tablet' is coded as 'fp ln cb'
@@ -1048,29 +976,82 @@
 What is the code for 'and'?</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>fb</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>cb</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>tc</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>cb</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Letter Coding (Substitution)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AP  Technical education service exam 2026</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In a certain code language, ‘GOWN’ is coded as ‘4593’ and ‘SOWN’ is coded as ‘9135’.What is the code for ‘S’ in the given code
+language?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>fb</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>cb</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>in</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>tc</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>cb</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -1082,7 +1063,6 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1094,37 +1074,39 @@
         <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>In a certain code language, ‘GOWN’ is coded as ‘4593’ and ‘SOWN’ is coded as ‘9135’.What is the code for ‘S’ in the given code
-language?</t>
+          <t>In the following triad, each group of letters is related to the subsequent one following a certain logic. Select from the given options, the one
+which follows the same logic.
+SINK - NSIK - KNIS
+KIND - NKID - DNIK</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>HOTS - THOS - STOH</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>CARD - CRAD - DRAC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>MIND - IMND - DINM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SHOP - OSHP - HOPS</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>HOTS - THOS - STOH</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1132,11 +1114,10 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Letter Coding (Substitution)</t>
+          <t>Blood Relations (General)</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1148,39 +1129,38 @@
         <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>In the following triad, each group of letters is related to the subsequent one following a certain logic. Select from the given options, the one
-which follows the same logic.
-SINK - NSIK - KNIS
-KIND - NKID - DNIK</t>
+          <t>Based on the alphabetical order, three of the following four are alike in a certain way and thus form a group. Which is the one that does not
+belong to that group?
+(Note: The odd one out is not based on the number of consonants/vowels or their position in the letter cluster)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HOTS - THOS - STOH</t>
+          <t>MRO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CARD - CRAD - DRAC</t>
+          <t>INS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MIND - IMND - DINM</t>
+          <t>NSX</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SHOP - OSHP - HOPS</t>
+          <t>DIN</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>HOTS - THOS - STOH</t>
+          <t>MRO</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1188,11 +1168,10 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Blood Relations (General)</t>
+          <t>Word Classification</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1201,41 +1180,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Based on the alphabetical order, three of the following four are alike in a certain way and thus form a group. Which is the one that does not
-belong to that group?
-(Note: The odd one out is not based on the number of consonants/vowels or their position in the letter cluster)</t>
+          <t>The following contain two pairs of words which are related to each other in a certain way. Three of the following four word pairs are alike
+as these have the same relationship and thus form a group. Which word pair is the one that does not belong to that group?</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>MRO</t>
+          <t>Below-Above</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>INS</t>
+          <t>Select-Choose</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>NSX</t>
+          <t>Trip-Journey</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>DIN</t>
+          <t>Good-Fine</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MRO</t>
+          <t>Below-Above</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1243,79 +1221,2096 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Word Classification</t>
+          <t>Blood Relations (General)</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AP  Technical education service exam 2026</t>
+          <t>Kerala PSC Exam 2024</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>The following contain two pairs of words which are related to each other in a certain way. Three of the following four word pairs are alike
-as these have the same relationship and thus form a group. Which word pair is the one that does not belong to that group?</t>
+          <t>Who among the following was hanged on 23 march,1931 in the lahore Conspiracy
+Case ?</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Below-Above</t>
+          <t>Sury Sen</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Select-Choose</t>
+          <t>Rajguru</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Trip-Journey</t>
+          <t>Chandrashekar Azad</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Good-Fine</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Below-Above</t>
-        </is>
-      </c>
+          <t>None of these</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Blood Relations (General)</t>
+          <t>Month Based Puzzle</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1604&amp;¤ yLoPf]q]pOoLp] v|LkLq WqLr]¤ J¡RÕŸ cˆV W|LkVã¢ BqLp]qOÐO ?</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vLº¡ SYLRz¢</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vL¢ r}Ra</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Rc RsSjLpV</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>^]UlVSlLcV</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>fLRuÕrpOÐvp]¤ JRfLR¨ yUZajWRtpLeV Aa]pÍqLvò¨Ls¾V j]SqLi]
+ˆ]q]¨OÐfV ?
+1) ^oLA¾V&amp;C&amp;CþLo]
+2) RSS
+3) BjÎV oL¡YV
+4) oLSvLp]ðV CP (ml)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Only (1 and 2)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Only (1, 2 and 4)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Only (1, 2 and 3)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>oOWt]sOçvRpŠLU (1, 2, 3 and 4)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sLSzL¡ YPdLSsL\j SWy]¤ 1931 oL¡ˆV 23&amp;jV fLRu krpOÐvq]¤ BqLeV fP¨]
+SsãRÕŸfV ?</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>yPq| Ry¢</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>qL^VYOqO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>\NÎSwX¡ ByLhV</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>CvqLqOoŠ</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>8</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fLRu RWLaO¾]q]¨OÐ NkñLvjWt]¤ wq]pŠL¾SffV ?
+1) NlµV v]†vOoLp] mÌRÕŸfLp]qOÐO SqpV¢ KLlV Rar¡.
+2) ‡c] y¦Sc ASoq]¨¢ v]†vvOoLp] mÌRÕŸ]q]¨OÐO.
+3) 1688&amp;¤ CU…º]¤ oz¾Lp v]†vU jaÐO.
+4) 1949&amp;¤ RR\jp]¤ Shw}p v]†vU RkLŸ]ÕOrRÕŸO.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Only (1 and 3)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Only (2 and 4)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Only (3)</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>oOWt]sOçvRpŠLU (1, 2, 3 and 4)
+a
+-3-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Read the following statements carefully.
+i) Fold mountains are formed due to folding of sedimentary rocks.
+ii) The Urals and the Appalachians are examples of old fold mountains.
+iii) The Andes and the Himalayas are examples of young fold mountains.
+Which of these are true ?</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>All of the above (i, ii and iii)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>i and ii only</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>i and iii only</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ii and iii only</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Syllogism (Two Statement)</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" t="n">
+        <v>13</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Examine the following statements.
+i) The day on which the earth is at perihelion occurs between the winter solstice and
+the vernal equinox of the Northern hemisphere.
+ii) The sun is the farthest from the earth on or around July 4th.
+iii) The seasonal change from summer to winter is due to the inclination of the earth's
+rotational axis to the orbital plane.
+Which of these are true ?</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>i and ii only</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ii and iii only</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>i and iii only</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>All of the above (i, ii and iii)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Month Based Puzzle</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" t="n">
+        <v>10</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>yo}kWLs CNyLSp¤&amp;zoLyV yUZ¡x¾]¤ Daja] Rva]j]¡¾¤ Bvw|RÕaOÐ
+UN ^jr¤ AyU‡]p]Rs NkSop¾]jV AjOWPsoLp] SvLŸV R\pÅ fLRu RWLaO¾]ŸOç
+qL^|°t]¤ JfLeV/JRfL¨pLeV ?
+1) RRsm]q]p
+2) CÍ|
+3) CNyLSp¤
+4) pORReãcV SðãVyV</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Only (1 and 2)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Only (1)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Only (2)</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Only (3 and 4)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>fLRu RWLaO¾]ŸOç NkñLvjW¥ kq]SwLi]¨OW.
+i) va¨¢ A¡ÈSYLt¾]Rs w}fWLs ArOf]W¥¨OU vyÍ v]xOv¾]jOU Cap]¤ nPo]
+Rkq]Rzs]p¢ Bp]q]¨OÐ h]vyU yUnv]¨OÐO.
+ii) ^PRRs 4&amp;SjL Af]jaOS¾L BeV yPq|¢ nPo]p]¤ j]ÐV JãvOU AWRspOttfV.
+iii) Svj¤ oOf¤ w}fWLsU vRqpOç WLsLjOyQfoLp oLãU nPo]pORa Nnoe AˆO
+fº] R£ kq]NWoe fs¾]Ss¨Oç \LpVvLeV.
+Cvp]¤ JfLeV wq] ?</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>i and ii only</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ii and iii only</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>i and iii only</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>oOWt]sOçvRpŠLU (i, ii and iii)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" t="n">
+        <v>15</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>yoONh°t]Rs yPƒÜ^}v]WRt¨Or]ˆOU AÍq}ƒ¾]Rs yPƒÜWe°Rt¨Or]ˆOU
+kb]¨L¢ 2024 RlNmOvq] 8&amp;jV PACE IÐV SkqOç KqO DkNYzU jLy v]Sƒk]ˆO.
+PACE IÐL¤</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>†LËVSãL¦, ISqLy¤, S„LcV, KLx|¢ CS¨Ly]ðU</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>†LËVSãL¦, ISqLy¤, S„LcV, CS¨Ly]ðU</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>†LËVSãL¦, B¤YL, S„LcV, KLx|¢ CS¨Ly]ðU</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>†LËVSãL¦, ASãLo]y¡, S„LcV, CS¨Ly]ðU
+a
+-5-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="n">
+        <v>17</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RBI pORa SoLe]ãr] SkLt]y]Rp yUmÌ]ˆV fLRuÕrpOÐ NkñLvjWt]¤ JfLeV
+wq] ?
+i) RBI BrOoLy¾]RsLq]¨¤ SoLe]ãr] r]SÕL¡ŸV Nky]È}Wq]¨OU.
+ii) RBI Yv¡erLeV SoLe]ãr] SkLt]y] WÚ]ã]pORa IWõV Kl}Sx|L R\p¡SkuVy¦.
+iii) mPC&amp;¤ 7 AUY°tLeOçfV.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Only (i and ii)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Only (i and iii)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Only (ii and iii)</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>All (i, ii and iii)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>8</v>
+      </c>
+      <c r="C26" t="n">
+        <v>26</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>The term ‘eKranti’ is related to</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Automation of Electronic Industry</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Electronic delivery of Services</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>digital Broadband Access</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Solar Electric Project</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>fLRuÕrpOÐ Cj°t]¤ JfLeV 7&amp;LU Rxc|Pt]R£ W¦Wr£V s]ð]sOçfV ?</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>SkLðOWtOU Ras]NYLlOU</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>SkLs}yV</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>RkLfO^jLSqLY|vOU wO\]f~vOU</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>yLoPz]W yOqƒpOU yLoPz]W C¢xOr¢yOU</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>9</v>
+      </c>
+      <c r="C28" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>"C&amp;NWLÍ]' IÐ khU __________ IÐfOoLp] mÌRÕŸ]q]¨OÐO.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CsSNûLe]WV v|vyLp¾]R£ KLSŸLSox¢</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Syvj°tORa CsSNûLe]WV Rcs]vr]</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>c]^]ã¤ SNmLcVmL¢cV BWVyyV</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>SyLtL¡ CsNû]WV kÈf]</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>10</v>
+      </c>
+      <c r="C29" t="n">
+        <v>37</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>When was the ‘Children’s Film Society of India’ established ?</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>11 march 1965</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>21 July 1956</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>21 September 1966</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>11 may 1955</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Month Based Puzzle</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="n">
+        <v>39</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-¤ RRwf|WLs Kt]Ò]WõV Iv]RapLeV ja¨OÐfV ?</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>kLq}yV</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>YL¡o]xV&amp;kL¡Ÿ¢W]¡\ÿ¢</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>o]sLjOU SWL¡Ÿ]j c] BRÒSyLpOU</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Nm]yVSm¢
+a
+-11-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>14</v>
+      </c>
+      <c r="C31" t="n">
+        <v>56</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>What is the next number; 5, 6, 14, 45, __ ?</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Number Series (Missing Term)</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>14</v>
+      </c>
+      <c r="C32" t="n">
+        <v>59</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>In a certain code language dISCIPlINE is written as CHRBHOKHmd. How is
+EdUCATION written in that code ?</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>FEVdBUJPO</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>FCyBBSJNO</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>dCTBZSHNm</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>dCTBBSHNm</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Letter Coding (Substitution)</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>14</v>
+      </c>
+      <c r="C33" t="n">
+        <v>60</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Abel has a brother Tom, Abel is the son of dennis. dany is dennis’s father. In terms
+of relationship what is Tom of dany ?</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Son</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grandson</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Grand father</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Brother
+a
+-14-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" t="n">
+        <v>58</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PQ IÐfV SWNÎU ‘O’ Dç KqO vQ¾¾]R£ v|LyoLeV. P p]¤ aL¢R^£V vqàOW,
+vQ¾¾]¤ R KqO SkLp]£V AapLtRÕaO¾OW, S&amp;¤ P aL¢R^£]Rj yUSpL^]¨OÐ
+QR j]¡Ú]¨OW. ∠ PSQ = 48° BReË]¤ ∠ PQR =</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>48°</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>42°</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>90°</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>96°</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>63</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>If the 6th day of a month is 2 days earlier than Thursday. What day will it be on the
+18th day of the month ?</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Day Based Puzzle</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>64</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>How many triangles are there in the following figure ?</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Counting Figures</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>65</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>deepak walks 1 km towards east, then he turns to south and walks 5 km. Again he
+turns to east and walks 2 km. After this he turns to north and walks 9 km. Now, how
+far is he from his starting point ?</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>16 km</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>7 km</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Direction Sense</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="n">
+        <v>63</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>KqO oLy¾]Rs 6&amp;LU h]vyU v|LuLuV\Sp¨L¥ 2 h]vyU oOÒLReË]¤, oLy¾]Rs 18&amp;LU
+h]vyU JfV h]vyoLp]q]¨OU ?</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>R\Lvÿ</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>mOi¢</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>`Lp¡</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>f]Ë¥</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>17</v>
+      </c>
+      <c r="C39" t="n">
+        <v>66</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>KqO WæLô]Rs Rk¦WOŸ]W¥ Kãvq]p]¤ j]¤¨OÐO. KqO Rk¦WOŸ] qºã¾Oj]ÐOU 17&amp;LU
+òLj¾LeV.  WæLô]¤ INf Rk¦WOŸ]WtOºV ?</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Symbol Coding</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Kerala PSC Exam 2024</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>88</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Find out the correct sentence.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>I think him as a silly boy</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>I think him as to be a silly boy</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>I think to be him as a silly boy</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>I think him a silly boy</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Word Analogy</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="n">
+        <v>5</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>In a certain code language, ‘cart light’ is coded
+as ‘straw handle’, ‘plug light’ is coded as ‘toes
+handle’, and ‘cart plug’ is coded as ‘toes straw’.
+What is the code word for ‘cart’?</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>plug</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>straw</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>handle</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>toes</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Letter Coding (Substitution)</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Which of the following numbers will replace the
+question mark (?) in the given series?
+1, 6, 31, 156, ?, 3906</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2125</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>1225</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Missing Character / Number</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="n">
+        <v>7</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Which two signs should be interchanged to make
+the below equation mathematically correct?
+72 × 6 + 18 ÷ 5 – 9 = 93</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>× and +</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>+ and –</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>÷ and -</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>× and ÷</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Coded Equations / Symbol Operations</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="n">
+        <v>8</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Which of the following numbers will replace the
+question mark (?) in the given series?
+33, 47, 44, 58, 56, 70, 69, ?</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Missing Character / Number</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Select the set in which the numbers are related in
+the same way as are the numbers of the following
+set.
+(NOTE : Operations should be performed on
+the whole numbers, without breaking down
+the numbers into its constituent digits. E.g. 13 -
+Operations on 13 such as adding /subtracting/
+multiplying etc. to 13 can be performed. Breaking
+down 13 into 1 and 3 and then performing
+mathematical operations on 1 and 3 is NOT
+allowe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(20, 30, 450)
+(35, 25, 540)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>(9, 17, 264)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>(20, 9, 297)</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(7,18,225)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Word Analogy</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the fifth letter-
+cluster in the same way as the second letter-
+cluster is related to the first letter-cluster and
+the fourth letter-cluster is related to the third
+letter-cluster.
+YOUR : XPEJ :: TONE : SPLW :: BANK : ?</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>XYOP</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>CBOL</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>ABLQ</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>YZMP</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Select the option that is related to the fifth letter-
+cluster in the same way as the second letter-
+cluster is related to the first letter-cluster and
+the fourth letter-cluster is related to the third
+letter-cluster.
+COMFORT : OCFMTRO :: CONTROL :
+OCTNLOR :: DIGITAL : ?</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>IDIGLAT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>GITALDI</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>GIDLATI</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>LATIGID</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" t="n">
+        <v>11</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Six people are sitting around a circular table
+facing the centre. Kaya is the immediate
+neighbour of Jaya and Tara. Sonal is the
+immediate neighbour of Priya and Swati. Sonal is
+sitting immediate right of Priya, Tara and Swati
+are not sitting immediately next to each other.
+Who is sitting to the immediate left of Priya?</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Tara</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kaya</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Jaya</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Swati</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>2</v>
+      </c>
+      <c r="C49" t="n">
+        <v>12</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Two different positions of the same dice are
+shown having alphabets P to U Find the alphabet
+on the face opposite the face showing ‘U’.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>× and +</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>÷ and +</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Cube and Dice (Standard)</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" t="n">
+        <v>17</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Which letter-cluster will replace the question
+mark (?) to complete the given series?
+ZACF, WXZC, ? , QRTW, NOQT</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>XUVZ</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>XUYZ</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>VWZC</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>TUWZ</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Mixed Letter-Number Coding</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" t="n">
+        <v>18</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>In this question, three statements are given,
+followed by two conclusions numbered I and II.
+Assuming the statements to be true, even if they
+seem to be at variance with commonly known
+facts, decide which of the conclusions logically
+follows/follow from the statements.
+Statements:
+All bottles are bags.
+Some bags are pencils.
+Some pencils are sharpeners.
+Conclusions:
+I.
+Some sharpeners are bottles.
+II.	 Some bottles are pencils.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Both conclusions I and II follow.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Neither conclusion I nor II follows.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Only conclusion II follows.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Only conclusion I follows.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Syllogism (Two Statement)</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Six colleagues A, B, C, D, E and F are having
+lunch together on a circular table at equal
+distance, facing the centre of the circle. D is
+the immediate neighbour of E and B while C
+is the immediate neighbour of A and F. If A is
+to the immediate left of E, then who is on the
+immediate left of C?</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Circular Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C53" t="n">
+        <v>14</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Which of the following terms will replace the
+question mark (?) in the given series?
+EZF, GXH, KTL, QNR, ?</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>WEY</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>YGY</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>YFZ</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>XFZ</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Missing Character / Number</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" t="n">
+        <v>16</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Which two signs should be interchanged to make
+the below equation mathematically correct?
+42 + 16 ÷ 7 – 36 × 16 = 76</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>+ and –</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>÷ and ×</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Coded Equations / Symbol Operations</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SSC-CHSL-Reasoning-PDF</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>5</v>
+      </c>
+      <c r="C55" t="n">
+        <v>42</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Find the odd one out.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Mizoram</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sikkim</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Kohima</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Word Classification</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="B56" t="n">
         <v>1</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C56" t="n">
         <v>1</v>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Select the option that is related to the third word in the same way as the second word
 is related to the first word. (The words must be considered as meaningful English
@@ -1324,55 +3319,54 @@
 Animal : Zoology :: Plant : ?</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Geology</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Palaeontology</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Biology</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Botany</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Botany</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B57" t="n">
         <v>1</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C57" t="n">
         <v>2</v>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>A, B, C, D, E, F, G and H are sitting around a square table not facing the centre. Some
 of them are sitting at the corners while some are sitting at the exact centre of the
@@ -1382,55 +3376,54 @@
 is sitting to the left of F. Who is sitting between A and D?</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B58" t="n">
         <v>1</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C58" t="n">
         <v>3</v>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Which option represents the correct order of the given words as they would appear in
 the English dictionary?
@@ -1441,55 +3434,54 @@
 5 Sadly</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>3, 5, 1, 2, 4</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>5, 1, 3, 2, 4</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>5, 1, 3, 4, 2</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>5, 3, 1, 2, 4</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>5, 1, 3, 2, 4</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B59" t="n">
         <v>2</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C59" t="n">
         <v>4</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>Two Statements are given followed by Two conclusions numbered I and II. Assuming
 the statements to be true, even if they seem to be at variance with commonly known
@@ -1502,163 +3494,160 @@
 II. No jeep is a bus.</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Only conclusion II follows.</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>Neither conclusion I nor II follows.</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Both conclusions I and II follows.</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>Only conclusion I follows.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Both conclusions I and II follows.</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B60" t="n">
         <v>2</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C60" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>In a code language, 'PARUL' is coded as RDTXN and 'MADHU' is coded as ODFKW.
 How will 'VIJAY' be coded in the same language?</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>XKLCB</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>XLLDA</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>XLMDA</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>XMLCA</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>XLLDA</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B61" t="n">
         <v>2</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C61" t="n">
         <v>6</v>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Pointing at a girl, Seema said, “She is my father’s mother’s husband’s only son’s
 daughter.” How is that girl related to Seema?</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Mother’s sister</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Mother</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Daughter</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Sister</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B62" t="n">
         <v>2</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C62" t="n">
         <v>7</v>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>In this question, the statement is followed by two conclusions. Which of the two
 conclusions is/are true?
@@ -1667,382 +3656,375 @@
 II. C &lt; F</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Neither conclusion I nor II is true</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>Both conclusions I and II are true</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Only conclusion II is true</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Only conclusion I is true</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Only conclusion I is true</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
         <is>
           <t>Mathematical Inequality (Direct)</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B63" t="n">
         <v>3</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C63" t="n">
         <v>8</v>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 3, 7, 5, 61, 363 ?</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>3367</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>3348</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>3630</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>3267</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>3367</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="B64" t="n">
         <v>3</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C64" t="n">
         <v>10</v>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>Select the option that represents the letters that, when sequentially placed from left to
 right in the blanks below, will complete the letter series.
 _ M _ B A J M Q _ A _ M Q B _ J _ _ B _</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>J Q B J A M Q A</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>B Q A J M Q A B</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>A M B Q J M J Q</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>J A M M Q A B J</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>J Q B J A M Q A</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
         <is>
           <t>Letter Series</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="B65" t="n">
         <v>4</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C65" t="n">
         <v>12</v>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>Town C is to the south of Town A. Town D is to the west of town A. Town B is to the
 east of town D. Town E is to the south of town B and south-east of Town C. What is the
 position of town A with respect to town B?</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>South</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>West</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B66" t="n">
         <v>4</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C66" t="n">
         <v>13</v>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>In a certain code language, 'DAM’ is coded as '50' and 'PAD' is coded as '47'. How will
 'MAP' be coded in that language?</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="B67" t="n">
         <v>5</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C67" t="n">
         <v>14</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>Select the letter-cluster that will replace the question mark (?) in the given series and
 make it logically complete.
 FRP, HTR, JVT, ?, NZX</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>IWV</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>KWU</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>IUS</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>LXV</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>LXV</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="B68" t="n">
         <v>5</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C68" t="n">
         <v>15</v>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>Which letter cluster will replace the question mark (?) to complete the given series?
 GROW, NJGG, ?, BTQA, ILIK</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>YDER</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F68" t="inlineStr">
         <is>
           <t>VIWQ</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>PSJW</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>UBYQ</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>UBYQ</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B69" t="n">
         <v>5</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C69" t="n">
         <v>16</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>Select the set in which the number are related in the same way as the numbers of the
 given sets. (NOTE : Operations should be performed on the whole numbers, without
@@ -2053,227 +4035,160 @@
 (238, 212, 15)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>(370, 348, 19)</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>(336, 302, 17)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>(142, 126, 11)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>(337, 311, 18)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>(337, 311, 18)</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C30" t="n">
-        <v>17</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Read the given statements and conclusions carefully. Assuming that the information
-given in the statements is true, even if it appears to be at variance with commonly
-known facts, decide which of the given conclusions logically follow(s) from the
-statements.
-Statements:
-• All trojans are fairies.
-• No fairy is a flower.
-• All viruses are trojans.
-Conclusions:
-I. No flower is a trojan.
-II. Some viruses are trojans.
-III. No trojan is a virus.</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Only conclusion I follows</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Only conclusion I and III follow</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Only conclusion I and II follow</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Only conclusion II follows</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Only conclusion I and II follow</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Syllogism (Two Statement)</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
+      <c r="B70" t="n">
         <v>6</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C70" t="n">
         <v>18</v>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 420, 462, 506, ?, 600, 650, 702</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>564</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>552</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>562</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>554</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>552</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="B71" t="n">
         <v>6</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C71" t="n">
         <v>19</v>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>Three of the following four letter-clusters are alike in a certain way and one is different.
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>TWGD</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>ADZE</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>PSKH</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>FIUR</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>ADZE</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
         <is>
           <t>Word Classification</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B72" t="n">
         <v>6</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C72" t="n">
         <v>20</v>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as are the numbers of
 the following set.
@@ -2285,164 +4200,161 @@
 (256, 123, 133)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>(182, 74, 108)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F72" t="inlineStr">
         <is>
           <t>(240, 105, 110)</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>(196, 89, 91)</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>(292, 122, 160)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>(182, 74, 108)</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="B73" t="n">
         <v>6</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C73" t="n">
         <v>21</v>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>Select the correct combination of mathematical signs to sequentially replace the *
 signs and balance the given equation.
 65	*	56	*	8	*	19	*	2	*	34</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>−, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F73" t="inlineStr">
         <is>
           <t>+, +, −, ×, =</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>+, ×, −, ×, =</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>+, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>+, ÷, −, ×, =</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="B74" t="n">
         <v>7</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C74" t="n">
         <v>22</v>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Three of the following four letter-clusters are alike in a certain way and one is different.
 Pick the odd one out.</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>MPJ</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F74" t="inlineStr">
         <is>
           <t>DIB</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>HKE</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>TWQ</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>DIB</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
         <is>
           <t>Word Classification</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B75" t="n">
         <v>7</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C75" t="n">
         <v>23</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>Three statements are given followed by three conclusions numbered I, II and III.
 Assuming the statements to be true, even if they seem to be at variance with
@@ -2458,55 +4370,54 @@
 III. Some nails are pendants.</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Only conclusion III follows</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Only conclusions I and II follow</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Only conclusion I follows</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Only conclusion III follows</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B76" t="n">
         <v>7</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C76" t="n">
         <v>24</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are NOT related in the same way as are the
 numbers of the given set.
@@ -2517,55 +4428,54 @@
 (16, 11, 377)</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>(12, 15, 367)</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>(16, 14, 452)</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>(14, 12, 340)</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>(18, 13, 493)</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>(12, 15, 367)</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B77" t="n">
         <v>7</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C77" t="n">
         <v>25</v>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>Town M is to the west of Town D. Town C is to the south-west of Town D. Town D is to
 the north of Town B. Town A is to the south of Town C. Town M is to the north of Town
@@ -2573,55 +4483,54 @@
 Town M?</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>North</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>East</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>South-east</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>North-west</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>South-east</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B78" t="n">
         <v>8</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C78" t="n">
         <v>26</v>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as the numbers of the
 given sets. (NOTE : Operations should be performed on the whole numbers, without
@@ -2632,110 +4541,108 @@
 (14, 104, 300)</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>(15, 175, 390)</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F78" t="inlineStr">
         <is>
           <t>(17, 131, 410)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>(19, 121, 445)</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>(13, 162, 331)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>(13, 162, 331)</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B79" t="n">
         <v>8</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C79" t="n">
         <v>27</v>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>Which two numbers from amongst the given options should be interchanged to make
 the given equation correct?
 (357 ÷ 2 + 3) ÷ 11 − 4 = (28 × 3 + 7) ÷ 9</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>11 and 28</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F79" t="inlineStr">
         <is>
           <t>2 and 3</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>7 and 9</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2 and 9</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>2 and 3</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B41" t="n">
+      <c r="B80" t="n">
         <v>8</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C80" t="n">
         <v>29</v>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>Select the option that is related to the third number in the same way as the second
 number is related to the first number and the sixth number is related to the fifth
@@ -2743,110 +4650,108 @@
 6 : 43 :: 11 : ? :: 4 : 21</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>122</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F80" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>110</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>133</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B81" t="n">
         <v>9</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C81" t="n">
         <v>31</v>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>Select the option that is related to the third term in the same way as the second term is
 related to the first term and the sixth term is related to the fifth term.
 16 : 50 :: 49 : ? :: 144 : 338</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F81" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>136</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>124</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>128</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B43" t="n">
+      <c r="B82" t="n">
         <v>9</v>
       </c>
-      <c r="C43" t="n">
+      <c r="C82" t="n">
         <v>32</v>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Select the option that is related to the fifth letter-cluster in the same way as the second
 letter-cluster is related to the first letter-cluster and the fourth letter-cluster is related
@@ -2854,109 +4759,107 @@
 MASTER : TSAMRE :: SMILES : LIMSSE :: FLIMSY : ?</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>FLIMYS</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>FILMYS</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>MILFYS</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>MLYFIS</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>MILFYS</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B44" t="n">
+      <c r="B83" t="n">
         <v>9</v>
       </c>
-      <c r="C44" t="n">
+      <c r="C83" t="n">
         <v>33</v>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Which of the following numbers will replace the question mark (?) in the given series?
 144, 127, 110, ?, 76, 59</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B45" t="n">
+      <c r="B84" t="n">
         <v>10</v>
       </c>
-      <c r="C45" t="n">
+      <c r="C84" t="n">
         <v>34</v>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>Six friends A, C, D, E, F and G are sitting in a straight row, facing north. They are
 waiting for their seventh friend B to join. Exactly three people are sitting to the left of
@@ -2964,55 +4867,54 @@
 the immediate left of A, and E is second to the right of A, where will B sit?</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Fourth to the right of F</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>Fifth to the right of G</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>To the immediate right of E</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Third to the right of D</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>Fourth to the right of F</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B46" t="n">
+      <c r="B85" t="n">
         <v>10</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C85" t="n">
         <v>36</v>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as are the numbers of
 the following sets.
@@ -3024,55 +4926,54 @@
 (65, 55, 68)</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>(95,	85,	124)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>(95,	85,	104)</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>(95,	80,	104)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>(90,	85,	104)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>(95,	85,	104)</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B47" t="n">
+      <c r="B86" t="n">
         <v>10</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C86" t="n">
         <v>37</v>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>I, J, K, L, M, N and O are seven friends having different ages. I is elder than K but
 younger than J. K is elder than N but younger than I. J is elder than I but younger than
@@ -3080,109 +4981,107 @@
 many people is between I and N?</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
         <is>
           <t>Year/Age Puzzle</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B48" t="n">
+      <c r="B87" t="n">
         <v>11</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C87" t="n">
         <v>39</v>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>In a certain code language, 'FUTURE' is coded as ‘91’ and ‘MONEY’ is coded as ‘72’.
 How will 'SECURE' be coded in that language?</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>72</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B49" t="n">
+      <c r="B88" t="n">
         <v>12</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C88" t="n">
         <v>41</v>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>Study the given pattern carefully and select the number that can replace the question
 mark (?) in it.
@@ -3195,165 +5094,162 @@
 3 and then performing mathematical operations on 1 and 3 is not allowed)</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
         <is>
           <t>Linear Seating Arrangement</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B50" t="n">
+      <c r="B89" t="n">
         <v>13</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C89" t="n">
         <v>43</v>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>In a code language, 'AMIT' is coded as 86 and 'VIJAY' is coded as</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>How will
 'GARIMA' be coded in the same language?</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>49</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>How will
 'GARIMA' be coded in the same language?</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B51" t="n">
+      <c r="B90" t="n">
         <v>13</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C90" t="n">
         <v>44</v>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>Which two symbols from amongst the given options should be interchanged to make
 the given equation correct?
 272 ÷ 17 − 196 ÷ ( 5 × 3 + 1) = 30</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>× and −</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F90" t="inlineStr">
         <is>
           <t>× and +</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>+ and ÷</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>+ and −</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>+ and −</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B52" t="n">
+      <c r="B91" t="n">
         <v>14</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C91" t="n">
         <v>45</v>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>Three statements are given, followed by three conclusions numbered I, II and III.
 Assuming the statements to be true, even if they seem to be at variance with
@@ -3369,326 +5265,1173 @@
 III. Some actresses are rich.</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E91" t="inlineStr">
         <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F91" t="inlineStr">
         <is>
           <t>Only conclusions I and III follow</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>All the conclusions follow</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>Only conclusions I and II follow</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Only conclusions II and III follow</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B53" t="n">
+      <c r="B92" t="n">
         <v>14</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C92" t="n">
         <v>46</v>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>Which two symbols from amongst the given options should be interchanged to make
 the given equation correct?
 (35 – 2) × 3 = (56 × 8 ÷ 3 + 100) × 11</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>÷ and +</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F92" t="inlineStr">
         <is>
           <t>× and ÷</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>+ and −</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>× and −</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>× and ÷</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
         <is>
           <t>Coded Equations / Symbol Operations</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B54" t="n">
+      <c r="B93" t="n">
         <v>14</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C93" t="n">
         <v>47</v>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>Select the correct option that indicates the arrangement of the following words in a
 logical and meaningful order.</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F93" t="inlineStr">
         <is>
           <t>Europe</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>West Europe</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Nice</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
         <is>
           <t>Direction Sense</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B55" t="n">
+      <c r="B94" t="n">
         <v>14</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C94" t="n">
         <v>48</v>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>Select the correct combination of mathematical signs to replace the * signs and to
 balance the given equation.
 831 * 3 * 13 * 45 * 245 * 1</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>÷, +, −, =, ×</t>
         </is>
       </c>
-      <c r="F55">
+      <c r="F94">
         <f>, ×, ÷, +, −</f>
         <v/>
       </c>
-      <c r="G55">
+      <c r="G94">
         <f>, −, ÷, +, −</f>
         <v/>
       </c>
-      <c r="H55">
+      <c r="H94">
         <f>, ÷, +, −, ×</f>
         <v/>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>÷, +, −, =, ×</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
         <is>
           <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
         </is>
       </c>
-      <c r="B56" t="n">
+      <c r="B95" t="n">
         <v>15</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C95" t="n">
         <v>49</v>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D95" t="inlineStr">
         <is>
           <t>What will be the day of the week on 19th November 2053?</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F95" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
         <is>
           <t>Day Based Puzzle</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>15</v>
-      </c>
-      <c r="C57" t="n">
-        <v>50</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>‘P + Q’ means ‘P is the daughter of Q’.
-‘P % Q’ means ‘P is the son of Q’.
-‘P # Q’ means ‘P is the wife of Q’.
-If A + B # C % D # E, which of the following statements is NOT correct?
-Section : General Awareness</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>C is the father of A.</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>B is sister of E’s son.</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>D is the mother of B’s husband.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>A is the daughter of E’s son.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>B is sister of E’s son.</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>2</v>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Que. 2
+How is H related to J?</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>) Uncle</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>) Father</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>) Brother</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>) Brother-in-law</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Que. 3
+How is M related to G?</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>) Son</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>) Daughter</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>) Brother-in-law</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>) Grandson</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>2</v>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Que. 4
+How is I related to F?</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>) Brother</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>) Sister</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>) Niece</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>) Nephew</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Blood Relations (General)</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>3</v>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Que. 6
+Who is sitting the immediate right of person C?</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>) E</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>) B</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>) H</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>) G</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>3</v>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Que. 7
+Which of the following statement is correct?</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>) G is facing towards the table but sitting opposite A.</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>) F is sitting second to the right of E.</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>) D is third to the left of G.</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>) H is sitting between C and E.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>3</v>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Que. 8
+Who is sitting exactly between the H and D?</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>) E</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>) C</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>) F</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>) A</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Que. 16
+What is the direction of R with respect to V?</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>) North-east</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>) North-west</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>) South-east</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>) South-west</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Direction Sense</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>5</v>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Que. 18
+What is the direction of P with respect to U?</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>) North</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>) North-east</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>) South-west
+Page - 5</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>Direction Sense</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>6</v>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Que. 19
+Direction: In the question below two statements are given followed by two conclusions numbered I and II. You have to
+take the given statements to be true even if they seem to be at variance with commonly known facts. Read all the
+conclusions and then decide which of the given conclusions logically follows from the given statements disregarding
+commonly known facts.
+Statements:
+Some eyes are not worthy.
+Some eyes are lucky.
+Conclusions:
+I. Some worthy are lucky.
+II. No worthy is lucky.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>) Only I follows</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>) Only II follows</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>) Either I or II follows</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>) Neither I nor II follows</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Syllogism (Two Statement)</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>6</v>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Que. 20
+Direction: In the question below three statements are given followed by two conclusions numbered I and II. You have
+to take the given statements to be true even if they seem to be at variance with commonly known facts. Read all the
+conclusions and then decide which of the given conclusions logically follows from the given statements disregarding
+commonly known facts.
+Statements:
+All A are B.
+All B are C.
+Only a few D are C.
+Conclusions:
+I. Some D are not C.
+II. Some D are  A.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>) Only conclusion I follows</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>) Only conclusion II follows</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>) Both conclusion I and II follow</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>) Either conclusion I or II follows</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Syllogism (Two Statement)</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>7</v>
+      </c>
+      <c r="C106" t="n">
+        <v>1</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Que. 22
+Direction:- In the question below are given two statements followed by two conclusions numbered I, II. You have to
+take the given statements to be true even if they seem to be at variance with commonly known facts. Read all the
+conclusions and then decide which of the given conclusions logically follows from the given statements disregarding
+commonly known facts.
+Statements:
+All Eggs are Hen.
+Some Hen are Chicks.
+Conclusion:
+I. Some Eggs are Chicks.
+II. No eggs is Chicks.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>) Only I follows.</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>) Only II follows</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>) Both I and II follows</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>) Either I or II follows</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Syllogism (Two Statement)</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>8</v>
+      </c>
+      <c r="C107" t="n">
+        <v>1</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Que. 26
+Direction: Study the given information carefully and answer the following questions.
+There are eight persons namely P, Q, R, S, T, U, V, and W living in a building with four floors. The ground floor is
+numbered as 1 while the top floor is numbered as</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Each floor has two flats such Flat A and Flat B. Flat A of all floors
+stays vertically in the same line and Flat B of all floors stays vertically in the same line. Flat B of all floors stays east to
+flat A of all floors.
+U lives to the west of P. There are two floors between Q and P who do not live on the ground floor. R and S live on the
+same floor. R lives one floor above W. There is a one-floor gap between P and V and Both live on the same numbered
+flat. W does not live on flat B of any floors. T does not live on flat B. R lives same numbered flat as U
+Who among the following stays on the ground floor?</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>) R</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>) S</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>) U</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Floor Puzzle</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>9</v>
+      </c>
+      <c r="C108" t="n">
+        <v>1</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Que. 27
+Who lives on flat B of third floor?</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>) V</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>) T</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>) R</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>) S</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Floor Puzzle</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>9</v>
+      </c>
+      <c r="C109" t="n">
+        <v>1</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Que. 29
+Four of the following five are similar in a certain way in the group, find the one that does not belong to the group?</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>) P</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>) U</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>) T</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>) W</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Word Classification</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>10</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Que. 32
+Who is sitting opposite to S?</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>) U</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>) V</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>) R</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>) P</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>11</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Que. 37
+Who is sitting second to the left of C?</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>) B</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>) E</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>) F</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>) G</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Que. 39
+Who is sitting to the immediate left of H?</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>) G</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>) B</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>) C</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>) F</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Linear Seating Arrangement</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>11</v>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Que. 40
+Four of the following five are alike in a certain way and thus form a group. Which of the following does not belong to
+the group?</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>) H</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>) A
+Page - 11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Word Classification</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B58" t="n">
+      <c r="B114" t="n">
         <v>1</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C114" t="n">
         <v>1</v>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D114" t="inlineStr">
         <is>
           <t>Parts of the following sentence have been given as options. Select the option that
 contains an error.
@@ -3696,52 +6439,51 @@
 A</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>along the path
 s/</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F114" t="inlineStr">
         <is>
           <t>besides the lake</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>She was</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>fond of walking</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B59" t="n">
+      <c r="B115" t="n">
         <v>1</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C115" t="n">
         <v>2</v>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D115" t="inlineStr">
         <is>
           <t>The following sentence has been divided into parts. One of them may contain an error.
 Select the part that contains the error from the given options. If you don’t find any
@@ -3750,51 +6492,50 @@
 s/</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E115" t="inlineStr">
         <is>
           <t>No error</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F115" t="inlineStr">
         <is>
           <t>in his hand to</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>go through it once again</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Father took the newspaper</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B60" t="n">
+      <c r="B116" t="n">
         <v>1</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C116" t="n">
         <v>3</v>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D116" t="inlineStr">
         <is>
           <t>Parts of the following sentence have been underlined and given as options. Select the
 option that contains an error.
@@ -3803,314 +6544,249 @@
 ^</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>policeman</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F116" t="inlineStr">
         <is>
           <t>a house</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>my village</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>a person</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B61" t="n">
+      <c r="B117" t="n">
         <v>5</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C117" t="n">
         <v>18</v>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D117" t="inlineStr">
         <is>
           <t>Select the most appropriate option that can substitute the underlined segment in the
 given sentence.
 No sooner did we reach at the party that it began to rain.</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E117" t="inlineStr">
         <is>
           <t>before it began to rain</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F117" t="inlineStr">
         <is>
           <t>as it began to rain</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>it began to rain</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>than it began to rain</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B62" t="n">
+      <c r="B118" t="n">
         <v>7</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C118" t="n">
         <v>3</v>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Ill a certain code language, DZLW is coded as 'HDIT and 'CQYH' is coded as ‘GUWF’. What is the code for ‘MTBE</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>QXZC
 in the given code language?</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>YZXB</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>QZYB</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>YAYB</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>QXZC
 in the given code language?</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
         <is>
           <t>Letter Coding (Substitution)</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B63" t="n">
+      <c r="B119" t="n">
         <v>7</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C119" t="n">
         <v>4</v>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>If 24 July 1999 was Saturday, then what was the day of the week on 28 July 2003?</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F119" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G119" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>Sunday
 ^^ Download SSO C:GL,( :i dSL E-BOOKS ^—^</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
         <is>
           <t>Day Based Puzzle</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B64" t="n">
+      <c r="B120" t="n">
         <v>8</v>
       </c>
-      <c r="C64" t="n">
-        <v>5</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>hi a certain language,
-A &amp; B means A is the wife of B,
-A t B means A is the daughter of B,
-A x B means A is the son of B,
-A + B means A is the sister of B and
-A @ B means A is the father of B.
-P&amp;Q@L+T&amp;U@V
-Based on the above, how is Q related to V?</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Mother's father</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Sister</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Mother</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Father's mother</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Mother's father</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Blood Relations (General)</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>8</v>
-      </c>
-      <c r="C65" t="n">
+      <c r="C120" t="n">
         <v>6</v>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>JHDC is related to KGEB in a certain way based on the English alphabetical order. In
 the same way, QOKJ is related to RNLI. To which of the following is USON related,
 following the same logic?</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E120" t="inlineStr">
         <is>
           <t>VRQM</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F120" t="inlineStr">
         <is>
           <t>VSQM</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G120" t="inlineStr">
         <is>
           <t>VSPM</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="N120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B66" t="n">
+      <c r="B121" t="n">
         <v>8</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C121" t="n">
         <v>7</v>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>In this question, three statements are given, followed by three conclusions numbered
 I, II and III. Assuming the statements to be true, even if they seem to be at variance
@@ -4126,51 +6802,50 @@
 III. Some ladders are stairs.</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>Only conclusion III follows.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>Only conclusion I follows.</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G121" t="inlineStr">
         <is>
           <t>Both conclusions I and II follow.</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>Only conclusion II follows.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
         <is>
           <t>Syllogism (Two Statement)</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="N121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B67" t="n">
+      <c r="B122" t="n">
         <v>13</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C122" t="n">
         <v>18</v>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>Select the set in which the numbers are related in the same way as are the numbers of
 the following sets.
@@ -4182,55 +6857,54 @@
 (27, 9, 36)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E122" t="inlineStr">
         <is>
           <t>(39, 13, 52)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>(37, 13, 52)</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="G122" t="inlineStr">
         <is>
           <t>(39, 13, 54)</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>(39, 15, 52)</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>(39, 13, 52)</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="N122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B68" t="n">
+      <c r="B123" t="n">
         <v>13</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C123" t="n">
         <v>19</v>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D123" t="inlineStr">
         <is>
           <t>Select the word-pair that best represents a similar relationship to the one expressed in
 the pair of words given below.
@@ -4240,152 +6914,149 @@
 Leaf : Oak</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E123" t="inlineStr">
         <is>
           <t>Needle : Pine</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F123" t="inlineStr">
         <is>
           <t>Tree : Forest</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="G123" t="inlineStr">
         <is>
           <t>Berry : Fruit</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>Bulb : Tulip</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="N123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B69" t="n">
+      <c r="B124" t="n">
         <v>13</v>
       </c>
-      <c r="C69" t="n">
+      <c r="C124" t="n">
         <v>20</v>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D124" t="inlineStr">
         <is>
           <t>If ‘A’ stands for ’^-', -B‘ stands for ‘x’, ‘C’ stands for *+’ and ‘D’ stands for •-’, what will come in place of the question
 mark (?) in the following equation?
 62 B 2 D 190 A 5 C 7 = ?</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>93</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>92</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="N124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B70" t="n">
+      <c r="B125" t="n">
         <v>13</v>
       </c>
-      <c r="C70" t="n">
+      <c r="C125" t="n">
         <v>21</v>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>What should come in place of the question mark (?) m the given series?
 66,</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>99, 132,</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F125" t="inlineStr">
         <is>
           <t>?</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G125" t="inlineStr">
         <is>
           <t>231</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>232</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
         <is>
           <t>Missing Character / Number</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="N125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B71" t="n">
+      <c r="B126" t="n">
         <v>13</v>
       </c>
-      <c r="C71" t="n">
+      <c r="C126" t="n">
         <v>22</v>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D126" t="inlineStr">
         <is>
           <t>Four letter-clusters have been given, out of which three are alike in some manner and
 one is different. Select the letter-cluster that is different.
@@ -4393,598 +7064,542 @@
 position in the letter cluster)</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>PKRI</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F126" t="inlineStr">
         <is>
           <t>MNOL</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G126" t="inlineStr">
         <is>
           <t>AZCX</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>PLRI</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
         <is>
           <t>Mixed Letter-Number Coding</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="N126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B72" t="n">
+      <c r="B127" t="n">
         <v>14</v>
       </c>
-      <c r="C72" t="n">
+      <c r="C127" t="n">
         <v>24</v>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D127" t="inlineStr">
         <is>
           <t>GJHK is related to IMKM in a certain way based on the English alphabetical order. In
 the same way, QTRU is related to SWUW. To which of the following is ILJM related,
 following the same logic?</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="E127" t="inlineStr">
         <is>
           <t>KPNP</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F127" t="inlineStr">
         <is>
           <t>KOMO</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="G127" t="inlineStr">
         <is>
           <t>KMON</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>KNMN</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
         <is>
           <t>Blood Relations (General)</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="N127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B73" t="n">
+      <c r="B128" t="n">
         <v>14</v>
       </c>
-      <c r="C73" t="n">
+      <c r="C128" t="n">
         <v>25</v>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>Select the correct mirror image of the given figtire when the mirror is placed at NIN as shown below.
 Dh57erk</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>kisveha</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Mi 97 S ri Cl</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>M J a V 2 ri a</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="N128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B74" t="n">
+      <c r="B129" t="n">
         <v>20</v>
       </c>
-      <c r="C74" t="n">
+      <c r="C129" t="n">
         <v>19</v>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>A number increased by 20% gives</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>Find the number.</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F129" t="inlineStr">
         <is>
           <t>250</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>280</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
         <is>
           <t>Symbol Coding</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="N129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B75" t="n">
+      <c r="B130" t="n">
         <v>21</v>
       </c>
-      <c r="C75" t="n">
+      <c r="C130" t="n">
         <v>4</v>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>Which of the following statements most accurately describes the Cyclostomata
 group?</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E130" t="inlineStr">
         <is>
           <t>Their skin is covered with scales/plates and their hearts have only two chambers.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F130" t="inlineStr">
         <is>
           <t>They are ectothermic animals having mucus glands in the skin, and a three­
 chambered heart.</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G130" t="inlineStr">
         <is>
           <t>They are warm-blooded, oviparous, bipedal, feathered, winged and toothless
 vertebrates.</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>They are characterised by having an elongated eel-like body, circular mouth, slimy
 skin and are scaleless.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
         <is>
           <t>Circular Seating Arrangement</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="N130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B76" t="n">
+      <c r="B131" t="n">
         <v>22</v>
       </c>
-      <c r="C76" t="n">
+      <c r="C131" t="n">
         <v>7</v>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D131" t="inlineStr">
         <is>
           <t>__________ was named as the new Shiv Sena president at the party national executive</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E131" t="inlineStr">
         <is>
           <t>Eknath Shinde
 meeting in Mumbai in</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F131" t="inlineStr">
         <is>
           <t>Narayan Rane</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="G131" t="inlineStr">
         <is>
           <t>Rahul Ramesh Shewale</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>Aditya Uddhav Thackeray</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I131" t="inlineStr">
         <is>
           <t>Eknath Shinde
 meeting in Mumbai in</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
         <is>
           <t>Time Slot / Scheduling Puzzle</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="N131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B77" t="n">
+      <c r="B132" t="n">
         <v>22</v>
       </c>
-      <c r="C77" t="n">
+      <c r="C132" t="n">
         <v>8</v>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D132" t="inlineStr">
         <is>
           <t>The famous folk music of Rajasthan that was developed in royal courts is known as:</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E132" t="inlineStr">
         <is>
           <t>Maand</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F132" t="inlineStr">
         <is>
           <t>Lavani</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="G132" t="inlineStr">
         <is>
           <t>Sohar</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>Dandiya</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I132" t="inlineStr">
         <is>
           <t>Maand</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="N132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B78" t="n">
+      <c r="B133" t="n">
         <v>22</v>
       </c>
-      <c r="C78" t="n">
+      <c r="C133" t="n">
         <v>9</v>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>Where did India win its last Olympic medal in men’s hockey? (As of March, 2024).</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>Rio</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Tokyo</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G133" t="inlineStr">
         <is>
           <t>Munich</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>Mexico City</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
         <is>
           <t>Month Based Puzzle</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="N133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B79" t="n">
+      <c r="B134" t="n">
         <v>23</v>
       </c>
-      <c r="C79" t="n">
+      <c r="C134" t="n">
         <v>12</v>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>Which of the following isotopes is used as a fuel in nuclear power plants for
 generating electricity?</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="E134" t="inlineStr">
         <is>
           <t>Arsenic-74</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F134" t="inlineStr">
         <is>
           <t>Carbon-14</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G134" t="inlineStr">
         <is>
           <t>Uranium- 235</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>Sodium-24</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
         <is>
           <t>Word Analogy</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="N134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>23</v>
-      </c>
-      <c r="C80" t="n">
-        <v>14</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Which of the following statements about planet Saturn is true?</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Saturn is the fourth planet from the Sun and the largest planet in our solar system.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Satellites like Enceladus and Titan of Saturn are home to internal oceans, could
-possibly support life.</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Saturn's environment is conducive to life.</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Saturn is a massive ball made up mostly of nitrogen.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>Syllogism (Two Statement)</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>24</v>
-      </c>
-      <c r="C81" t="n">
-        <v>20</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>On 11 August 2021, the General Insurance Business (Nationalisation) Amendment Bill,
-2021 was passed by the Parliament and it amended the _____ .</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Motor Insurance (Nationalisation) Act, 1980</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>General Insurance Business (Nationalisation) Act, 1972</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>General Business (Nationalisation) Act, 1970</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Life Insurance (Nationalisation) Act, 1975</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Month Based Puzzle</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
+      <c r="B135" t="n">
         <v>26</v>
       </c>
-      <c r="C82" t="n">
+      <c r="C135" t="n">
         <v>25</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>In which year did Swami Vivekananda give his speech at the Chicago Parliament of
 Religions?</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E135" t="inlineStr">
         <is>
           <t>1893</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F135" t="inlineStr">
         <is>
           <t>1892</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G135" t="inlineStr">
         <is>
           <t>1891</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>1890
 '^^ Download SSO C Page L 23 of 23 1SL E-BOOKS ^—&lt;&lt;</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I135" t="inlineStr">
         <is>
           <t>1893</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
         <is>
           <t>Mathematical Inequality (Direct)</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ssc-mts-2020-held-on-11-10-2021-shift-1-paper-general-english</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>2</v>
+      </c>
+      <c r="C136" t="n">
+        <v>5</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Select the most appropriate option to substitute the underlined segment in the given
+sentence.
+When have you been waiting for me here?</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>How long</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>How far</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>What time</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>How late</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>How long</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Direction Sense (Shortest Distance)</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4997,7 +7612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -5083,67 +7698,241 @@
         <v>100</v>
       </c>
       <c r="H2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1.pdf</t>
+          <t>CSAT_20UPSC_202023_20Ans._20Key_20English.pdf</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Kerala PSC Exam 2024.pdf</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>24</v>
+      </c>
+      <c r="C4" t="n">
+        <v>162</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>162</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>26</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SSC GD CONSTABLE 10-Jan-2023-Shift-1-Paper.pdf</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>16</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SSC-CHSL-Reasoning-PDF.pdf</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SSC-Stenographer-Question-Paper-18-November-2022-Shift-1.pdf</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" t="n">
+        <v>46</v>
+      </c>
+      <c r="D7" t="n">
+        <v>53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>100</v>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ibps-rrb-po-reasoning-5db69019.pdf</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>34</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>ssc-chsl-tier-1-paper-2024-held-on-11-july-2024-shift-1.pdf</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B9" t="n">
         <v>26</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C9" t="n">
         <v>73</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D9" t="n">
         <v>20</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E9" t="n">
         <v>20</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F9" t="n">
         <v>53</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G9" t="n">
         <v>27.4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H9" t="n">
+        <v>22</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ssc-mts-2020-held-on-11-10-2021-shift-1-paper-general-english.pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="n">
         <v>25</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>25</v>
+      </c>
+      <c r="E10" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
